--- a/Data/External data/mw_cpi.xlsx
+++ b/Data/External data/mw_cpi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tp01040\Downloads\msc-dissertation-roe\Data\External data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A69891A-1615-41B8-88B1-D3B8865093BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F7083D-6E9E-454E-BDF7-DE0EBDBC96F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{CBF8D809-2CCE-4683-B951-0D73F9F5ACB4}"/>
   </bookViews>
@@ -1483,7 +1483,9 @@
       <c r="A2" s="5">
         <v>1999</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="C2" s="5">
         <v>3</v>
       </c>
@@ -1516,7 +1518,9 @@
       <c r="A3" s="5">
         <v>2000</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="C3" s="5">
         <v>3.2</v>
       </c>
@@ -1549,7 +1553,9 @@
       <c r="A4" s="5">
         <v>2001</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="C4" s="5">
         <v>3.5</v>
       </c>
@@ -1582,7 +1588,9 @@
       <c r="A5" s="5">
         <v>2002</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="C5" s="5">
         <v>3.5</v>
       </c>
@@ -1615,7 +1623,9 @@
       <c r="A6" s="5">
         <v>2003</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="C6" s="5">
         <v>3.8</v>
       </c>
@@ -2433,30 +2443,39 @@
         <v>1999</v>
       </c>
       <c r="B2" t="e">
+        <f>IF(ISNA(nom_unconverted!B2),NA(),nom_unconverted!B2/nom_unconverted!$K2*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C2" t="e">
+        <f>IF(ISNA(nom_unconverted!C2),NA(),nom_unconverted!C2/nom_unconverted!$K2*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D2" t="e">
+        <f>IF(ISNA(nom_unconverted!D2),NA(),nom_unconverted!D2/nom_unconverted!$K2*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E2" t="e">
+        <f>IF(ISNA(nom_unconverted!E2),NA(),nom_unconverted!E2/nom_unconverted!$K2*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F2" t="e">
+        <f>IF(ISNA(nom_unconverted!F2),NA(),nom_unconverted!F2/nom_unconverted!$K2*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G2" t="e">
+        <f>IF(ISNA(nom_unconverted!G2),NA(),nom_unconverted!G2/nom_unconverted!$K2*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H2" t="e">
+        <f>IF(ISNA(nom_unconverted!H2),NA(),nom_unconverted!H2/nom_unconverted!$K2*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I2">
+        <f>IF(ISNA(nom_unconverted!I2),NA(),nom_unconverted!I2/nom_unconverted!$K2*100)</f>
         <v>3.7259676122962895</v>
       </c>
       <c r="J2">
+        <f>nom_unconverted!J2/nom_unconverted!$K2*100</f>
         <v>4.4711611347555484</v>
       </c>
     </row>
@@ -2465,31 +2484,40 @@
         <v>2000</v>
       </c>
       <c r="B3" t="e">
+        <f>IF(ISNA(nom_unconverted!B3),NA(),nom_unconverted!B3/nom_unconverted!$K3*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C3" t="e">
+        <f>IF(ISNA(nom_unconverted!C3),NA(),nom_unconverted!C3/nom_unconverted!$K3*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D3" t="e">
+        <f>IF(ISNA(nom_unconverted!D3),NA(),nom_unconverted!D3/nom_unconverted!$K3*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E3" t="e">
+        <f>IF(ISNA(nom_unconverted!E3),NA(),nom_unconverted!E3/nom_unconverted!$K3*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F3" t="e">
+        <f>IF(ISNA(nom_unconverted!F3),NA(),nom_unconverted!F3/nom_unconverted!$K3*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G3" t="e">
+        <f>IF(ISNA(nom_unconverted!G3),NA(),nom_unconverted!G3/nom_unconverted!$K3*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H3" t="e">
+        <f>IF(ISNA(nom_unconverted!H3),NA(),nom_unconverted!H3/nom_unconverted!$K3*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I3">
-        <v>3.9743654531160426</v>
+        <f>IF(ISNA(nom_unconverted!I3),NA(),nom_unconverted!I3/nom_unconverted!$K3*100)</f>
+        <v>3.9279001136179477</v>
       </c>
       <c r="J3">
-        <v>4.5953600551654246</v>
+        <f>nom_unconverted!J3/nom_unconverted!$K3*100</f>
+        <v>4.5416345063707526</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2497,31 +2525,40 @@
         <v>2001</v>
       </c>
       <c r="B4" t="e">
+        <f>IF(ISNA(nom_unconverted!B4),NA(),nom_unconverted!B4/nom_unconverted!$K4*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C4" t="e">
+        <f>IF(ISNA(nom_unconverted!C4),NA(),nom_unconverted!C4/nom_unconverted!$K4*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D4" t="e">
+        <f>IF(ISNA(nom_unconverted!D4),NA(),nom_unconverted!D4/nom_unconverted!$K4*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E4" t="e">
+        <f>IF(ISNA(nom_unconverted!E4),NA(),nom_unconverted!E4/nom_unconverted!$K4*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F4" t="e">
+        <f>IF(ISNA(nom_unconverted!F4),NA(),nom_unconverted!F4/nom_unconverted!$K4*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G4" t="e">
+        <f>IF(ISNA(nom_unconverted!G4),NA(),nom_unconverted!G4/nom_unconverted!$K4*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H4" t="e">
+        <f>IF(ISNA(nom_unconverted!H4),NA(),nom_unconverted!H4/nom_unconverted!$K4*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I4">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_unconverted!I4),NA(),nom_unconverted!I4/nom_unconverted!$K4*100)</f>
+        <v>4.2313024035612399</v>
       </c>
       <c r="J4">
-        <v>5.0921557368049291</v>
+        <f>nom_unconverted!J4/nom_unconverted!$K4*100</f>
+        <v>4.9566685298860236</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2529,31 +2566,40 @@
         <v>2002</v>
       </c>
       <c r="B5" t="e">
+        <f>IF(ISNA(nom_unconverted!B5),NA(),nom_unconverted!B5/nom_unconverted!$K5*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C5" t="e">
+        <f>IF(ISNA(nom_unconverted!C5),NA(),nom_unconverted!C5/nom_unconverted!$K5*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D5" t="e">
+        <f>IF(ISNA(nom_unconverted!D5),NA(),nom_unconverted!D5/nom_unconverted!$K5*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E5" t="e">
+        <f>IF(ISNA(nom_unconverted!E5),NA(),nom_unconverted!E5/nom_unconverted!$K5*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F5" t="e">
+        <f>IF(ISNA(nom_unconverted!F5),NA(),nom_unconverted!F5/nom_unconverted!$K5*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G5" t="e">
+        <f>IF(ISNA(nom_unconverted!G5),NA(),nom_unconverted!G5/nom_unconverted!$K5*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H5" t="e">
+        <f>IF(ISNA(nom_unconverted!H5),NA(),nom_unconverted!H5/nom_unconverted!$K5*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I5">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_unconverted!I5),NA(),nom_unconverted!I5/nom_unconverted!$K5*100)</f>
+        <v>4.1679330469780185</v>
       </c>
       <c r="J5">
-        <v>5.2163546572148061</v>
+        <f>nom_unconverted!J5/nom_unconverted!$K5*100</f>
+        <v>5.0015196563736213</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2561,31 +2607,40 @@
         <v>2003</v>
       </c>
       <c r="B6" t="e">
+        <f>IF(ISNA(nom_unconverted!B6),NA(),nom_unconverted!B6/nom_unconverted!$K6*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C6" t="e">
+        <f>IF(ISNA(nom_unconverted!C6),NA(),nom_unconverted!C6/nom_unconverted!$K6*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D6" t="e">
+        <f>IF(ISNA(nom_unconverted!D6),NA(),nom_unconverted!D6/nom_unconverted!$K6*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E6" t="e">
+        <f>IF(ISNA(nom_unconverted!E6),NA(),nom_unconverted!E6/nom_unconverted!$K6*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F6" t="e">
+        <f>IF(ISNA(nom_unconverted!F6),NA(),nom_unconverted!F6/nom_unconverted!$K6*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G6" t="e">
+        <f>IF(ISNA(nom_unconverted!G6),NA(),nom_unconverted!G6/nom_unconverted!$K6*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H6" t="e">
+        <f>IF(ISNA(nom_unconverted!H6),NA(),nom_unconverted!H6/nom_unconverted!$K6*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I6">
-        <v>4.7195589755753007</v>
+        <f>IF(ISNA(nom_unconverted!I6),NA(),nom_unconverted!I6/nom_unconverted!$K6*100)</f>
+        <v>4.463741038241972</v>
       </c>
       <c r="J6">
-        <v>5.5889514184444353</v>
+        <f>nom_unconverted!J6/nom_unconverted!$K6*100</f>
+        <v>5.2860091242339138</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2593,31 +2648,40 @@
         <v>2004</v>
       </c>
       <c r="B7">
-        <v>3.7259676122962895</v>
+        <f>IF(ISNA(nom_unconverted!B7),NA(),nom_unconverted!B7/nom_unconverted!$K7*100)</f>
+        <v>3.4756803085082799</v>
       </c>
       <c r="C7" t="e">
+        <f>IF(ISNA(nom_unconverted!C7),NA(),nom_unconverted!C7/nom_unconverted!$K7*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D7" t="e">
+        <f>IF(ISNA(nom_unconverted!D7),NA(),nom_unconverted!D7/nom_unconverted!$K7*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E7" t="e">
+        <f>IF(ISNA(nom_unconverted!E7),NA(),nom_unconverted!E7/nom_unconverted!$K7*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F7" t="e">
+        <f>IF(ISNA(nom_unconverted!F7),NA(),nom_unconverted!F7/nom_unconverted!$K7*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G7" t="e">
+        <f>IF(ISNA(nom_unconverted!G7),NA(),nom_unconverted!G7/nom_unconverted!$K7*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H7" t="e">
+        <f>IF(ISNA(nom_unconverted!H7),NA(),nom_unconverted!H7/nom_unconverted!$K7*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I7">
-        <v>5.0921557368049291</v>
+        <f>IF(ISNA(nom_unconverted!I7),NA(),nom_unconverted!I7/nom_unconverted!$K7*100)</f>
+        <v>4.7500964216279824</v>
       </c>
       <c r="J7">
-        <v>6.0236476398790009</v>
+        <f>nom_unconverted!J7/nom_unconverted!$K7*100</f>
+        <v>5.6190164987550517</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2625,31 +2689,40 @@
         <v>2005</v>
       </c>
       <c r="B8">
-        <v>3.7259676122962895</v>
+        <f>IF(ISNA(nom_unconverted!B8),NA(),nom_unconverted!B8/nom_unconverted!$K8*100)</f>
+        <v>3.4045545177744434</v>
       </c>
       <c r="C8" t="e">
+        <f>IF(ISNA(nom_unconverted!C8),NA(),nom_unconverted!C8/nom_unconverted!$K8*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D8" t="e">
+        <f>IF(ISNA(nom_unconverted!D8),NA(),nom_unconverted!D8/nom_unconverted!$K8*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E8" t="e">
+        <f>IF(ISNA(nom_unconverted!E8),NA(),nom_unconverted!E8/nom_unconverted!$K8*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F8" t="e">
+        <f>IF(ISNA(nom_unconverted!F8),NA(),nom_unconverted!F8/nom_unconverted!$K8*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G8" t="e">
+        <f>IF(ISNA(nom_unconverted!G8),NA(),nom_unconverted!G8/nom_unconverted!$K8*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H8" t="e">
+        <f>IF(ISNA(nom_unconverted!H8),NA(),nom_unconverted!H8/nom_unconverted!$K8*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I8">
-        <v>5.2784541174197441</v>
+        <f>IF(ISNA(nom_unconverted!I8),NA(),nom_unconverted!I8/nom_unconverted!$K8*100)</f>
+        <v>4.8231189001804609</v>
       </c>
       <c r="J8">
-        <v>6.272045480698754</v>
+        <f>nom_unconverted!J8/nom_unconverted!$K8*100</f>
+        <v>5.7310001049203123</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2657,31 +2730,40 @@
         <v>2006</v>
       </c>
       <c r="B9">
-        <v>4.0985643735259192</v>
+        <f>IF(ISNA(nom_unconverted!B9),NA(),nom_unconverted!B9/nom_unconverted!$K9*100)</f>
+        <v>3.655249411060483</v>
       </c>
       <c r="C9" t="e">
+        <f>IF(ISNA(nom_unconverted!C9),NA(),nom_unconverted!C9/nom_unconverted!$K9*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D9" t="e">
+        <f>IF(ISNA(nom_unconverted!D9),NA(),nom_unconverted!D9/nom_unconverted!$K9*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E9" t="e">
+        <f>IF(ISNA(nom_unconverted!E9),NA(),nom_unconverted!E9/nom_unconverted!$K9*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F9" t="e">
+        <f>IF(ISNA(nom_unconverted!F9),NA(),nom_unconverted!F9/nom_unconverted!$K9*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G9" t="e">
+        <f>IF(ISNA(nom_unconverted!G9),NA(),nom_unconverted!G9/nom_unconverted!$K9*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H9" t="e">
+        <f>IF(ISNA(nom_unconverted!H9),NA(),nom_unconverted!H9/nom_unconverted!$K9*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I9">
-        <v>5.5268519582394964</v>
+        <f>IF(ISNA(nom_unconverted!I9),NA(),nom_unconverted!I9/nom_unconverted!$K9*100)</f>
+        <v>4.9290484482482269</v>
       </c>
       <c r="J9">
-        <v>6.6446422419283833</v>
+        <f>nom_unconverted!J9/nom_unconverted!$K9*100</f>
+        <v>5.925934651264722</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2689,31 +2771,40 @@
         <v>2007</v>
       </c>
       <c r="B10">
-        <v>4.2227632939357953</v>
+        <f>IF(ISNA(nom_unconverted!B10),NA(),nom_unconverted!B10/nom_unconverted!$K10*100)</f>
+        <v>3.6782312924859499</v>
       </c>
       <c r="C10" t="e">
+        <f>IF(ISNA(nom_unconverted!C10),NA(),nom_unconverted!C10/nom_unconverted!$K10*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D10" t="e">
+        <f>IF(ISNA(nom_unconverted!D10),NA(),nom_unconverted!D10/nom_unconverted!$K10*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E10" t="e">
+        <f>IF(ISNA(nom_unconverted!E10),NA(),nom_unconverted!E10/nom_unconverted!$K10*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F10" t="e">
+        <f>IF(ISNA(nom_unconverted!F10),NA(),nom_unconverted!F10/nom_unconverted!$K10*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G10" t="e">
+        <f>IF(ISNA(nom_unconverted!G10),NA(),nom_unconverted!G10/nom_unconverted!$K10*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H10" t="e">
+        <f>IF(ISNA(nom_unconverted!H10),NA(),nom_unconverted!H10/nom_unconverted!$K10*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I10">
-        <v>5.7131503388543106</v>
+        <f>IF(ISNA(nom_unconverted!I10),NA(),nom_unconverted!I10/nom_unconverted!$K10*100)</f>
+        <v>4.9764305721868736</v>
       </c>
       <c r="J10">
-        <v>6.8557804066251729</v>
+        <f>nom_unconverted!J10/nom_unconverted!$K10*100</f>
+        <v>5.9717166866242479</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2721,31 +2812,40 @@
         <v>2008</v>
       </c>
       <c r="B11">
-        <v>4.3842218904686341</v>
+        <f>IF(ISNA(nom_unconverted!B11),NA(),nom_unconverted!B11/nom_unconverted!$K11*100)</f>
+        <v>3.6889659838609457</v>
       </c>
       <c r="C11" t="e">
+        <f>IF(ISNA(nom_unconverted!C11),NA(),nom_unconverted!C11/nom_unconverted!$K11*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D11" t="e">
+        <f>IF(ISNA(nom_unconverted!D11),NA(),nom_unconverted!D11/nom_unconverted!$K11*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E11" t="e">
+        <f>IF(ISNA(nom_unconverted!E11),NA(),nom_unconverted!E11/nom_unconverted!$K11*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F11" t="e">
+        <f>IF(ISNA(nom_unconverted!F11),NA(),nom_unconverted!F11/nom_unconverted!$K11*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G11" t="e">
+        <f>IF(ISNA(nom_unconverted!G11),NA(),nom_unconverted!G11/nom_unconverted!$K11*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H11" t="e">
+        <f>IF(ISNA(nom_unconverted!H11),NA(),nom_unconverted!H11/nom_unconverted!$K11*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I11">
-        <v>5.9242885035511001</v>
+        <f>IF(ISNA(nom_unconverted!I11),NA(),nom_unconverted!I11/nom_unconverted!$K11*100)</f>
+        <v>4.984806726067057</v>
       </c>
       <c r="J11">
-        <v>7.116598139485915</v>
+        <f>nom_unconverted!J11/nom_unconverted!$K11*100</f>
+        <v>5.9880382684201763</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2753,31 +2853,40 @@
         <v>2009</v>
       </c>
       <c r="B12">
-        <v>4.4339014586325849</v>
+        <f>IF(ISNA(nom_unconverted!B12),NA(),nom_unconverted!B12/nom_unconverted!$K12*100)</f>
+        <v>3.6589877736558298</v>
       </c>
       <c r="C12" t="e">
+        <f>IF(ISNA(nom_unconverted!C12),NA(),nom_unconverted!C12/nom_unconverted!$K12*100)</f>
         <v>#N/A</v>
       </c>
       <c r="D12" t="e">
+        <f>IF(ISNA(nom_unconverted!D12),NA(),nom_unconverted!D12/nom_unconverted!$K12*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E12" t="e">
+        <f>IF(ISNA(nom_unconverted!E12),NA(),nom_unconverted!E12/nom_unconverted!$K12*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F12" t="e">
+        <f>IF(ISNA(nom_unconverted!F12),NA(),nom_unconverted!F12/nom_unconverted!$K12*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G12" t="e">
+        <f>IF(ISNA(nom_unconverted!G12),NA(),nom_unconverted!G12/nom_unconverted!$K12*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H12" t="e">
+        <f>IF(ISNA(nom_unconverted!H12),NA(),nom_unconverted!H12/nom_unconverted!$K12*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I12">
-        <v>5.9988078557970264</v>
+        <f>IF(ISNA(nom_unconverted!I12),NA(),nom_unconverted!I12/nom_unconverted!$K12*100)</f>
+        <v>4.9503952231814177</v>
       </c>
       <c r="J12">
-        <v>7.2035373837728276</v>
+        <f>nom_unconverted!J12/nom_unconverted!$K12*100</f>
+        <v>5.944573974006671</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -2785,30 +2894,39 @@
         <v>2010</v>
       </c>
       <c r="B13">
-        <v>4.5208407029194984</v>
+        <f>IF(ISNA(nom_unconverted!B13),NA(),nom_unconverted!B13/nom_unconverted!$K13*100)</f>
+        <v>3.64</v>
       </c>
       <c r="C13">
-        <v>6.1105868841659152</v>
+        <f>IF(ISNA(nom_unconverted!C13),NA(),nom_unconverted!C13/nom_unconverted!$K13*100)</f>
+        <v>4.92</v>
       </c>
       <c r="D13">
-        <v>7.3649959803056664</v>
+        <f>IF(ISNA(nom_unconverted!D13),NA(),nom_unconverted!D13/nom_unconverted!$K13*100)</f>
+        <v>5.93</v>
       </c>
       <c r="E13" t="e">
+        <f>IF(ISNA(nom_unconverted!E13),NA(),nom_unconverted!E13/nom_unconverted!$K13*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F13" t="e">
+        <f>IF(ISNA(nom_unconverted!F13),NA(),nom_unconverted!F13/nom_unconverted!$K13*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G13" t="e">
+        <f>IF(ISNA(nom_unconverted!G13),NA(),nom_unconverted!G13/nom_unconverted!$K13*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H13" t="e">
+        <f>IF(ISNA(nom_unconverted!H13),NA(),nom_unconverted!H13/nom_unconverted!$K13*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I13" t="e">
+        <f>IF(ISNA(nom_unconverted!I13),NA(),nom_unconverted!I13/nom_unconverted!$K13*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J13" t="e">
+        <f>nom_unconverted!J13/nom_unconverted!$K13*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -2817,30 +2935,39 @@
         <v>2011</v>
       </c>
       <c r="B14">
-        <v>4.5705202710834492</v>
+        <f>IF(ISNA(nom_unconverted!B14),NA(),nom_unconverted!B14/nom_unconverted!$K14*100)</f>
+        <v>3.5433639050791199</v>
       </c>
       <c r="C14">
-        <v>6.1851062364118414</v>
+        <f>IF(ISNA(nom_unconverted!C14),NA(),nom_unconverted!C14/nom_unconverted!$K14*100)</f>
+        <v>4.795095719373375</v>
       </c>
       <c r="D14">
-        <v>7.5512943609204815</v>
+        <f>IF(ISNA(nom_unconverted!D14),NA(),nom_unconverted!D14/nom_unconverted!$K14*100)</f>
+        <v>5.8542534083915898</v>
       </c>
       <c r="E14" t="e">
+        <f>IF(ISNA(nom_unconverted!E14),NA(),nom_unconverted!E14/nom_unconverted!$K14*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F14" t="e">
+        <f>IF(ISNA(nom_unconverted!F14),NA(),nom_unconverted!F14/nom_unconverted!$K14*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G14" t="e">
+        <f>IF(ISNA(nom_unconverted!G14),NA(),nom_unconverted!G14/nom_unconverted!$K14*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H14" t="e">
+        <f>IF(ISNA(nom_unconverted!H14),NA(),nom_unconverted!H14/nom_unconverted!$K14*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I14" t="e">
+        <f>IF(ISNA(nom_unconverted!I14),NA(),nom_unconverted!I14/nom_unconverted!$K14*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J14" t="e">
+        <f>nom_unconverted!J14/nom_unconverted!$K14*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -2849,30 +2976,39 @@
         <v>2012</v>
       </c>
       <c r="B15">
-        <v>4.5705202710834492</v>
+        <f>IF(ISNA(nom_unconverted!B15),NA(),nom_unconverted!B15/nom_unconverted!$K15*100)</f>
+        <v>3.4544722212704428</v>
       </c>
       <c r="C15">
-        <v>6.1851062364118414</v>
+        <f>IF(ISNA(nom_unconverted!C15),NA(),nom_unconverted!C15/nom_unconverted!$K15*100)</f>
+        <v>4.6748020820453284</v>
       </c>
       <c r="D15">
-        <v>7.6879131733713457</v>
+        <f>IF(ISNA(nom_unconverted!D15),NA(),nom_unconverted!D15/nom_unconverted!$K15*100)</f>
+        <v>5.8106475678434899</v>
       </c>
       <c r="E15" t="e">
+        <f>IF(ISNA(nom_unconverted!E15),NA(),nom_unconverted!E15/nom_unconverted!$K15*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F15" t="e">
+        <f>IF(ISNA(nom_unconverted!F15),NA(),nom_unconverted!F15/nom_unconverted!$K15*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G15" t="e">
+        <f>IF(ISNA(nom_unconverted!G15),NA(),nom_unconverted!G15/nom_unconverted!$K15*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H15" t="e">
+        <f>IF(ISNA(nom_unconverted!H15),NA(),nom_unconverted!H15/nom_unconverted!$K15*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I15" t="e">
+        <f>IF(ISNA(nom_unconverted!I15),NA(),nom_unconverted!I15/nom_unconverted!$K15*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J15" t="e">
+        <f>nom_unconverted!J15/nom_unconverted!$K15*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -2881,30 +3017,39 @@
         <v>2013</v>
       </c>
       <c r="B16">
-        <v>4.6201998392474</v>
+        <f>IF(ISNA(nom_unconverted!B16),NA(),nom_unconverted!B16/nom_unconverted!$K16*100)</f>
+        <v>3.4137881871565945</v>
       </c>
       <c r="C16">
-        <v>6.2472056966167795</v>
+        <f>IF(ISNA(nom_unconverted!C16),NA(),nom_unconverted!C16/nom_unconverted!$K16*100)</f>
+        <v>4.6159555326337829</v>
       </c>
       <c r="D16">
-        <v>7.8369518778631964</v>
+        <f>IF(ISNA(nom_unconverted!D16),NA(),nom_unconverted!D16/nom_unconverted!$K16*100)</f>
+        <v>5.7905923282145455</v>
       </c>
       <c r="E16" t="e">
+        <f>IF(ISNA(nom_unconverted!E16),NA(),nom_unconverted!E16/nom_unconverted!$K16*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F16" t="e">
+        <f>IF(ISNA(nom_unconverted!F16),NA(),nom_unconverted!F16/nom_unconverted!$K16*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G16" t="e">
+        <f>IF(ISNA(nom_unconverted!G16),NA(),nom_unconverted!G16/nom_unconverted!$K16*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H16" t="e">
+        <f>IF(ISNA(nom_unconverted!H16),NA(),nom_unconverted!H16/nom_unconverted!$K16*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I16" t="e">
+        <f>IF(ISNA(nom_unconverted!I16),NA(),nom_unconverted!I16/nom_unconverted!$K16*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J16" t="e">
+        <f>nom_unconverted!J16/nom_unconverted!$K16*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -2913,30 +3058,39 @@
         <v>2014</v>
       </c>
       <c r="B17">
-        <v>4.7071390835343134</v>
+        <f>IF(ISNA(nom_unconverted!B17),NA(),nom_unconverted!B17/nom_unconverted!$K17*100)</f>
+        <v>3.428277708520437</v>
       </c>
       <c r="C17">
-        <v>6.3714046170266565</v>
+        <f>IF(ISNA(nom_unconverted!C17),NA(),nom_unconverted!C17/nom_unconverted!$K17*100)</f>
+        <v>4.6403864497915146</v>
       </c>
       <c r="D17">
-        <v>8.0729298266419605</v>
+        <f>IF(ISNA(nom_unconverted!D17),NA(),nom_unconverted!D17/nom_unconverted!$K17*100)</f>
+        <v>5.8796319539268715</v>
       </c>
       <c r="E17" t="e">
+        <f>IF(ISNA(nom_unconverted!E17),NA(),nom_unconverted!E17/nom_unconverted!$K17*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F17" t="e">
+        <f>IF(ISNA(nom_unconverted!F17),NA(),nom_unconverted!F17/nom_unconverted!$K17*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G17" t="e">
+        <f>IF(ISNA(nom_unconverted!G17),NA(),nom_unconverted!G17/nom_unconverted!$K17*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H17" t="e">
+        <f>IF(ISNA(nom_unconverted!H17),NA(),nom_unconverted!H17/nom_unconverted!$K17*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I17" t="e">
+        <f>IF(ISNA(nom_unconverted!I17),NA(),nom_unconverted!I17/nom_unconverted!$K17*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J17" t="e">
+        <f>nom_unconverted!J17/nom_unconverted!$K17*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -2945,30 +3099,39 @@
         <v>2015</v>
       </c>
       <c r="B18">
-        <v>4.8064982198622141</v>
+        <f>IF(ISNA(nom_unconverted!B18),NA(),nom_unconverted!B18/nom_unconverted!$K18*100)</f>
+        <v>3.4878056499953285</v>
       </c>
       <c r="C18">
-        <v>6.5825427817234452</v>
+        <f>IF(ISNA(nom_unconverted!C18),NA(),nom_unconverted!C18/nom_unconverted!$K18*100)</f>
+        <v>4.7765813811305531</v>
       </c>
       <c r="D18">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_unconverted!D18),NA(),nom_unconverted!D18/nom_unconverted!$K18*100)</f>
+        <v>6.0383198591650391</v>
       </c>
       <c r="E18" t="e">
+        <f>IF(ISNA(nom_unconverted!E18),NA(),nom_unconverted!E18/nom_unconverted!$K18*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F18" t="e">
+        <f>IF(ISNA(nom_unconverted!F18),NA(),nom_unconverted!F18/nom_unconverted!$K18*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G18" t="e">
+        <f>IF(ISNA(nom_unconverted!G18),NA(),nom_unconverted!G18/nom_unconverted!$K18*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H18" t="e">
+        <f>IF(ISNA(nom_unconverted!H18),NA(),nom_unconverted!H18/nom_unconverted!$K18*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I18" t="e">
+        <f>IF(ISNA(nom_unconverted!I18),NA(),nom_unconverted!I18/nom_unconverted!$K18*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J18" t="e">
+        <f>nom_unconverted!J18/nom_unconverted!$K18*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -2977,30 +3140,39 @@
         <v>2016</v>
       </c>
       <c r="B19">
-        <v>4.8064982198622141</v>
+        <f>IF(ISNA(nom_unconverted!B19),NA(),nom_unconverted!B19/nom_unconverted!$K19*100)</f>
+        <v>3.4529851486225436</v>
       </c>
       <c r="C19">
-        <v>6.5825427817234452</v>
+        <f>IF(ISNA(nom_unconverted!C19),NA(),nom_unconverted!C19/nom_unconverted!$K19*100)</f>
+        <v>4.7288943895864293</v>
       </c>
       <c r="D19" t="e">
+        <f>IF(ISNA(nom_unconverted!D19),NA(),nom_unconverted!D19/nom_unconverted!$K19*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E19" t="e">
+        <f>IF(ISNA(nom_unconverted!E19),NA(),nom_unconverted!E19/nom_unconverted!$K19*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F19" t="e">
+        <f>IF(ISNA(nom_unconverted!F19),NA(),nom_unconverted!F19/nom_unconverted!$K19*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G19">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_unconverted!G19),NA(),nom_unconverted!G19/nom_unconverted!$K19*100)</f>
+        <v>5.9780363038168067</v>
       </c>
       <c r="H19">
-        <v>8.9423222695110969</v>
+        <f>IF(ISNA(nom_unconverted!H19),NA(),nom_unconverted!H19/nom_unconverted!$K19*100)</f>
+        <v>6.4241584160419416</v>
       </c>
       <c r="I19" t="e">
+        <f>IF(ISNA(nom_unconverted!I19),NA(),nom_unconverted!I19/nom_unconverted!$K19*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J19" t="e">
+        <f>nom_unconverted!J19/nom_unconverted!$K19*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -3009,30 +3181,39 @@
         <v>2017</v>
       </c>
       <c r="B20">
-        <v>5.030056276599991</v>
+        <f>IF(ISNA(nom_unconverted!B20),NA(),nom_unconverted!B20/nom_unconverted!$K20*100)</f>
+        <v>3.5234674187786559</v>
       </c>
       <c r="C20">
-        <v>6.9551395429530745</v>
+        <f>IF(ISNA(nom_unconverted!C20),NA(),nom_unconverted!C20/nom_unconverted!$K20*100)</f>
+        <v>4.8719549494223386</v>
       </c>
       <c r="D20" t="e">
+        <f>IF(ISNA(nom_unconverted!D20),NA(),nom_unconverted!D20/nom_unconverted!$K20*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E20" t="e">
+        <f>IF(ISNA(nom_unconverted!E20),NA(),nom_unconverted!E20/nom_unconverted!$K20*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F20" t="e">
+        <f>IF(ISNA(nom_unconverted!F20),NA(),nom_unconverted!F20/nom_unconverted!$K20*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G20">
-        <v>8.75602388889628</v>
+        <f>IF(ISNA(nom_unconverted!G20),NA(),nom_unconverted!G20/nom_unconverted!$K20*100)</f>
+        <v>6.1334432845406228</v>
       </c>
       <c r="H20">
-        <v>9.3149190307407252</v>
+        <f>IF(ISNA(nom_unconverted!H20),NA(),nom_unconverted!H20/nom_unconverted!$K20*100)</f>
+        <v>6.5249396644049176</v>
       </c>
       <c r="I20" t="e">
+        <f>IF(ISNA(nom_unconverted!I20),NA(),nom_unconverted!I20/nom_unconverted!$K20*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J20" t="e">
+        <f>nom_unconverted!J20/nom_unconverted!$K20*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -3041,30 +3222,39 @@
         <v>2018</v>
       </c>
       <c r="B21">
-        <v>5.2163546572148061</v>
+        <f>IF(ISNA(nom_unconverted!B21),NA(),nom_unconverted!B21/nom_unconverted!$K21*100)</f>
+        <v>3.5720644900318912</v>
       </c>
       <c r="C21">
-        <v>7.3277363041827037</v>
+        <f>IF(ISNA(nom_unconverted!C21),NA(),nom_unconverted!C21/nom_unconverted!$K21*100)</f>
+        <v>5.0179001169495612</v>
       </c>
       <c r="D21" t="e">
+        <f>IF(ISNA(nom_unconverted!D21),NA(),nom_unconverted!D21/nom_unconverted!$K21*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E21" t="e">
+        <f>IF(ISNA(nom_unconverted!E21),NA(),nom_unconverted!E21/nom_unconverted!$K21*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F21" t="e">
+        <f>IF(ISNA(nom_unconverted!F21),NA(),nom_unconverted!F21/nom_unconverted!$K21*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G21">
-        <v>9.1658803262488728</v>
+        <f>IF(ISNA(nom_unconverted!G21),NA(),nom_unconverted!G21/nom_unconverted!$K21*100)</f>
+        <v>6.2766276039131803</v>
       </c>
       <c r="H21">
-        <v>9.7247754680933163</v>
+        <f>IF(ISNA(nom_unconverted!H21),NA(),nom_unconverted!H21/nom_unconverted!$K21*100)</f>
+        <v>6.6593487992737401</v>
       </c>
       <c r="I21" t="e">
+        <f>IF(ISNA(nom_unconverted!I21),NA(),nom_unconverted!I21/nom_unconverted!$K21*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J21" t="e">
+        <f>nom_unconverted!J21/nom_unconverted!$K21*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -3073,30 +3263,39 @@
         <v>2019</v>
       </c>
       <c r="B22">
-        <v>5.4026530378296194</v>
+        <f>IF(ISNA(nom_unconverted!B22),NA(),nom_unconverted!B22/nom_unconverted!$K22*100)</f>
+        <v>3.6364332096525551</v>
       </c>
       <c r="C22">
-        <v>7.6382336052073949</v>
+        <f>IF(ISNA(nom_unconverted!C22),NA(),nom_unconverted!C22/nom_unconverted!$K22*100)</f>
+        <v>5.1411641929570608</v>
       </c>
       <c r="D22" t="e">
+        <f>IF(ISNA(nom_unconverted!D22),NA(),nom_unconverted!D22/nom_unconverted!$K22*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E22" t="e">
+        <f>IF(ISNA(nom_unconverted!E22),NA(),nom_unconverted!E22/nom_unconverted!$K22*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F22" t="e">
+        <f>IF(ISNA(nom_unconverted!F22),NA(),nom_unconverted!F22/nom_unconverted!$K22*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G22">
-        <v>9.5633168715604775</v>
+        <f>IF(ISNA(nom_unconverted!G22),NA(),nom_unconverted!G22/nom_unconverted!$K22*100)</f>
+        <v>6.4369047619137181</v>
       </c>
       <c r="H22">
-        <v>10.196731365650848</v>
+        <f>IF(ISNA(nom_unconverted!H22),NA(),nom_unconverted!H22/nom_unconverted!$K22*100)</f>
+        <v>6.8632452071833283</v>
       </c>
       <c r="I22" t="e">
+        <f>IF(ISNA(nom_unconverted!I22),NA(),nom_unconverted!I22/nom_unconverted!$K22*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J22" t="e">
+        <f>nom_unconverted!J22/nom_unconverted!$K22*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -3105,30 +3304,39 @@
         <v>2020</v>
       </c>
       <c r="B23">
-        <v>5.6510508786493725</v>
+        <f>IF(ISNA(nom_unconverted!B23),NA(),nom_unconverted!B23/nom_unconverted!$K23*100)</f>
+        <v>3.7663579309123154</v>
       </c>
       <c r="C23">
-        <v>8.0108303664370233</v>
+        <f>IF(ISNA(nom_unconverted!C23),NA(),nom_unconverted!C23/nom_unconverted!$K23*100)</f>
+        <v>5.3391227811833923</v>
       </c>
       <c r="D23" t="e">
+        <f>IF(ISNA(nom_unconverted!D23),NA(),nom_unconverted!D23/nom_unconverted!$K23*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E23" t="e">
+        <f>IF(ISNA(nom_unconverted!E23),NA(),nom_unconverted!E23/nom_unconverted!$K23*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F23" t="e">
+        <f>IF(ISNA(nom_unconverted!F23),NA(),nom_unconverted!F23/nom_unconverted!$K23*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G23">
-        <v>10.184311473609858</v>
+        <f>IF(ISNA(nom_unconverted!G23),NA(),nom_unconverted!G23/nom_unconverted!$K23*100)</f>
+        <v>6.7877219853804363</v>
       </c>
       <c r="H23">
-        <v>10.830145859741217</v>
+        <f>IF(ISNA(nom_unconverted!H23),NA(),nom_unconverted!H23/nom_unconverted!$K23*100)</f>
+        <v>7.2181628917704161</v>
       </c>
       <c r="I23" t="e">
+        <f>IF(ISNA(nom_unconverted!I23),NA(),nom_unconverted!I23/nom_unconverted!$K23*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J23" t="e">
+        <f>nom_unconverted!J23/nom_unconverted!$K23*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -3137,30 +3345,39 @@
         <v>2021</v>
       </c>
       <c r="B24">
-        <v>5.7379901229362869</v>
+        <f>IF(ISNA(nom_unconverted!B24),NA(),nom_unconverted!B24/nom_unconverted!$K24*100)</f>
+        <v>3.7303576503974472</v>
       </c>
       <c r="C24">
-        <v>8.1474491788878858</v>
+        <f>IF(ISNA(nom_unconverted!C24),NA(),nom_unconverted!C24/nom_unconverted!$K24*100)</f>
+        <v>5.2967848888760285</v>
       </c>
       <c r="D24" t="e">
+        <f>IF(ISNA(nom_unconverted!D24),NA(),nom_unconverted!D24/nom_unconverted!$K24*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E24" t="e">
+        <f>IF(ISNA(nom_unconverted!E24),NA(),nom_unconverted!E24/nom_unconverted!$K24*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F24" t="e">
+        <f>IF(ISNA(nom_unconverted!F24),NA(),nom_unconverted!F24/nom_unconverted!$K24*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G24">
-        <v>10.383029746265661</v>
+        <f>IF(ISNA(nom_unconverted!G24),NA(),nom_unconverted!G24/nom_unconverted!$K24*100)</f>
+        <v>6.7501709864334751</v>
       </c>
       <c r="H24">
-        <v>11.066123808519981</v>
+        <f>IF(ISNA(nom_unconverted!H24),NA(),nom_unconverted!H24/nom_unconverted!$K24*100)</f>
+        <v>7.1942611829093632</v>
       </c>
       <c r="I24" t="e">
+        <f>IF(ISNA(nom_unconverted!I24),NA(),nom_unconverted!I24/nom_unconverted!$K24*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J24" t="e">
+        <f>nom_unconverted!J24/nom_unconverted!$K24*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -3169,30 +3386,39 @@
         <v>2022</v>
       </c>
       <c r="B25">
-        <v>5.973968071715051</v>
+        <f>IF(ISNA(nom_unconverted!B25),NA(),nom_unconverted!B25/nom_unconverted!$K25*100)</f>
+        <v>3.5986813333286114</v>
       </c>
       <c r="C25">
-        <v>8.4827862639945533</v>
+        <f>IF(ISNA(nom_unconverted!C25),NA(),nom_unconverted!C25/nom_unconverted!$K25*100)</f>
+        <v>5.1099778600071559</v>
       </c>
       <c r="D25" t="e">
+        <f>IF(ISNA(nom_unconverted!D25),NA(),nom_unconverted!D25/nom_unconverted!$K25*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E25">
-        <v>11.401460893626647</v>
+        <f>IF(ISNA(nom_unconverted!E25),NA(),nom_unconverted!E25/nom_unconverted!$K25*100)</f>
+        <v>6.8681693638163521</v>
       </c>
       <c r="F25">
-        <v>11.798897438938251</v>
+        <f>IF(ISNA(nom_unconverted!F25),NA(),nom_unconverted!F25/nom_unconverted!$K25*100)</f>
+        <v>7.1075826749733491</v>
       </c>
       <c r="G25" t="e">
+        <f>IF(ISNA(nom_unconverted!G25),NA(),nom_unconverted!G25/nom_unconverted!$K25*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H25" t="e">
+        <f>IF(ISNA(nom_unconverted!H25),NA(),nom_unconverted!H25/nom_unconverted!$K25*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I25" t="e">
+        <f>IF(ISNA(nom_unconverted!I25),NA(),nom_unconverted!I25/nom_unconverted!$K25*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J25" t="e">
+        <f>nom_unconverted!J25/nom_unconverted!$K25*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -3201,30 +3427,39 @@
         <v>2023</v>
       </c>
       <c r="B26">
-        <v>6.5577029976414707</v>
+        <f>IF(ISNA(nom_unconverted!B26),NA(),nom_unconverted!B26/nom_unconverted!$K26*100)</f>
+        <v>3.6990101072046406</v>
       </c>
       <c r="C26">
-        <v>9.3024991386997371</v>
+        <f>IF(ISNA(nom_unconverted!C26),NA(),nom_unconverted!C26/nom_unconverted!$K26*100)</f>
+        <v>5.2472700195005224</v>
       </c>
       <c r="D26" t="e">
+        <f>IF(ISNA(nom_unconverted!D26),NA(),nom_unconverted!D26/nom_unconverted!$K26*100)</f>
         <v>#N/A</v>
       </c>
       <c r="E26">
-        <v>12.64345009772541</v>
+        <f>IF(ISNA(nom_unconverted!E26),NA(),nom_unconverted!E26/nom_unconverted!$K26*100)</f>
+        <v>7.1318035779059166</v>
       </c>
       <c r="F26">
-        <v>12.941527506709113</v>
+        <f>IF(ISNA(nom_unconverted!F26),NA(),nom_unconverted!F26/nom_unconverted!$K26*100)</f>
+        <v>7.2999404009606739</v>
       </c>
       <c r="G26" t="e">
+        <f>IF(ISNA(nom_unconverted!G26),NA(),nom_unconverted!G26/nom_unconverted!$K26*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H26" t="e">
+        <f>IF(ISNA(nom_unconverted!H26),NA(),nom_unconverted!H26/nom_unconverted!$K26*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I26" t="e">
+        <f>IF(ISNA(nom_unconverted!I26),NA(),nom_unconverted!I26/nom_unconverted!$K26*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J26" t="e">
+        <f>nom_unconverted!J26/nom_unconverted!$K26*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -3233,30 +3468,39 @@
         <v>2024</v>
       </c>
       <c r="B27">
-        <v>7.9487309062320852</v>
+        <f>IF(ISNA(nom_unconverted!B27),NA(),nom_unconverted!B27/nom_unconverted!$K27*100)</f>
+        <v>4.3416096864427214</v>
       </c>
       <c r="C27">
-        <v>10.681107155249364</v>
+        <f>IF(ISNA(nom_unconverted!C27),NA(),nom_unconverted!C27/nom_unconverted!$K27*100)</f>
+        <v>5.8340380161574057</v>
       </c>
       <c r="D27">
-        <v>14.208356494889852</v>
+        <f>IF(ISNA(nom_unconverted!D27),NA(),nom_unconverted!D27/nom_unconverted!$K27*100)</f>
+        <v>7.7606273145163618</v>
       </c>
       <c r="E27" t="e">
+        <f>IF(ISNA(nom_unconverted!E27),NA(),nom_unconverted!E27/nom_unconverted!$K27*100)</f>
         <v>#N/A</v>
       </c>
       <c r="F27" t="e">
+        <f>IF(ISNA(nom_unconverted!F27),NA(),nom_unconverted!F27/nom_unconverted!$K27*100)</f>
         <v>#N/A</v>
       </c>
       <c r="G27" t="e">
+        <f>IF(ISNA(nom_unconverted!G27),NA(),nom_unconverted!G27/nom_unconverted!$K27*100)</f>
         <v>#N/A</v>
       </c>
       <c r="H27" t="e">
+        <f>IF(ISNA(nom_unconverted!H27),NA(),nom_unconverted!H27/nom_unconverted!$K27*100)</f>
         <v>#N/A</v>
       </c>
       <c r="I27" t="e">
+        <f>IF(ISNA(nom_unconverted!I27),NA(),nom_unconverted!I27/nom_unconverted!$K27*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J27" t="e">
+        <f>nom_unconverted!J27/nom_unconverted!$K27*100</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -3313,30 +3557,39 @@
         <v>1999</v>
       </c>
       <c r="B2" t="e">
+        <f>IF(ISNA(nom_converted!B2),NA(),nom_converted!B2/nom_converted!$K2*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C2">
+        <f>IF(ISNA(nom_converted!C2),NA(),nom_converted!C2/nom_converted!$K2*100)</f>
         <v>3.7259676122962895</v>
       </c>
       <c r="D2">
+        <f>IF(ISNA(nom_converted!D2),NA(),nom_converted!D2/nom_converted!$K2*100)</f>
         <v>3.7259676122962895</v>
       </c>
       <c r="E2">
+        <f>IF(ISNA(nom_converted!E2),NA(),nom_converted!E2/nom_converted!$K2*100)</f>
         <v>3.7259676122962895</v>
       </c>
       <c r="F2">
+        <f>IF(ISNA(nom_converted!F2),NA(),nom_converted!F2/nom_converted!$K2*100)</f>
         <v>3.7259676122962895</v>
       </c>
       <c r="G2">
+        <f>IF(ISNA(nom_converted!G2),NA(),nom_converted!G2/nom_converted!$K2*100)</f>
         <v>4.4711611347555484</v>
       </c>
       <c r="H2">
+        <f>IF(ISNA(nom_converted!H2),NA(),nom_converted!H2/nom_converted!$K2*100)</f>
         <v>4.4711611347555484</v>
       </c>
       <c r="I2">
+        <f>IF(ISNA(nom_converted!I2),NA(),nom_converted!I2/nom_converted!$K2*100)</f>
         <v>4.4711611347555484</v>
       </c>
       <c r="J2">
+        <f>IF(ISNA(nom_converted!J2),NA(),nom_converted!J2/nom_converted!$K2*100)</f>
         <v>4.4711611347555484</v>
       </c>
       <c r="K2">
@@ -3348,31 +3601,40 @@
         <v>2000</v>
       </c>
       <c r="B3" t="e">
+        <f>IF(ISNA(nom_converted!B3),NA(),nom_converted!B3/nom_converted!$K3*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C3">
-        <v>3.9743654531160426</v>
+        <f>IF(ISNA(nom_converted!C3),NA(),nom_converted!C3/nom_converted!$K3*100)</f>
+        <v>3.9279001136179477</v>
       </c>
       <c r="D3">
-        <v>3.9743654531160426</v>
+        <f>IF(ISNA(nom_converted!D3),NA(),nom_converted!D3/nom_converted!$K3*100)</f>
+        <v>3.9279001136179477</v>
       </c>
       <c r="E3">
-        <v>3.9743654531160426</v>
+        <f>IF(ISNA(nom_converted!E3),NA(),nom_converted!E3/nom_converted!$K3*100)</f>
+        <v>3.9279001136179477</v>
       </c>
       <c r="F3">
-        <v>3.9743654531160426</v>
+        <f>IF(ISNA(nom_converted!F3),NA(),nom_converted!F3/nom_converted!$K3*100)</f>
+        <v>3.9279001136179477</v>
       </c>
       <c r="G3">
-        <v>4.5953600551654246</v>
+        <f>IF(ISNA(nom_converted!G3),NA(),nom_converted!G3/nom_converted!$K3*100)</f>
+        <v>4.5416345063707526</v>
       </c>
       <c r="H3">
-        <v>4.5953600551654246</v>
+        <f>IF(ISNA(nom_converted!H3),NA(),nom_converted!H3/nom_converted!$K3*100)</f>
+        <v>4.5416345063707526</v>
       </c>
       <c r="I3">
-        <v>4.5953600551654246</v>
+        <f>IF(ISNA(nom_converted!I3),NA(),nom_converted!I3/nom_converted!$K3*100)</f>
+        <v>4.5416345063707526</v>
       </c>
       <c r="J3">
-        <v>4.5953600551654246</v>
+        <f>IF(ISNA(nom_converted!J3),NA(),nom_converted!J3/nom_converted!$K3*100)</f>
+        <v>4.5416345063707526</v>
       </c>
       <c r="K3">
         <v>81.468466800000002</v>
@@ -3383,31 +3645,40 @@
         <v>2001</v>
       </c>
       <c r="B4" t="e">
+        <f>IF(ISNA(nom_converted!B4),NA(),nom_converted!B4/nom_converted!$K4*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C4">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_converted!C4),NA(),nom_converted!C4/nom_converted!$K4*100)</f>
+        <v>4.2313024035612399</v>
       </c>
       <c r="D4">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_converted!D4),NA(),nom_converted!D4/nom_converted!$K4*100)</f>
+        <v>4.2313024035612399</v>
       </c>
       <c r="E4">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_converted!E4),NA(),nom_converted!E4/nom_converted!$K4*100)</f>
+        <v>4.2313024035612399</v>
       </c>
       <c r="F4">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_converted!F4),NA(),nom_converted!F4/nom_converted!$K4*100)</f>
+        <v>4.2313024035612399</v>
       </c>
       <c r="G4">
-        <v>5.0921557368049291</v>
+        <f>IF(ISNA(nom_converted!G4),NA(),nom_converted!G4/nom_converted!$K4*100)</f>
+        <v>4.9566685298860236</v>
       </c>
       <c r="H4">
-        <v>5.0921557368049291</v>
+        <f>IF(ISNA(nom_converted!H4),NA(),nom_converted!H4/nom_converted!$K4*100)</f>
+        <v>4.9566685298860236</v>
       </c>
       <c r="I4">
-        <v>5.0921557368049291</v>
+        <f>IF(ISNA(nom_converted!I4),NA(),nom_converted!I4/nom_converted!$K4*100)</f>
+        <v>4.9566685298860236</v>
       </c>
       <c r="J4">
-        <v>5.0921557368049291</v>
+        <f>IF(ISNA(nom_converted!J4),NA(),nom_converted!J4/nom_converted!$K4*100)</f>
+        <v>4.9566685298860236</v>
       </c>
       <c r="K4">
         <v>82.716848529999993</v>
@@ -3418,31 +3689,40 @@
         <v>2002</v>
       </c>
       <c r="B5" t="e">
+        <f>IF(ISNA(nom_converted!B5),NA(),nom_converted!B5/nom_converted!$K5*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C5">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_converted!C5),NA(),nom_converted!C5/nom_converted!$K5*100)</f>
+        <v>4.1679330469780185</v>
       </c>
       <c r="D5">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_converted!D5),NA(),nom_converted!D5/nom_converted!$K5*100)</f>
+        <v>4.1679330469780185</v>
       </c>
       <c r="E5">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_converted!E5),NA(),nom_converted!E5/nom_converted!$K5*100)</f>
+        <v>4.1679330469780185</v>
       </c>
       <c r="F5">
-        <v>4.3469622143456714</v>
+        <f>IF(ISNA(nom_converted!F5),NA(),nom_converted!F5/nom_converted!$K5*100)</f>
+        <v>4.1679330469780185</v>
       </c>
       <c r="G5">
-        <v>5.2163546572148061</v>
+        <f>IF(ISNA(nom_converted!G5),NA(),nom_converted!G5/nom_converted!$K5*100)</f>
+        <v>5.0015196563736213</v>
       </c>
       <c r="H5">
-        <v>5.2163546572148061</v>
+        <f>IF(ISNA(nom_converted!H5),NA(),nom_converted!H5/nom_converted!$K5*100)</f>
+        <v>5.0015196563736213</v>
       </c>
       <c r="I5">
-        <v>5.2163546572148061</v>
+        <f>IF(ISNA(nom_converted!I5),NA(),nom_converted!I5/nom_converted!$K5*100)</f>
+        <v>5.0015196563736213</v>
       </c>
       <c r="J5">
-        <v>5.2163546572148061</v>
+        <f>IF(ISNA(nom_converted!J5),NA(),nom_converted!J5/nom_converted!$K5*100)</f>
+        <v>5.0015196563736213</v>
       </c>
       <c r="K5">
         <v>83.974477530000001</v>
@@ -3453,31 +3733,40 @@
         <v>2003</v>
       </c>
       <c r="B6" t="e">
+        <f>IF(ISNA(nom_converted!B6),NA(),nom_converted!B6/nom_converted!$K6*100)</f>
         <v>#N/A</v>
       </c>
       <c r="C6">
-        <v>4.7195589755753007</v>
+        <f>IF(ISNA(nom_converted!C6),NA(),nom_converted!C6/nom_converted!$K6*100)</f>
+        <v>4.463741038241972</v>
       </c>
       <c r="D6">
-        <v>4.7195589755753007</v>
+        <f>IF(ISNA(nom_converted!D6),NA(),nom_converted!D6/nom_converted!$K6*100)</f>
+        <v>4.463741038241972</v>
       </c>
       <c r="E6">
-        <v>4.7195589755753007</v>
+        <f>IF(ISNA(nom_converted!E6),NA(),nom_converted!E6/nom_converted!$K6*100)</f>
+        <v>4.463741038241972</v>
       </c>
       <c r="F6">
-        <v>4.7195589755753007</v>
+        <f>IF(ISNA(nom_converted!F6),NA(),nom_converted!F6/nom_converted!$K6*100)</f>
+        <v>4.463741038241972</v>
       </c>
       <c r="G6">
-        <v>5.5889514184444353</v>
+        <f>IF(ISNA(nom_converted!G6),NA(),nom_converted!G6/nom_converted!$K6*100)</f>
+        <v>5.2860091242339138</v>
       </c>
       <c r="H6">
-        <v>5.5889514184444353</v>
+        <f>IF(ISNA(nom_converted!H6),NA(),nom_converted!H6/nom_converted!$K6*100)</f>
+        <v>5.2860091242339138</v>
       </c>
       <c r="I6">
-        <v>5.5889514184444353</v>
+        <f>IF(ISNA(nom_converted!I6),NA(),nom_converted!I6/nom_converted!$K6*100)</f>
+        <v>5.2860091242339138</v>
       </c>
       <c r="J6">
-        <v>5.5889514184444353</v>
+        <f>IF(ISNA(nom_converted!J6),NA(),nom_converted!J6/nom_converted!$K6*100)</f>
+        <v>5.2860091242339138</v>
       </c>
       <c r="K6">
         <v>85.130386540000003</v>
@@ -3488,31 +3777,40 @@
         <v>2004</v>
       </c>
       <c r="B7">
-        <v>3.7259676122962895</v>
+        <f>IF(ISNA(nom_converted!B7),NA(),nom_converted!B7/nom_converted!$K7*100)</f>
+        <v>3.4756803085082799</v>
       </c>
       <c r="C7">
-        <v>5.0921557368049291</v>
+        <f>IF(ISNA(nom_converted!C7),NA(),nom_converted!C7/nom_converted!$K7*100)</f>
+        <v>4.7500964216279824</v>
       </c>
       <c r="D7">
-        <v>5.0921557368049291</v>
+        <f>IF(ISNA(nom_converted!D7),NA(),nom_converted!D7/nom_converted!$K7*100)</f>
+        <v>4.7500964216279824</v>
       </c>
       <c r="E7">
-        <v>5.0921557368049291</v>
+        <f>IF(ISNA(nom_converted!E7),NA(),nom_converted!E7/nom_converted!$K7*100)</f>
+        <v>4.7500964216279824</v>
       </c>
       <c r="F7">
-        <v>5.0921557368049291</v>
+        <f>IF(ISNA(nom_converted!F7),NA(),nom_converted!F7/nom_converted!$K7*100)</f>
+        <v>4.7500964216279824</v>
       </c>
       <c r="G7">
-        <v>6.0236476398790009</v>
+        <f>IF(ISNA(nom_converted!G7),NA(),nom_converted!G7/nom_converted!$K7*100)</f>
+        <v>5.6190164987550517</v>
       </c>
       <c r="H7">
-        <v>6.0236476398790009</v>
+        <f>IF(ISNA(nom_converted!H7),NA(),nom_converted!H7/nom_converted!$K7*100)</f>
+        <v>5.6190164987550517</v>
       </c>
       <c r="I7">
-        <v>6.0236476398790009</v>
+        <f>IF(ISNA(nom_converted!I7),NA(),nom_converted!I7/nom_converted!$K7*100)</f>
+        <v>5.6190164987550517</v>
       </c>
       <c r="J7">
-        <v>6.0236476398790009</v>
+        <f>IF(ISNA(nom_converted!J7),NA(),nom_converted!J7/nom_converted!$K7*100)</f>
+        <v>5.6190164987550517</v>
       </c>
       <c r="K7">
         <v>86.31403736</v>
@@ -3523,31 +3821,40 @@
         <v>2005</v>
       </c>
       <c r="B8">
-        <v>3.7259676122962895</v>
+        <f>IF(ISNA(nom_converted!B8),NA(),nom_converted!B8/nom_converted!$K8*100)</f>
+        <v>3.4045545177744434</v>
       </c>
       <c r="C8">
-        <v>5.2784541174197441</v>
+        <f>IF(ISNA(nom_converted!C8),NA(),nom_converted!C8/nom_converted!$K8*100)</f>
+        <v>4.8231189001804609</v>
       </c>
       <c r="D8">
-        <v>5.2784541174197441</v>
+        <f>IF(ISNA(nom_converted!D8),NA(),nom_converted!D8/nom_converted!$K8*100)</f>
+        <v>4.8231189001804609</v>
       </c>
       <c r="E8">
-        <v>5.2784541174197441</v>
+        <f>IF(ISNA(nom_converted!E8),NA(),nom_converted!E8/nom_converted!$K8*100)</f>
+        <v>4.8231189001804609</v>
       </c>
       <c r="F8">
-        <v>5.2784541174197441</v>
+        <f>IF(ISNA(nom_converted!F8),NA(),nom_converted!F8/nom_converted!$K8*100)</f>
+        <v>4.8231189001804609</v>
       </c>
       <c r="G8">
-        <v>6.272045480698754</v>
+        <f>IF(ISNA(nom_converted!G8),NA(),nom_converted!G8/nom_converted!$K8*100)</f>
+        <v>5.7310001049203123</v>
       </c>
       <c r="H8">
-        <v>6.272045480698754</v>
+        <f>IF(ISNA(nom_converted!H8),NA(),nom_converted!H8/nom_converted!$K8*100)</f>
+        <v>5.7310001049203123</v>
       </c>
       <c r="I8">
-        <v>6.272045480698754</v>
+        <f>IF(ISNA(nom_converted!I8),NA(),nom_converted!I8/nom_converted!$K8*100)</f>
+        <v>5.7310001049203123</v>
       </c>
       <c r="J8">
-        <v>6.272045480698754</v>
+        <f>IF(ISNA(nom_converted!J8),NA(),nom_converted!J8/nom_converted!$K8*100)</f>
+        <v>5.7310001049203123</v>
       </c>
       <c r="K8">
         <v>88.117255409999999</v>
@@ -3558,31 +3865,40 @@
         <v>2006</v>
       </c>
       <c r="B9">
-        <v>4.0985643735259192</v>
+        <f>IF(ISNA(nom_converted!B9),NA(),nom_converted!B9/nom_converted!$K9*100)</f>
+        <v>3.655249411060483</v>
       </c>
       <c r="C9">
-        <v>5.5268519582394964</v>
+        <f>IF(ISNA(nom_converted!C9),NA(),nom_converted!C9/nom_converted!$K9*100)</f>
+        <v>4.9290484482482269</v>
       </c>
       <c r="D9">
-        <v>5.5268519582394964</v>
+        <f>IF(ISNA(nom_converted!D9),NA(),nom_converted!D9/nom_converted!$K9*100)</f>
+        <v>4.9290484482482269</v>
       </c>
       <c r="E9">
-        <v>5.5268519582394964</v>
+        <f>IF(ISNA(nom_converted!E9),NA(),nom_converted!E9/nom_converted!$K9*100)</f>
+        <v>4.9290484482482269</v>
       </c>
       <c r="F9">
-        <v>5.5268519582394964</v>
+        <f>IF(ISNA(nom_converted!F9),NA(),nom_converted!F9/nom_converted!$K9*100)</f>
+        <v>4.9290484482482269</v>
       </c>
       <c r="G9">
-        <v>6.6446422419283833</v>
+        <f>IF(ISNA(nom_converted!G9),NA(),nom_converted!G9/nom_converted!$K9*100)</f>
+        <v>5.925934651264722</v>
       </c>
       <c r="H9">
-        <v>6.6446422419283833</v>
+        <f>IF(ISNA(nom_converted!H9),NA(),nom_converted!H9/nom_converted!$K9*100)</f>
+        <v>5.925934651264722</v>
       </c>
       <c r="I9">
-        <v>6.6446422419283833</v>
+        <f>IF(ISNA(nom_converted!I9),NA(),nom_converted!I9/nom_converted!$K9*100)</f>
+        <v>5.925934651264722</v>
       </c>
       <c r="J9">
-        <v>6.6446422419283833</v>
+        <f>IF(ISNA(nom_converted!J9),NA(),nom_converted!J9/nom_converted!$K9*100)</f>
+        <v>5.925934651264722</v>
       </c>
       <c r="K9">
         <v>90.281117069999993</v>
@@ -3593,31 +3909,40 @@
         <v>2007</v>
       </c>
       <c r="B10">
-        <v>4.2227632939357953</v>
+        <f>IF(ISNA(nom_converted!B10),NA(),nom_converted!B10/nom_converted!$K10*100)</f>
+        <v>3.6782312924859499</v>
       </c>
       <c r="C10">
-        <v>5.7131503388543106</v>
+        <f>IF(ISNA(nom_converted!C10),NA(),nom_converted!C10/nom_converted!$K10*100)</f>
+        <v>4.9764305721868736</v>
       </c>
       <c r="D10">
-        <v>5.7131503388543106</v>
+        <f>IF(ISNA(nom_converted!D10),NA(),nom_converted!D10/nom_converted!$K10*100)</f>
+        <v>4.9764305721868736</v>
       </c>
       <c r="E10">
-        <v>5.7131503388543106</v>
+        <f>IF(ISNA(nom_converted!E10),NA(),nom_converted!E10/nom_converted!$K10*100)</f>
+        <v>4.9764305721868736</v>
       </c>
       <c r="F10">
-        <v>5.7131503388543106</v>
+        <f>IF(ISNA(nom_converted!F10),NA(),nom_converted!F10/nom_converted!$K10*100)</f>
+        <v>4.9764305721868736</v>
       </c>
       <c r="G10">
-        <v>6.8557804066251729</v>
+        <f>IF(ISNA(nom_converted!G10),NA(),nom_converted!G10/nom_converted!$K10*100)</f>
+        <v>5.9717166866242479</v>
       </c>
       <c r="H10">
-        <v>6.8557804066251729</v>
+        <f>IF(ISNA(nom_converted!H10),NA(),nom_converted!H10/nom_converted!$K10*100)</f>
+        <v>5.9717166866242479</v>
       </c>
       <c r="I10">
-        <v>6.8557804066251729</v>
+        <f>IF(ISNA(nom_converted!I10),NA(),nom_converted!I10/nom_converted!$K10*100)</f>
+        <v>5.9717166866242479</v>
       </c>
       <c r="J10">
-        <v>6.8557804066251729</v>
+        <f>IF(ISNA(nom_converted!J10),NA(),nom_converted!J10/nom_converted!$K10*100)</f>
+        <v>5.9717166866242479</v>
       </c>
       <c r="K10">
         <v>92.43573146</v>
@@ -3628,31 +3953,40 @@
         <v>2008</v>
       </c>
       <c r="B11">
-        <v>4.3842218904686341</v>
+        <f>IF(ISNA(nom_converted!B11),NA(),nom_converted!B11/nom_converted!$K11*100)</f>
+        <v>3.6889659838609457</v>
       </c>
       <c r="C11">
-        <v>5.9242885035511001</v>
+        <f>IF(ISNA(nom_converted!C11),NA(),nom_converted!C11/nom_converted!$K11*100)</f>
+        <v>4.984806726067057</v>
       </c>
       <c r="D11">
-        <v>5.9242885035511001</v>
+        <f>IF(ISNA(nom_converted!D11),NA(),nom_converted!D11/nom_converted!$K11*100)</f>
+        <v>4.984806726067057</v>
       </c>
       <c r="E11">
-        <v>5.9242885035511001</v>
+        <f>IF(ISNA(nom_converted!E11),NA(),nom_converted!E11/nom_converted!$K11*100)</f>
+        <v>4.984806726067057</v>
       </c>
       <c r="F11">
-        <v>5.9242885035511001</v>
+        <f>IF(ISNA(nom_converted!F11),NA(),nom_converted!F11/nom_converted!$K11*100)</f>
+        <v>4.984806726067057</v>
       </c>
       <c r="G11">
-        <v>7.116598139485915</v>
+        <f>IF(ISNA(nom_converted!G11),NA(),nom_converted!G11/nom_converted!$K11*100)</f>
+        <v>5.9880382684201763</v>
       </c>
       <c r="H11">
-        <v>7.116598139485915</v>
+        <f>IF(ISNA(nom_converted!H11),NA(),nom_converted!H11/nom_converted!$K11*100)</f>
+        <v>5.9880382684201763</v>
       </c>
       <c r="I11">
-        <v>7.116598139485915</v>
+        <f>IF(ISNA(nom_converted!I11),NA(),nom_converted!I11/nom_converted!$K11*100)</f>
+        <v>5.9880382684201763</v>
       </c>
       <c r="J11">
-        <v>7.116598139485915</v>
+        <f>IF(ISNA(nom_converted!J11),NA(),nom_converted!J11/nom_converted!$K11*100)</f>
+        <v>5.9880382684201763</v>
       </c>
       <c r="K11">
         <v>95.690771220000002</v>
@@ -3663,31 +3997,40 @@
         <v>2009</v>
       </c>
       <c r="B12">
-        <v>4.4339014586325849</v>
+        <f>IF(ISNA(nom_converted!B12),NA(),nom_converted!B12/nom_converted!$K12*100)</f>
+        <v>3.6589877736558298</v>
       </c>
       <c r="C12">
-        <v>5.9988078557970264</v>
+        <f>IF(ISNA(nom_converted!C12),NA(),nom_converted!C12/nom_converted!$K12*100)</f>
+        <v>4.9503952231814177</v>
       </c>
       <c r="D12">
-        <v>5.9988078557970264</v>
+        <f>IF(ISNA(nom_converted!D12),NA(),nom_converted!D12/nom_converted!$K12*100)</f>
+        <v>4.9503952231814177</v>
       </c>
       <c r="E12">
-        <v>5.9988078557970264</v>
+        <f>IF(ISNA(nom_converted!E12),NA(),nom_converted!E12/nom_converted!$K12*100)</f>
+        <v>4.9503952231814177</v>
       </c>
       <c r="F12">
-        <v>5.9988078557970264</v>
+        <f>IF(ISNA(nom_converted!F12),NA(),nom_converted!F12/nom_converted!$K12*100)</f>
+        <v>4.9503952231814177</v>
       </c>
       <c r="G12">
-        <v>7.2035373837728276</v>
+        <f>IF(ISNA(nom_converted!G12),NA(),nom_converted!G12/nom_converted!$K12*100)</f>
+        <v>5.944573974006671</v>
       </c>
       <c r="H12">
-        <v>7.2035373837728276</v>
+        <f>IF(ISNA(nom_converted!H12),NA(),nom_converted!H12/nom_converted!$K12*100)</f>
+        <v>5.944573974006671</v>
       </c>
       <c r="I12">
-        <v>7.2035373837728276</v>
+        <f>IF(ISNA(nom_converted!I12),NA(),nom_converted!I12/nom_converted!$K12*100)</f>
+        <v>5.944573974006671</v>
       </c>
       <c r="J12">
-        <v>7.2035373837728276</v>
+        <f>IF(ISNA(nom_converted!J12),NA(),nom_converted!J12/nom_converted!$K12*100)</f>
+        <v>5.944573974006671</v>
       </c>
       <c r="K12">
         <v>97.567967449999998</v>
@@ -3698,31 +4041,40 @@
         <v>2010</v>
       </c>
       <c r="B13">
-        <v>4.5208407029194984</v>
+        <f>IF(ISNA(nom_converted!B13),NA(),nom_converted!B13/nom_converted!$K13*100)</f>
+        <v>3.64</v>
       </c>
       <c r="C13">
-        <v>6.1105868841659152</v>
+        <f>IF(ISNA(nom_converted!C13),NA(),nom_converted!C13/nom_converted!$K13*100)</f>
+        <v>4.92</v>
       </c>
       <c r="D13">
-        <v>6.1105868841659152</v>
+        <f>IF(ISNA(nom_converted!D13),NA(),nom_converted!D13/nom_converted!$K13*100)</f>
+        <v>4.92</v>
       </c>
       <c r="E13">
-        <v>6.1105868841659152</v>
+        <f>IF(ISNA(nom_converted!E13),NA(),nom_converted!E13/nom_converted!$K13*100)</f>
+        <v>4.92</v>
       </c>
       <c r="F13">
-        <v>7.3649959803056664</v>
+        <f>IF(ISNA(nom_converted!F13),NA(),nom_converted!F13/nom_converted!$K13*100)</f>
+        <v>5.93</v>
       </c>
       <c r="G13">
-        <v>7.3649959803056664</v>
+        <f>IF(ISNA(nom_converted!G13),NA(),nom_converted!G13/nom_converted!$K13*100)</f>
+        <v>5.93</v>
       </c>
       <c r="H13">
-        <v>7.3649959803056664</v>
+        <f>IF(ISNA(nom_converted!H13),NA(),nom_converted!H13/nom_converted!$K13*100)</f>
+        <v>5.93</v>
       </c>
       <c r="I13">
-        <v>7.3649959803056664</v>
+        <f>IF(ISNA(nom_converted!I13),NA(),nom_converted!I13/nom_converted!$K13*100)</f>
+        <v>5.93</v>
       </c>
       <c r="J13">
-        <v>7.3649959803056664</v>
+        <f>IF(ISNA(nom_converted!J13),NA(),nom_converted!J13/nom_converted!$K13*100)</f>
+        <v>5.93</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3733,31 +4085,40 @@
         <v>2011</v>
       </c>
       <c r="B14">
-        <v>4.5705202710834492</v>
+        <f>IF(ISNA(nom_converted!B14),NA(),nom_converted!B14/nom_converted!$K14*100)</f>
+        <v>3.5433639050791199</v>
       </c>
       <c r="C14">
-        <v>6.1851062364118414</v>
+        <f>IF(ISNA(nom_converted!C14),NA(),nom_converted!C14/nom_converted!$K14*100)</f>
+        <v>4.795095719373375</v>
       </c>
       <c r="D14">
-        <v>6.1851062364118414</v>
+        <f>IF(ISNA(nom_converted!D14),NA(),nom_converted!D14/nom_converted!$K14*100)</f>
+        <v>4.795095719373375</v>
       </c>
       <c r="E14">
-        <v>6.1851062364118414</v>
+        <f>IF(ISNA(nom_converted!E14),NA(),nom_converted!E14/nom_converted!$K14*100)</f>
+        <v>4.795095719373375</v>
       </c>
       <c r="F14">
-        <v>7.5512943609204815</v>
+        <f>IF(ISNA(nom_converted!F14),NA(),nom_converted!F14/nom_converted!$K14*100)</f>
+        <v>5.8542534083915898</v>
       </c>
       <c r="G14">
-        <v>7.5512943609204815</v>
+        <f>IF(ISNA(nom_converted!G14),NA(),nom_converted!G14/nom_converted!$K14*100)</f>
+        <v>5.8542534083915898</v>
       </c>
       <c r="H14">
-        <v>7.5512943609204815</v>
+        <f>IF(ISNA(nom_converted!H14),NA(),nom_converted!H14/nom_converted!$K14*100)</f>
+        <v>5.8542534083915898</v>
       </c>
       <c r="I14">
-        <v>7.5512943609204815</v>
+        <f>IF(ISNA(nom_converted!I14),NA(),nom_converted!I14/nom_converted!$K14*100)</f>
+        <v>5.8542534083915898</v>
       </c>
       <c r="J14">
-        <v>7.5512943609204815</v>
+        <f>IF(ISNA(nom_converted!J14),NA(),nom_converted!J14/nom_converted!$K14*100)</f>
+        <v>5.8542534083915898</v>
       </c>
       <c r="K14">
         <v>103.8561124</v>
@@ -3768,31 +4129,40 @@
         <v>2012</v>
       </c>
       <c r="B15">
-        <v>4.5705202710834492</v>
+        <f>IF(ISNA(nom_converted!B15),NA(),nom_converted!B15/nom_converted!$K15*100)</f>
+        <v>3.4544722212704428</v>
       </c>
       <c r="C15">
-        <v>6.1851062364118414</v>
+        <f>IF(ISNA(nom_converted!C15),NA(),nom_converted!C15/nom_converted!$K15*100)</f>
+        <v>4.6748020820453284</v>
       </c>
       <c r="D15">
-        <v>6.1851062364118414</v>
+        <f>IF(ISNA(nom_converted!D15),NA(),nom_converted!D15/nom_converted!$K15*100)</f>
+        <v>4.6748020820453284</v>
       </c>
       <c r="E15">
-        <v>6.1851062364118414</v>
+        <f>IF(ISNA(nom_converted!E15),NA(),nom_converted!E15/nom_converted!$K15*100)</f>
+        <v>4.6748020820453284</v>
       </c>
       <c r="F15">
-        <v>7.6879131733713457</v>
+        <f>IF(ISNA(nom_converted!F15),NA(),nom_converted!F15/nom_converted!$K15*100)</f>
+        <v>5.8106475678434899</v>
       </c>
       <c r="G15">
-        <v>7.6879131733713457</v>
+        <f>IF(ISNA(nom_converted!G15),NA(),nom_converted!G15/nom_converted!$K15*100)</f>
+        <v>5.8106475678434899</v>
       </c>
       <c r="H15">
-        <v>7.6879131733713457</v>
+        <f>IF(ISNA(nom_converted!H15),NA(),nom_converted!H15/nom_converted!$K15*100)</f>
+        <v>5.8106475678434899</v>
       </c>
       <c r="I15">
-        <v>7.6879131733713457</v>
+        <f>IF(ISNA(nom_converted!I15),NA(),nom_converted!I15/nom_converted!$K15*100)</f>
+        <v>5.8106475678434899</v>
       </c>
       <c r="J15">
-        <v>7.6879131733713457</v>
+        <f>IF(ISNA(nom_converted!J15),NA(),nom_converted!J15/nom_converted!$K15*100)</f>
+        <v>5.8106475678434899</v>
       </c>
       <c r="K15">
         <v>106.5285741</v>
@@ -3803,31 +4173,40 @@
         <v>2013</v>
       </c>
       <c r="B16">
-        <v>4.6201998392474</v>
+        <f>IF(ISNA(nom_converted!B16),NA(),nom_converted!B16/nom_converted!$K16*100)</f>
+        <v>3.4137881871565945</v>
       </c>
       <c r="C16">
-        <v>6.2472056966167795</v>
+        <f>IF(ISNA(nom_converted!C16),NA(),nom_converted!C16/nom_converted!$K16*100)</f>
+        <v>4.6159555326337829</v>
       </c>
       <c r="D16">
-        <v>6.2472056966167795</v>
+        <f>IF(ISNA(nom_converted!D16),NA(),nom_converted!D16/nom_converted!$K16*100)</f>
+        <v>4.6159555326337829</v>
       </c>
       <c r="E16">
-        <v>6.2472056966167795</v>
+        <f>IF(ISNA(nom_converted!E16),NA(),nom_converted!E16/nom_converted!$K16*100)</f>
+        <v>4.6159555326337829</v>
       </c>
       <c r="F16">
-        <v>7.8369518778631964</v>
+        <f>IF(ISNA(nom_converted!F16),NA(),nom_converted!F16/nom_converted!$K16*100)</f>
+        <v>5.7905923282145455</v>
       </c>
       <c r="G16">
-        <v>7.8369518778631964</v>
+        <f>IF(ISNA(nom_converted!G16),NA(),nom_converted!G16/nom_converted!$K16*100)</f>
+        <v>5.7905923282145455</v>
       </c>
       <c r="H16">
-        <v>7.8369518778631964</v>
+        <f>IF(ISNA(nom_converted!H16),NA(),nom_converted!H16/nom_converted!$K16*100)</f>
+        <v>5.7905923282145455</v>
       </c>
       <c r="I16">
-        <v>7.8369518778631964</v>
+        <f>IF(ISNA(nom_converted!I16),NA(),nom_converted!I16/nom_converted!$K16*100)</f>
+        <v>5.7905923282145455</v>
       </c>
       <c r="J16">
-        <v>7.8369518778631964</v>
+        <f>IF(ISNA(nom_converted!J16),NA(),nom_converted!J16/nom_converted!$K16*100)</f>
+        <v>5.7905923282145455</v>
       </c>
       <c r="K16">
         <v>108.9698539</v>
@@ -3838,31 +4217,40 @@
         <v>2014</v>
       </c>
       <c r="B17">
-        <v>4.7071390835343134</v>
+        <f>IF(ISNA(nom_converted!B17),NA(),nom_converted!B17/nom_converted!$K17*100)</f>
+        <v>3.428277708520437</v>
       </c>
       <c r="C17">
-        <v>6.3714046170266565</v>
+        <f>IF(ISNA(nom_converted!C17),NA(),nom_converted!C17/nom_converted!$K17*100)</f>
+        <v>4.6403864497915146</v>
       </c>
       <c r="D17">
-        <v>6.3714046170266565</v>
+        <f>IF(ISNA(nom_converted!D17),NA(),nom_converted!D17/nom_converted!$K17*100)</f>
+        <v>4.6403864497915146</v>
       </c>
       <c r="E17">
-        <v>6.3714046170266565</v>
+        <f>IF(ISNA(nom_converted!E17),NA(),nom_converted!E17/nom_converted!$K17*100)</f>
+        <v>4.6403864497915146</v>
       </c>
       <c r="F17">
-        <v>8.0729298266419605</v>
+        <f>IF(ISNA(nom_converted!F17),NA(),nom_converted!F17/nom_converted!$K17*100)</f>
+        <v>5.8796319539268715</v>
       </c>
       <c r="G17">
-        <v>8.0729298266419605</v>
+        <f>IF(ISNA(nom_converted!G17),NA(),nom_converted!G17/nom_converted!$K17*100)</f>
+        <v>5.8796319539268715</v>
       </c>
       <c r="H17">
-        <v>8.0729298266419605</v>
+        <f>IF(ISNA(nom_converted!H17),NA(),nom_converted!H17/nom_converted!$K17*100)</f>
+        <v>5.8796319539268715</v>
       </c>
       <c r="I17">
-        <v>8.0729298266419605</v>
+        <f>IF(ISNA(nom_converted!I17),NA(),nom_converted!I17/nom_converted!$K17*100)</f>
+        <v>5.8796319539268715</v>
       </c>
       <c r="J17">
-        <v>8.0729298266419605</v>
+        <f>IF(ISNA(nom_converted!J17),NA(),nom_converted!J17/nom_converted!$K17*100)</f>
+        <v>5.8796319539268715</v>
       </c>
       <c r="K17">
         <v>110.5511374</v>
@@ -3873,31 +4261,40 @@
         <v>2015</v>
       </c>
       <c r="B18">
-        <v>4.8064982198622141</v>
+        <f>IF(ISNA(nom_converted!B18),NA(),nom_converted!B18/nom_converted!$K18*100)</f>
+        <v>3.4878056499953285</v>
       </c>
       <c r="C18">
-        <v>6.5825427817234452</v>
+        <f>IF(ISNA(nom_converted!C18),NA(),nom_converted!C18/nom_converted!$K18*100)</f>
+        <v>4.7765813811305531</v>
       </c>
       <c r="D18">
-        <v>6.5825427817234452</v>
+        <f>IF(ISNA(nom_converted!D18),NA(),nom_converted!D18/nom_converted!$K18*100)</f>
+        <v>4.7765813811305531</v>
       </c>
       <c r="E18">
-        <v>6.5825427817234452</v>
+        <f>IF(ISNA(nom_converted!E18),NA(),nom_converted!E18/nom_converted!$K18*100)</f>
+        <v>4.7765813811305531</v>
       </c>
       <c r="F18">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_converted!F18),NA(),nom_converted!F18/nom_converted!$K18*100)</f>
+        <v>6.0383198591650391</v>
       </c>
       <c r="G18">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_converted!G18),NA(),nom_converted!G18/nom_converted!$K18*100)</f>
+        <v>6.0383198591650391</v>
       </c>
       <c r="H18">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_converted!H18),NA(),nom_converted!H18/nom_converted!$K18*100)</f>
+        <v>6.0383198591650391</v>
       </c>
       <c r="I18">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_converted!I18),NA(),nom_converted!I18/nom_converted!$K18*100)</f>
+        <v>6.0383198591650391</v>
       </c>
       <c r="J18">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_converted!J18),NA(),nom_converted!J18/nom_converted!$K18*100)</f>
+        <v>6.0383198591650391</v>
       </c>
       <c r="K18">
         <v>110.9580174</v>
@@ -3908,31 +4305,40 @@
         <v>2016</v>
       </c>
       <c r="B19">
-        <v>4.8064982198622141</v>
+        <f>IF(ISNA(nom_converted!B19),NA(),nom_converted!B19/nom_converted!$K19*100)</f>
+        <v>3.4529851486225436</v>
       </c>
       <c r="C19">
-        <v>6.5825427817234452</v>
+        <f>IF(ISNA(nom_converted!C19),NA(),nom_converted!C19/nom_converted!$K19*100)</f>
+        <v>4.7288943895864293</v>
       </c>
       <c r="D19">
-        <v>6.5825427817234452</v>
+        <f>IF(ISNA(nom_converted!D19),NA(),nom_converted!D19/nom_converted!$K19*100)</f>
+        <v>4.7288943895864293</v>
       </c>
       <c r="E19">
-        <v>6.5825427817234452</v>
+        <f>IF(ISNA(nom_converted!E19),NA(),nom_converted!E19/nom_converted!$K19*100)</f>
+        <v>4.7288943895864293</v>
       </c>
       <c r="F19">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_converted!F19),NA(),nom_converted!F19/nom_converted!$K19*100)</f>
+        <v>5.9780363038168067</v>
       </c>
       <c r="G19">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_converted!G19),NA(),nom_converted!G19/nom_converted!$K19*100)</f>
+        <v>5.9780363038168067</v>
       </c>
       <c r="H19">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_converted!H19),NA(),nom_converted!H19/nom_converted!$K19*100)</f>
+        <v>5.9780363038168067</v>
       </c>
       <c r="I19">
-        <v>8.3213276674617145</v>
+        <f>IF(ISNA(nom_converted!I19),NA(),nom_converted!I19/nom_converted!$K19*100)</f>
+        <v>5.9780363038168067</v>
       </c>
       <c r="J19">
-        <v>8.9423222695110969</v>
+        <f>IF(ISNA(nom_converted!J19),NA(),nom_converted!J19/nom_converted!$K19*100)</f>
+        <v>6.4241584160419416</v>
       </c>
       <c r="K19">
         <v>112.0769373</v>
@@ -3943,31 +4349,40 @@
         <v>2017</v>
       </c>
       <c r="B20">
-        <v>5.030056276599991</v>
+        <f>IF(ISNA(nom_converted!B20),NA(),nom_converted!B20/nom_converted!$K20*100)</f>
+        <v>3.5234674187786559</v>
       </c>
       <c r="C20">
-        <v>6.9551395429530745</v>
+        <f>IF(ISNA(nom_converted!C20),NA(),nom_converted!C20/nom_converted!$K20*100)</f>
+        <v>4.8719549494223386</v>
       </c>
       <c r="D20">
-        <v>6.9551395429530745</v>
+        <f>IF(ISNA(nom_converted!D20),NA(),nom_converted!D20/nom_converted!$K20*100)</f>
+        <v>4.8719549494223386</v>
       </c>
       <c r="E20">
-        <v>6.9551395429530745</v>
+        <f>IF(ISNA(nom_converted!E20),NA(),nom_converted!E20/nom_converted!$K20*100)</f>
+        <v>4.8719549494223386</v>
       </c>
       <c r="F20">
-        <v>8.75602388889628</v>
+        <f>IF(ISNA(nom_converted!F20),NA(),nom_converted!F20/nom_converted!$K20*100)</f>
+        <v>6.1334432845406228</v>
       </c>
       <c r="G20">
-        <v>8.75602388889628</v>
+        <f>IF(ISNA(nom_converted!G20),NA(),nom_converted!G20/nom_converted!$K20*100)</f>
+        <v>6.1334432845406228</v>
       </c>
       <c r="H20">
-        <v>8.75602388889628</v>
+        <f>IF(ISNA(nom_converted!H20),NA(),nom_converted!H20/nom_converted!$K20*100)</f>
+        <v>6.1334432845406228</v>
       </c>
       <c r="I20">
-        <v>8.75602388889628</v>
+        <f>IF(ISNA(nom_converted!I20),NA(),nom_converted!I20/nom_converted!$K20*100)</f>
+        <v>6.1334432845406228</v>
       </c>
       <c r="J20">
-        <v>9.3149190307407252</v>
+        <f>IF(ISNA(nom_converted!J20),NA(),nom_converted!J20/nom_converted!$K20*100)</f>
+        <v>6.5249396644049176</v>
       </c>
       <c r="K20">
         <v>114.9435916</v>
@@ -3978,31 +4393,40 @@
         <v>2018</v>
       </c>
       <c r="B21">
-        <v>5.2163546572148061</v>
+        <f>IF(ISNA(nom_converted!B21),NA(),nom_converted!B21/nom_converted!$K21*100)</f>
+        <v>3.5720644900318912</v>
       </c>
       <c r="C21">
-        <v>7.3277363041827037</v>
+        <f>IF(ISNA(nom_converted!C21),NA(),nom_converted!C21/nom_converted!$K21*100)</f>
+        <v>5.0179001169495612</v>
       </c>
       <c r="D21">
-        <v>7.3277363041827037</v>
+        <f>IF(ISNA(nom_converted!D21),NA(),nom_converted!D21/nom_converted!$K21*100)</f>
+        <v>5.0179001169495612</v>
       </c>
       <c r="E21">
-        <v>7.3277363041827037</v>
+        <f>IF(ISNA(nom_converted!E21),NA(),nom_converted!E21/nom_converted!$K21*100)</f>
+        <v>5.0179001169495612</v>
       </c>
       <c r="F21">
-        <v>9.1658803262488728</v>
+        <f>IF(ISNA(nom_converted!F21),NA(),nom_converted!F21/nom_converted!$K21*100)</f>
+        <v>6.2766276039131803</v>
       </c>
       <c r="G21">
-        <v>9.1658803262488728</v>
+        <f>IF(ISNA(nom_converted!G21),NA(),nom_converted!G21/nom_converted!$K21*100)</f>
+        <v>6.2766276039131803</v>
       </c>
       <c r="H21">
-        <v>9.1658803262488728</v>
+        <f>IF(ISNA(nom_converted!H21),NA(),nom_converted!H21/nom_converted!$K21*100)</f>
+        <v>6.2766276039131803</v>
       </c>
       <c r="I21">
-        <v>9.1658803262488728</v>
+        <f>IF(ISNA(nom_converted!I21),NA(),nom_converted!I21/nom_converted!$K21*100)</f>
+        <v>6.2766276039131803</v>
       </c>
       <c r="J21">
-        <v>9.7247754680933163</v>
+        <f>IF(ISNA(nom_converted!J21),NA(),nom_converted!J21/nom_converted!$K21*100)</f>
+        <v>6.6593487992737401</v>
       </c>
       <c r="K21">
         <v>117.5790642</v>
@@ -4013,31 +4437,40 @@
         <v>2019</v>
       </c>
       <c r="B22">
-        <v>5.4026530378296194</v>
+        <f>IF(ISNA(nom_converted!B22),NA(),nom_converted!B22/nom_converted!$K22*100)</f>
+        <v>3.6364332096525551</v>
       </c>
       <c r="C22">
-        <v>7.6382336052073949</v>
+        <f>IF(ISNA(nom_converted!C22),NA(),nom_converted!C22/nom_converted!$K22*100)</f>
+        <v>5.1411641929570608</v>
       </c>
       <c r="D22">
-        <v>7.6382336052073949</v>
+        <f>IF(ISNA(nom_converted!D22),NA(),nom_converted!D22/nom_converted!$K22*100)</f>
+        <v>5.1411641929570608</v>
       </c>
       <c r="E22">
-        <v>7.6382336052073949</v>
+        <f>IF(ISNA(nom_converted!E22),NA(),nom_converted!E22/nom_converted!$K22*100)</f>
+        <v>5.1411641929570608</v>
       </c>
       <c r="F22">
-        <v>9.5633168715604775</v>
+        <f>IF(ISNA(nom_converted!F22),NA(),nom_converted!F22/nom_converted!$K22*100)</f>
+        <v>6.4369047619137181</v>
       </c>
       <c r="G22">
-        <v>9.5633168715604775</v>
+        <f>IF(ISNA(nom_converted!G22),NA(),nom_converted!G22/nom_converted!$K22*100)</f>
+        <v>6.4369047619137181</v>
       </c>
       <c r="H22">
-        <v>9.5633168715604775</v>
+        <f>IF(ISNA(nom_converted!H22),NA(),nom_converted!H22/nom_converted!$K22*100)</f>
+        <v>6.4369047619137181</v>
       </c>
       <c r="I22">
-        <v>9.5633168715604775</v>
+        <f>IF(ISNA(nom_converted!I22),NA(),nom_converted!I22/nom_converted!$K22*100)</f>
+        <v>6.4369047619137181</v>
       </c>
       <c r="J22">
-        <v>10.196731365650848</v>
+        <f>IF(ISNA(nom_converted!J22),NA(),nom_converted!J22/nom_converted!$K22*100)</f>
+        <v>6.8632452071833283</v>
       </c>
       <c r="K22">
         <v>119.62271130000001</v>
@@ -4048,31 +4481,40 @@
         <v>2020</v>
       </c>
       <c r="B23">
-        <v>5.6510508786493725</v>
+        <f>IF(ISNA(nom_converted!B23),NA(),nom_converted!B23/nom_converted!$K23*100)</f>
+        <v>3.7663579309123154</v>
       </c>
       <c r="C23">
-        <v>8.0108303664370233</v>
+        <f>IF(ISNA(nom_converted!C23),NA(),nom_converted!C23/nom_converted!$K23*100)</f>
+        <v>5.3391227811833923</v>
       </c>
       <c r="D23">
-        <v>8.0108303664370233</v>
+        <f>IF(ISNA(nom_converted!D23),NA(),nom_converted!D23/nom_converted!$K23*100)</f>
+        <v>5.3391227811833923</v>
       </c>
       <c r="E23">
-        <v>8.0108303664370233</v>
+        <f>IF(ISNA(nom_converted!E23),NA(),nom_converted!E23/nom_converted!$K23*100)</f>
+        <v>5.3391227811833923</v>
       </c>
       <c r="F23">
-        <v>10.184311473609858</v>
+        <f>IF(ISNA(nom_converted!F23),NA(),nom_converted!F23/nom_converted!$K23*100)</f>
+        <v>6.7877219853804363</v>
       </c>
       <c r="G23">
-        <v>10.184311473609858</v>
+        <f>IF(ISNA(nom_converted!G23),NA(),nom_converted!G23/nom_converted!$K23*100)</f>
+        <v>6.7877219853804363</v>
       </c>
       <c r="H23">
-        <v>10.184311473609858</v>
+        <f>IF(ISNA(nom_converted!H23),NA(),nom_converted!H23/nom_converted!$K23*100)</f>
+        <v>6.7877219853804363</v>
       </c>
       <c r="I23">
-        <v>10.184311473609858</v>
+        <f>IF(ISNA(nom_converted!I23),NA(),nom_converted!I23/nom_converted!$K23*100)</f>
+        <v>6.7877219853804363</v>
       </c>
       <c r="J23">
-        <v>10.830145859741217</v>
+        <f>IF(ISNA(nom_converted!J23),NA(),nom_converted!J23/nom_converted!$K23*100)</f>
+        <v>7.2181628917704161</v>
       </c>
       <c r="K23">
         <v>120.8063621</v>
@@ -4083,31 +4525,40 @@
         <v>2021</v>
       </c>
       <c r="B24">
-        <v>5.7379901229362869</v>
+        <f>IF(ISNA(nom_converted!B24),NA(),nom_converted!B24/nom_converted!$K24*100)</f>
+        <v>3.7303576503974472</v>
       </c>
       <c r="C24">
-        <v>8.1474491788878858</v>
+        <f>IF(ISNA(nom_converted!C24),NA(),nom_converted!C24/nom_converted!$K24*100)</f>
+        <v>5.2967848888760285</v>
       </c>
       <c r="D24">
-        <v>8.1474491788878858</v>
+        <f>IF(ISNA(nom_converted!D24),NA(),nom_converted!D24/nom_converted!$K24*100)</f>
+        <v>5.2967848888760285</v>
       </c>
       <c r="E24">
-        <v>8.1474491788878858</v>
+        <f>IF(ISNA(nom_converted!E24),NA(),nom_converted!E24/nom_converted!$K24*100)</f>
+        <v>5.2967848888760285</v>
       </c>
       <c r="F24">
-        <v>10.383029746265661</v>
+        <f>IF(ISNA(nom_converted!F24),NA(),nom_converted!F24/nom_converted!$K24*100)</f>
+        <v>6.7501709864334751</v>
       </c>
       <c r="G24">
-        <v>10.383029746265661</v>
+        <f>IF(ISNA(nom_converted!G24),NA(),nom_converted!G24/nom_converted!$K24*100)</f>
+        <v>6.7501709864334751</v>
       </c>
       <c r="H24">
-        <v>11.066123808519981</v>
+        <f>IF(ISNA(nom_converted!H24),NA(),nom_converted!H24/nom_converted!$K24*100)</f>
+        <v>7.1942611829093632</v>
       </c>
       <c r="I24">
-        <v>11.066123808519981</v>
+        <f>IF(ISNA(nom_converted!I24),NA(),nom_converted!I24/nom_converted!$K24*100)</f>
+        <v>7.1942611829093632</v>
       </c>
       <c r="J24">
-        <v>11.066123808519981</v>
+        <f>IF(ISNA(nom_converted!J24),NA(),nom_converted!J24/nom_converted!$K24*100)</f>
+        <v>7.1942611829093632</v>
       </c>
       <c r="K24">
         <v>123.84871459999999</v>
@@ -4118,31 +4569,40 @@
         <v>2022</v>
       </c>
       <c r="B25">
-        <v>5.973968071715051</v>
+        <f>IF(ISNA(nom_converted!B25),NA(),nom_converted!B25/nom_converted!$K25*100)</f>
+        <v>3.5986813333286114</v>
       </c>
       <c r="C25">
-        <v>8.4827862639945533</v>
+        <f>IF(ISNA(nom_converted!C25),NA(),nom_converted!C25/nom_converted!$K25*100)</f>
+        <v>5.1099778600071559</v>
       </c>
       <c r="D25">
-        <v>8.4827862639945533</v>
+        <f>IF(ISNA(nom_converted!D25),NA(),nom_converted!D25/nom_converted!$K25*100)</f>
+        <v>5.1099778600071559</v>
       </c>
       <c r="E25">
-        <v>8.4827862639945533</v>
+        <f>IF(ISNA(nom_converted!E25),NA(),nom_converted!E25/nom_converted!$K25*100)</f>
+        <v>5.1099778600071559</v>
       </c>
       <c r="F25">
-        <v>11.401460893626647</v>
+        <f>IF(ISNA(nom_converted!F25),NA(),nom_converted!F25/nom_converted!$K25*100)</f>
+        <v>6.8681693638163521</v>
       </c>
       <c r="G25">
-        <v>11.401460893626647</v>
+        <f>IF(ISNA(nom_converted!G25),NA(),nom_converted!G25/nom_converted!$K25*100)</f>
+        <v>6.8681693638163521</v>
       </c>
       <c r="H25">
-        <v>11.798897438938251</v>
+        <f>IF(ISNA(nom_converted!H25),NA(),nom_converted!H25/nom_converted!$K25*100)</f>
+        <v>7.1075826749733491</v>
       </c>
       <c r="I25">
-        <v>11.798897438938251</v>
+        <f>IF(ISNA(nom_converted!I25),NA(),nom_converted!I25/nom_converted!$K25*100)</f>
+        <v>7.1075826749733491</v>
       </c>
       <c r="J25">
-        <v>11.798897438938251</v>
+        <f>IF(ISNA(nom_converted!J25),NA(),nom_converted!J25/nom_converted!$K25*100)</f>
+        <v>7.1075826749733491</v>
       </c>
       <c r="K25">
         <v>133.6600703</v>
@@ -4153,31 +4613,40 @@
         <v>2023</v>
       </c>
       <c r="B26">
-        <v>6.5577029976414707</v>
+        <f>IF(ISNA(nom_converted!B26),NA(),nom_converted!B26/nom_converted!$K26*100)</f>
+        <v>3.6990101072046406</v>
       </c>
       <c r="C26">
-        <v>9.3024991386997371</v>
+        <f>IF(ISNA(nom_converted!C26),NA(),nom_converted!C26/nom_converted!$K26*100)</f>
+        <v>5.2472700195005224</v>
       </c>
       <c r="D26">
-        <v>9.3024991386997371</v>
+        <f>IF(ISNA(nom_converted!D26),NA(),nom_converted!D26/nom_converted!$K26*100)</f>
+        <v>5.2472700195005224</v>
       </c>
       <c r="E26">
-        <v>9.3024991386997371</v>
+        <f>IF(ISNA(nom_converted!E26),NA(),nom_converted!E26/nom_converted!$K26*100)</f>
+        <v>5.2472700195005224</v>
       </c>
       <c r="F26">
-        <v>12.64345009772541</v>
+        <f>IF(ISNA(nom_converted!F26),NA(),nom_converted!F26/nom_converted!$K26*100)</f>
+        <v>7.1318035779059166</v>
       </c>
       <c r="G26">
-        <v>12.64345009772541</v>
+        <f>IF(ISNA(nom_converted!G26),NA(),nom_converted!G26/nom_converted!$K26*100)</f>
+        <v>7.1318035779059166</v>
       </c>
       <c r="H26">
-        <v>12.941527506709113</v>
+        <f>IF(ISNA(nom_converted!H26),NA(),nom_converted!H26/nom_converted!$K26*100)</f>
+        <v>7.2999404009606739</v>
       </c>
       <c r="I26">
-        <v>12.941527506709113</v>
+        <f>IF(ISNA(nom_converted!I26),NA(),nom_converted!I26/nom_converted!$K26*100)</f>
+        <v>7.2999404009606739</v>
       </c>
       <c r="J26">
-        <v>12.941527506709113</v>
+        <f>IF(ISNA(nom_converted!J26),NA(),nom_converted!J26/nom_converted!$K26*100)</f>
+        <v>7.2999404009606739</v>
       </c>
       <c r="K26">
         <v>142.74089140000001</v>
@@ -4188,31 +4657,40 @@
         <v>2024</v>
       </c>
       <c r="B27">
-        <v>7.9487309062320852</v>
+        <f>IF(ISNA(nom_converted!B27),NA(),nom_converted!B27/nom_converted!$K27*100)</f>
+        <v>4.3416096864427214</v>
       </c>
       <c r="C27">
-        <v>10.681107155249364</v>
+        <f>IF(ISNA(nom_converted!C27),NA(),nom_converted!C27/nom_converted!$K27*100)</f>
+        <v>5.8340380161574057</v>
       </c>
       <c r="D27">
-        <v>10.681107155249364</v>
+        <f>IF(ISNA(nom_converted!D27),NA(),nom_converted!D27/nom_converted!$K27*100)</f>
+        <v>5.8340380161574057</v>
       </c>
       <c r="E27">
-        <v>10.681107155249364</v>
+        <f>IF(ISNA(nom_converted!E27),NA(),nom_converted!E27/nom_converted!$K27*100)</f>
+        <v>5.8340380161574057</v>
       </c>
       <c r="F27">
-        <v>14.208356494889852</v>
+        <f>IF(ISNA(nom_converted!F27),NA(),nom_converted!F27/nom_converted!$K27*100)</f>
+        <v>7.7606273145163618</v>
       </c>
       <c r="G27">
-        <v>14.208356494889852</v>
+        <f>IF(ISNA(nom_converted!G27),NA(),nom_converted!G27/nom_converted!$K27*100)</f>
+        <v>7.7606273145163618</v>
       </c>
       <c r="H27">
-        <v>14.208356494889852</v>
+        <f>IF(ISNA(nom_converted!H27),NA(),nom_converted!H27/nom_converted!$K27*100)</f>
+        <v>7.7606273145163618</v>
       </c>
       <c r="I27">
-        <v>14.208356494889852</v>
+        <f>IF(ISNA(nom_converted!I27),NA(),nom_converted!I27/nom_converted!$K27*100)</f>
+        <v>7.7606273145163618</v>
       </c>
       <c r="J27">
-        <v>14.208356494889852</v>
+        <f>IF(ISNA(nom_converted!J27),NA(),nom_converted!J27/nom_converted!$K27*100)</f>
+        <v>7.7606273145163618</v>
       </c>
       <c r="K27">
         <v>147.41076380000001</v>

--- a/Data/External data/mw_cpi.xlsx
+++ b/Data/External data/mw_cpi.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tp01040\Downloads\msc-dissertation-roe\Data\External data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F7083D-6E9E-454E-BDF7-DE0EBDBC96F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52269530-FDEC-4A21-8136-E2F852668556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{CBF8D809-2CCE-4683-B951-0D73F9F5ACB4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{CBF8D809-2CCE-4683-B951-0D73F9F5ACB4}"/>
   </bookViews>
   <sheets>
     <sheet name="nom_unconverted" sheetId="1" r:id="rId1"/>
     <sheet name="nom_converted" sheetId="2" r:id="rId2"/>
     <sheet name="real_unconverted" sheetId="3" r:id="rId3"/>
     <sheet name="real_converted" sheetId="4" r:id="rId4"/>
+    <sheet name="kaitz_index" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
   <si>
     <t>Under 18</t>
   </si>
@@ -82,12 +83,32 @@
   <si>
     <t>year</t>
   </si>
+  <si>
+    <t>median wage</t>
+  </si>
+  <si>
+    <t>minimum wage</t>
+  </si>
+  <si>
+    <t>kaitz</t>
+  </si>
+  <si>
+    <t>Kaitz</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="6">
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,6 +123,15 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -121,10 +151,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -144,9 +183,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="10">
+    <cellStyle name="Comma [0] 2" xfId="6" xr:uid="{203A52B5-AA4A-4E99-BCC8-BBE9F343FE5F}"/>
+    <cellStyle name="Comma 2" xfId="5" xr:uid="{2FD4F20A-E039-493F-912C-5855B5228F8E}"/>
+    <cellStyle name="Comma 3" xfId="9" xr:uid="{B5E717AD-8E7D-43B2-A3F2-5160B304313F}"/>
+    <cellStyle name="Currency [0] 2" xfId="4" xr:uid="{EBA49003-1846-42E7-BF79-5F311F6FFA84}"/>
+    <cellStyle name="Currency 2" xfId="3" xr:uid="{EFE0950E-59A6-43F1-9D04-CF4DEFE00C14}"/>
+    <cellStyle name="Currency 3" xfId="8" xr:uid="{6A41CB48-B3D9-4223-92E8-0C17E62B6AF7}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{56B6938B-1A63-4EF3-8C8B-7AE8419132AE}"/>
+    <cellStyle name="Normal 3" xfId="7" xr:uid="{40750C2C-DFF4-411E-8A5C-2C93798A5899}"/>
+    <cellStyle name="Percent 2" xfId="2" xr:uid="{15ADF33D-38C3-4A7A-9B52-3552B154BAC6}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -478,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AC5F7C-59DE-4BAE-AB15-0CFBE2C16D43}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.44140625" customWidth="1"/>
@@ -552,8 +615,8 @@
       <c r="J2" s="3">
         <v>3.6</v>
       </c>
-      <c r="K2">
-        <v>80.515997780000006</v>
+      <c r="K2" s="7">
+        <v>72.599999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -587,8 +650,8 @@
       <c r="J3" s="3">
         <v>3.7</v>
       </c>
-      <c r="K3">
-        <v>81.468466800000002</v>
+      <c r="K3" s="7">
+        <v>73.400000000000006</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -622,8 +685,8 @@
       <c r="J4" s="3">
         <v>4.0999999999999996</v>
       </c>
-      <c r="K4">
-        <v>82.716848529999993</v>
+      <c r="K4" s="7">
+        <v>74.599999999999994</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -657,8 +720,8 @@
       <c r="J5" s="3">
         <v>4.2</v>
       </c>
-      <c r="K5">
-        <v>83.974477530000001</v>
+      <c r="K5" s="7">
+        <v>75.7</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -692,8 +755,8 @@
       <c r="J6" s="3">
         <v>4.5</v>
       </c>
-      <c r="K6">
-        <v>85.130386540000003</v>
+      <c r="K6" s="7">
+        <v>76.7</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -727,8 +790,8 @@
       <c r="J7" s="3">
         <v>4.8499999999999996</v>
       </c>
-      <c r="K7">
-        <v>86.31403736</v>
+      <c r="K7" s="7">
+        <v>77.8</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -762,8 +825,8 @@
       <c r="J8" s="3">
         <v>5.05</v>
       </c>
-      <c r="K8">
-        <v>88.117255409999999</v>
+      <c r="K8" s="7">
+        <v>79.400000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -797,8 +860,8 @@
       <c r="J9" s="3">
         <v>5.35</v>
       </c>
-      <c r="K9">
-        <v>90.281117069999993</v>
+      <c r="K9" s="7">
+        <v>81.400000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -832,8 +895,8 @@
       <c r="J10" s="3">
         <v>5.52</v>
       </c>
-      <c r="K10">
-        <v>92.43573146</v>
+      <c r="K10" s="7">
+        <v>83.3</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -867,8 +930,8 @@
       <c r="J11" s="3">
         <v>5.73</v>
       </c>
-      <c r="K11">
-        <v>95.690771220000002</v>
+      <c r="K11" s="7">
+        <v>86.2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -902,8 +965,8 @@
       <c r="J12" s="3">
         <v>5.8</v>
       </c>
-      <c r="K12">
-        <v>97.567967449999998</v>
+      <c r="K12" s="7">
+        <v>87.9</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -937,8 +1000,8 @@
       <c r="J13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K13">
-        <v>100</v>
+      <c r="K13" s="7">
+        <v>90.1</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -972,8 +1035,8 @@
       <c r="J14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K14">
-        <v>103.8561124</v>
+      <c r="K14" s="7">
+        <v>93.6</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1007,8 +1070,8 @@
       <c r="J15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K15">
-        <v>106.5285741</v>
+      <c r="K15" s="7">
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1042,8 +1105,8 @@
       <c r="J16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K16">
-        <v>108.9698539</v>
+      <c r="K16" s="7">
+        <v>98.2</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1077,8 +1140,8 @@
       <c r="J17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K17">
-        <v>110.5511374</v>
+      <c r="K17" s="7">
+        <v>99.6</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1112,8 +1175,8 @@
       <c r="J18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K18">
-        <v>110.9580174</v>
+      <c r="K18" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -1147,8 +1210,8 @@
       <c r="J19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K19">
-        <v>112.0769373</v>
+      <c r="K19" s="7">
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -1182,8 +1245,8 @@
       <c r="J20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K20">
-        <v>114.9435916</v>
+      <c r="K20" s="7">
+        <v>103.6</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -1217,8 +1280,8 @@
       <c r="J21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K21">
-        <v>117.5790642</v>
+      <c r="K21" s="7">
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -1252,8 +1315,8 @@
       <c r="J22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K22">
-        <v>119.62271130000001</v>
+      <c r="K22" s="7">
+        <v>107.8</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -1287,8 +1350,8 @@
       <c r="J23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K23">
-        <v>120.8063621</v>
+      <c r="K23" s="7">
+        <v>108.9</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -1322,8 +1385,8 @@
       <c r="J24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K24">
-        <v>123.84871459999999</v>
+      <c r="K24" s="7">
+        <v>111.6</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -1357,8 +1420,8 @@
       <c r="J25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K25">
-        <v>133.6600703</v>
+      <c r="K25" s="7">
+        <v>120.5</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -1392,8 +1455,8 @@
       <c r="J26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K26">
-        <v>142.74089140000001</v>
+      <c r="K26" s="7">
+        <v>128.6</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -1427,8 +1490,43 @@
       <c r="J27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="K27">
-        <v>147.41076380000001</v>
+      <c r="K27" s="7">
+        <v>132.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B28" s="8">
+        <v>7.55</v>
+      </c>
+      <c r="C28" s="9">
+        <v>10</v>
+      </c>
+      <c r="D28" s="8">
+        <v>12.21</v>
+      </c>
+      <c r="E28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K28" s="7">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1438,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0582E92B-9DD8-47E6-A407-8E79DB563530}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="10" max="10" width="8.88671875" customWidth="1"/>
@@ -1510,8 +1608,8 @@
       <c r="J2" s="5">
         <v>3.6</v>
       </c>
-      <c r="K2">
-        <v>80.515997780000006</v>
+      <c r="K2" s="7">
+        <v>72.599999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1545,8 +1643,8 @@
       <c r="J3" s="5">
         <v>3.7</v>
       </c>
-      <c r="K3">
-        <v>81.468466800000002</v>
+      <c r="K3" s="7">
+        <v>73.400000000000006</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -1580,8 +1678,8 @@
       <c r="J4" s="5">
         <v>4.0999999999999996</v>
       </c>
-      <c r="K4">
-        <v>82.716848529999993</v>
+      <c r="K4" s="7">
+        <v>74.599999999999994</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -1615,8 +1713,8 @@
       <c r="J5" s="5">
         <v>4.2</v>
       </c>
-      <c r="K5">
-        <v>83.974477530000001</v>
+      <c r="K5" s="7">
+        <v>75.7</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -1650,8 +1748,8 @@
       <c r="J6" s="5">
         <v>4.5</v>
       </c>
-      <c r="K6">
-        <v>85.130386540000003</v>
+      <c r="K6" s="7">
+        <v>76.7</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1685,8 +1783,8 @@
       <c r="J7" s="5">
         <v>4.8499999999999996</v>
       </c>
-      <c r="K7">
-        <v>86.31403736</v>
+      <c r="K7" s="7">
+        <v>77.8</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1720,8 +1818,8 @@
       <c r="J8" s="5">
         <v>5.05</v>
       </c>
-      <c r="K8">
-        <v>88.117255409999999</v>
+      <c r="K8" s="7">
+        <v>79.400000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1755,8 +1853,8 @@
       <c r="J9" s="5">
         <v>5.35</v>
       </c>
-      <c r="K9">
-        <v>90.281117069999993</v>
+      <c r="K9" s="7">
+        <v>81.400000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1790,8 +1888,8 @@
       <c r="J10" s="5">
         <v>5.52</v>
       </c>
-      <c r="K10">
-        <v>92.43573146</v>
+      <c r="K10" s="7">
+        <v>83.3</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1825,8 +1923,8 @@
       <c r="J11" s="5">
         <v>5.73</v>
       </c>
-      <c r="K11">
-        <v>95.690771220000002</v>
+      <c r="K11" s="7">
+        <v>86.2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -1860,8 +1958,8 @@
       <c r="J12" s="5">
         <v>5.8</v>
       </c>
-      <c r="K12">
-        <v>97.567967449999998</v>
+      <c r="K12" s="7">
+        <v>87.9</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1895,8 +1993,8 @@
       <c r="J13" s="5">
         <v>5.93</v>
       </c>
-      <c r="K13">
-        <v>100</v>
+      <c r="K13" s="7">
+        <v>90.1</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1930,8 +2028,8 @@
       <c r="J14" s="5">
         <v>6.08</v>
       </c>
-      <c r="K14">
-        <v>103.8561124</v>
+      <c r="K14" s="7">
+        <v>93.6</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1965,8 +2063,8 @@
       <c r="J15" s="5">
         <v>6.19</v>
       </c>
-      <c r="K15">
-        <v>106.5285741</v>
+      <c r="K15" s="7">
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2000,8 +2098,8 @@
       <c r="J16" s="5">
         <v>6.31</v>
       </c>
-      <c r="K16">
-        <v>108.9698539</v>
+      <c r="K16" s="7">
+        <v>98.2</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -2035,8 +2133,8 @@
       <c r="J17" s="5">
         <v>6.5</v>
       </c>
-      <c r="K17">
-        <v>110.5511374</v>
+      <c r="K17" s="7">
+        <v>99.6</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -2070,8 +2168,8 @@
       <c r="J18" s="5">
         <v>6.7</v>
       </c>
-      <c r="K18">
-        <v>110.9580174</v>
+      <c r="K18" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -2105,8 +2203,8 @@
       <c r="J19" s="5">
         <v>7.2</v>
       </c>
-      <c r="K19">
-        <v>112.0769373</v>
+      <c r="K19" s="7">
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -2140,8 +2238,8 @@
       <c r="J20" s="5">
         <v>7.5</v>
       </c>
-      <c r="K20">
-        <v>114.9435916</v>
+      <c r="K20" s="7">
+        <v>103.6</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -2175,8 +2273,8 @@
       <c r="J21" s="5">
         <v>7.83</v>
       </c>
-      <c r="K21">
-        <v>117.5790642</v>
+      <c r="K21" s="7">
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -2210,8 +2308,8 @@
       <c r="J22" s="5">
         <v>8.2100000000000009</v>
       </c>
-      <c r="K22">
-        <v>119.62271130000001</v>
+      <c r="K22" s="7">
+        <v>107.8</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -2245,8 +2343,8 @@
       <c r="J23" s="5">
         <v>8.7200000000000006</v>
       </c>
-      <c r="K23">
-        <v>120.8063621</v>
+      <c r="K23" s="7">
+        <v>108.9</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -2280,8 +2378,8 @@
       <c r="J24" s="5">
         <v>8.91</v>
       </c>
-      <c r="K24">
-        <v>123.84871459999999</v>
+      <c r="K24" s="7">
+        <v>111.6</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -2315,8 +2413,8 @@
       <c r="J25" s="5">
         <v>9.5</v>
       </c>
-      <c r="K25">
-        <v>133.6600703</v>
+      <c r="K25" s="7">
+        <v>120.5</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -2350,8 +2448,8 @@
       <c r="J26" s="5">
         <v>10.42</v>
       </c>
-      <c r="K26">
-        <v>142.74089140000001</v>
+      <c r="K26" s="7">
+        <v>128.6</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -2385,8 +2483,43 @@
       <c r="J27" s="5">
         <v>11.44</v>
       </c>
-      <c r="K27">
-        <v>147.41076380000001</v>
+      <c r="K27" s="7">
+        <v>132.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B28" s="8">
+        <v>7.55</v>
+      </c>
+      <c r="C28" s="5">
+        <v>10</v>
+      </c>
+      <c r="D28" s="5">
+        <v>10</v>
+      </c>
+      <c r="E28" s="5">
+        <v>10</v>
+      </c>
+      <c r="F28" s="8">
+        <v>12.21</v>
+      </c>
+      <c r="G28" s="8">
+        <v>12.21</v>
+      </c>
+      <c r="H28" s="8">
+        <v>12.21</v>
+      </c>
+      <c r="I28" s="8">
+        <v>12.21</v>
+      </c>
+      <c r="J28" s="8">
+        <v>12.21</v>
+      </c>
+      <c r="K28" s="7">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2396,7 +2529,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BD27AA-F26B-430C-8B96-5327E2504D7E}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="11.44140625" customWidth="1"/>
@@ -2406,7 +2539,7 @@
     <col min="10" max="10" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -2437,8 +2570,11 @@
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1999</v>
       </c>
@@ -2472,14 +2608,18 @@
       </c>
       <c r="I2">
         <f>IF(ISNA(nom_unconverted!I2),NA(),nom_unconverted!I2/nom_unconverted!$K2*100)</f>
-        <v>3.7259676122962895</v>
+        <v>4.1322314049586781</v>
       </c>
       <c r="J2">
-        <f>nom_unconverted!J2/nom_unconverted!$K2*100</f>
-        <v>4.4711611347555484</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J2),NA(),nom_unconverted!J2/nom_unconverted!$K2*100)</f>
+        <v>4.9586776859504145</v>
+      </c>
+      <c r="K2">
+        <f>kaitz_index!D2</f>
+        <v>0.43269230769230771</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2000</v>
       </c>
@@ -2513,14 +2653,18 @@
       </c>
       <c r="I3">
         <f>IF(ISNA(nom_unconverted!I3),NA(),nom_unconverted!I3/nom_unconverted!$K3*100)</f>
-        <v>3.9279001136179477</v>
+        <v>4.3596730245231603</v>
       </c>
       <c r="J3">
-        <f>nom_unconverted!J3/nom_unconverted!$K3*100</f>
-        <v>4.5416345063707526</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J3),NA(),nom_unconverted!J3/nom_unconverted!$K3*100)</f>
+        <v>5.0408719346049047</v>
+      </c>
+      <c r="K3">
+        <f>kaitz_index!D3</f>
+        <v>0.4277456647398844</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2001</v>
       </c>
@@ -2554,14 +2698,18 @@
       </c>
       <c r="I4">
         <f>IF(ISNA(nom_unconverted!I4),NA(),nom_unconverted!I4/nom_unconverted!$K4*100)</f>
-        <v>4.2313024035612399</v>
+        <v>4.6916890080428955</v>
       </c>
       <c r="J4">
-        <f>nom_unconverted!J4/nom_unconverted!$K4*100</f>
-        <v>4.9566685298860236</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J4),NA(),nom_unconverted!J4/nom_unconverted!$K4*100)</f>
+        <v>5.4959785522788209</v>
+      </c>
+      <c r="K4">
+        <f>kaitz_index!D4</f>
+        <v>0.45555555555555549</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>2002</v>
       </c>
@@ -2595,14 +2743,18 @@
       </c>
       <c r="I5">
         <f>IF(ISNA(nom_unconverted!I5),NA(),nom_unconverted!I5/nom_unconverted!$K5*100)</f>
-        <v>4.1679330469780185</v>
+        <v>4.6235138705416112</v>
       </c>
       <c r="J5">
-        <f>nom_unconverted!J5/nom_unconverted!$K5*100</f>
-        <v>5.0015196563736213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J5),NA(),nom_unconverted!J5/nom_unconverted!$K5*100)</f>
+        <v>5.5482166446499335</v>
+      </c>
+      <c r="K5">
+        <f>kaitz_index!D5</f>
+        <v>0.44871794871794879</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>2003</v>
       </c>
@@ -2636,20 +2788,24 @@
       </c>
       <c r="I6">
         <f>IF(ISNA(nom_unconverted!I6),NA(),nom_unconverted!I6/nom_unconverted!$K6*100)</f>
-        <v>4.463741038241972</v>
+        <v>4.9543676662320726</v>
       </c>
       <c r="J6">
-        <f>nom_unconverted!J6/nom_unconverted!$K6*100</f>
-        <v>5.2860091242339138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J6),NA(),nom_unconverted!J6/nom_unconverted!$K6*100)</f>
+        <v>5.867014341590612</v>
+      </c>
+      <c r="K6">
+        <f>kaitz_index!D6</f>
+        <v>0.46343975283213179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>2004</v>
       </c>
       <c r="B7">
         <f>IF(ISNA(nom_unconverted!B7),NA(),nom_unconverted!B7/nom_unconverted!$K7*100)</f>
-        <v>3.4756803085082799</v>
+        <v>3.8560411311053984</v>
       </c>
       <c r="C7" t="e">
         <f>IF(ISNA(nom_unconverted!C7),NA(),nom_unconverted!C7/nom_unconverted!$K7*100)</f>
@@ -2677,20 +2833,24 @@
       </c>
       <c r="I7">
         <f>IF(ISNA(nom_unconverted!I7),NA(),nom_unconverted!I7/nom_unconverted!$K7*100)</f>
-        <v>4.7500964216279824</v>
+        <v>5.2699228791773782</v>
       </c>
       <c r="J7">
-        <f>nom_unconverted!J7/nom_unconverted!$K7*100</f>
-        <v>5.6190164987550517</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J7),NA(),nom_unconverted!J7/nom_unconverted!$K7*100)</f>
+        <v>6.2339331619537273</v>
+      </c>
+      <c r="K7">
+        <f>kaitz_index!D7</f>
+        <v>0.48067393458870167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>2005</v>
       </c>
       <c r="B8">
         <f>IF(ISNA(nom_unconverted!B8),NA(),nom_unconverted!B8/nom_unconverted!$K8*100)</f>
-        <v>3.4045545177744434</v>
+        <v>3.7783375314861458</v>
       </c>
       <c r="C8" t="e">
         <f>IF(ISNA(nom_unconverted!C8),NA(),nom_unconverted!C8/nom_unconverted!$K8*100)</f>
@@ -2718,20 +2878,24 @@
       </c>
       <c r="I8">
         <f>IF(ISNA(nom_unconverted!I8),NA(),nom_unconverted!I8/nom_unconverted!$K8*100)</f>
-        <v>4.8231189001804609</v>
+        <v>5.3526448362720398</v>
       </c>
       <c r="J8">
-        <f>nom_unconverted!J8/nom_unconverted!$K8*100</f>
-        <v>5.7310001049203123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J8),NA(),nom_unconverted!J8/nom_unconverted!$K8*100)</f>
+        <v>6.3602015113350117</v>
+      </c>
+      <c r="K8">
+        <f>kaitz_index!D8</f>
+        <v>0.48698167791706848</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>2006</v>
       </c>
       <c r="B9">
         <f>IF(ISNA(nom_unconverted!B9),NA(),nom_unconverted!B9/nom_unconverted!$K9*100)</f>
-        <v>3.655249411060483</v>
+        <v>4.0540540540540535</v>
       </c>
       <c r="C9" t="e">
         <f>IF(ISNA(nom_unconverted!C9),NA(),nom_unconverted!C9/nom_unconverted!$K9*100)</f>
@@ -2759,20 +2923,24 @@
       </c>
       <c r="I9">
         <f>IF(ISNA(nom_unconverted!I9),NA(),nom_unconverted!I9/nom_unconverted!$K9*100)</f>
-        <v>4.9290484482482269</v>
+        <v>5.4668304668304666</v>
       </c>
       <c r="J9">
-        <f>nom_unconverted!J9/nom_unconverted!$K9*100</f>
-        <v>5.925934651264722</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J9),NA(),nom_unconverted!J9/nom_unconverted!$K9*100)</f>
+        <v>6.5724815724815713</v>
+      </c>
+      <c r="K9">
+        <f>kaitz_index!D9</f>
+        <v>0.49906716417910441</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>2007</v>
       </c>
       <c r="B10">
         <f>IF(ISNA(nom_unconverted!B10),NA(),nom_unconverted!B10/nom_unconverted!$K10*100)</f>
-        <v>3.6782312924859499</v>
+        <v>4.0816326530612246</v>
       </c>
       <c r="C10" t="e">
         <f>IF(ISNA(nom_unconverted!C10),NA(),nom_unconverted!C10/nom_unconverted!$K10*100)</f>
@@ -2800,20 +2968,24 @@
       </c>
       <c r="I10">
         <f>IF(ISNA(nom_unconverted!I10),NA(),nom_unconverted!I10/nom_unconverted!$K10*100)</f>
-        <v>4.9764305721868736</v>
+        <v>5.5222088835534215</v>
       </c>
       <c r="J10">
-        <f>nom_unconverted!J10/nom_unconverted!$K10*100</f>
-        <v>5.9717166866242479</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J10),NA(),nom_unconverted!J10/nom_unconverted!$K10*100)</f>
+        <v>6.6266506602641053</v>
+      </c>
+      <c r="K10">
+        <f>kaitz_index!D10</f>
+        <v>0.49954751131221714</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>2008</v>
       </c>
       <c r="B11">
         <f>IF(ISNA(nom_unconverted!B11),NA(),nom_unconverted!B11/nom_unconverted!$K11*100)</f>
-        <v>3.6889659838609457</v>
+        <v>4.0951276102088165</v>
       </c>
       <c r="C11" t="e">
         <f>IF(ISNA(nom_unconverted!C11),NA(),nom_unconverted!C11/nom_unconverted!$K11*100)</f>
@@ -2841,20 +3013,24 @@
       </c>
       <c r="I11">
         <f>IF(ISNA(nom_unconverted!I11),NA(),nom_unconverted!I11/nom_unconverted!$K11*100)</f>
-        <v>4.984806726067057</v>
+        <v>5.5336426914153121</v>
       </c>
       <c r="J11">
-        <f>nom_unconverted!J11/nom_unconverted!$K11*100</f>
-        <v>5.9880382684201763</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J11),NA(),nom_unconverted!J11/nom_unconverted!$K11*100)</f>
+        <v>6.6473317865429236</v>
+      </c>
+      <c r="K11">
+        <f>kaitz_index!D11</f>
+        <v>0.50395778364116106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>2009</v>
       </c>
       <c r="B12">
         <f>IF(ISNA(nom_unconverted!B12),NA(),nom_unconverted!B12/nom_unconverted!$K12*100)</f>
-        <v>3.6589877736558298</v>
+        <v>4.0614334470989757</v>
       </c>
       <c r="C12" t="e">
         <f>IF(ISNA(nom_unconverted!C12),NA(),nom_unconverted!C12/nom_unconverted!$K12*100)</f>
@@ -2882,28 +3058,32 @@
       </c>
       <c r="I12">
         <f>IF(ISNA(nom_unconverted!I12),NA(),nom_unconverted!I12/nom_unconverted!$K12*100)</f>
-        <v>4.9503952231814177</v>
+        <v>5.4948805460750849</v>
       </c>
       <c r="J12">
-        <f>nom_unconverted!J12/nom_unconverted!$K12*100</f>
-        <v>5.944573974006671</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J12),NA(),nom_unconverted!J12/nom_unconverted!$K12*100)</f>
+        <v>6.5984072810011369</v>
+      </c>
+      <c r="K12">
+        <f>kaitz_index!D12</f>
+        <v>0.50129645635263609</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>2010</v>
       </c>
       <c r="B13">
         <f>IF(ISNA(nom_unconverted!B13),NA(),nom_unconverted!B13/nom_unconverted!$K13*100)</f>
-        <v>3.64</v>
+        <v>4.0399556048834633</v>
       </c>
       <c r="C13">
         <f>IF(ISNA(nom_unconverted!C13),NA(),nom_unconverted!C13/nom_unconverted!$K13*100)</f>
-        <v>4.92</v>
+        <v>5.4605993340732528</v>
       </c>
       <c r="D13">
         <f>IF(ISNA(nom_unconverted!D13),NA(),nom_unconverted!D13/nom_unconverted!$K13*100)</f>
-        <v>5.93</v>
+        <v>6.5815760266370704</v>
       </c>
       <c r="E13" t="e">
         <f>IF(ISNA(nom_unconverted!E13),NA(),nom_unconverted!E13/nom_unconverted!$K13*100)</f>
@@ -2926,25 +3106,29 @@
         <v>#N/A</v>
       </c>
       <c r="J13" t="e">
-        <f>nom_unconverted!J13/nom_unconverted!$K13*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J13),NA(),nom_unconverted!J13/nom_unconverted!$K13*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K13">
+        <f>kaitz_index!D13</f>
+        <v>0.50042194092827008</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>2011</v>
       </c>
       <c r="B14">
         <f>IF(ISNA(nom_unconverted!B14),NA(),nom_unconverted!B14/nom_unconverted!$K14*100)</f>
-        <v>3.5433639050791199</v>
+        <v>3.9316239316239323</v>
       </c>
       <c r="C14">
         <f>IF(ISNA(nom_unconverted!C14),NA(),nom_unconverted!C14/nom_unconverted!$K14*100)</f>
-        <v>4.795095719373375</v>
+        <v>5.3205128205128212</v>
       </c>
       <c r="D14">
         <f>IF(ISNA(nom_unconverted!D14),NA(),nom_unconverted!D14/nom_unconverted!$K14*100)</f>
-        <v>5.8542534083915898</v>
+        <v>6.4957264957264966</v>
       </c>
       <c r="E14" t="e">
         <f>IF(ISNA(nom_unconverted!E14),NA(),nom_unconverted!E14/nom_unconverted!$K14*100)</f>
@@ -2967,25 +3151,29 @@
         <v>#N/A</v>
       </c>
       <c r="J14" t="e">
-        <f>nom_unconverted!J14/nom_unconverted!$K14*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J14),NA(),nom_unconverted!J14/nom_unconverted!$K14*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K14">
+        <f>kaitz_index!D14</f>
+        <v>0.50414593698175791</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>2012</v>
       </c>
       <c r="B15">
         <f>IF(ISNA(nom_unconverted!B15),NA(),nom_unconverted!B15/nom_unconverted!$K15*100)</f>
-        <v>3.4544722212704428</v>
+        <v>3.8333333333333339</v>
       </c>
       <c r="C15">
         <f>IF(ISNA(nom_unconverted!C15),NA(),nom_unconverted!C15/nom_unconverted!$K15*100)</f>
-        <v>4.6748020820453284</v>
+        <v>5.1875</v>
       </c>
       <c r="D15">
         <f>IF(ISNA(nom_unconverted!D15),NA(),nom_unconverted!D15/nom_unconverted!$K15*100)</f>
-        <v>5.8106475678434899</v>
+        <v>6.447916666666667</v>
       </c>
       <c r="E15" t="e">
         <f>IF(ISNA(nom_unconverted!E15),NA(),nom_unconverted!E15/nom_unconverted!$K15*100)</f>
@@ -3008,25 +3196,29 @@
         <v>#N/A</v>
       </c>
       <c r="J15" t="e">
-        <f>nom_unconverted!J15/nom_unconverted!$K15*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J15),NA(),nom_unconverted!J15/nom_unconverted!$K15*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K15">
+        <f>kaitz_index!D15</f>
+        <v>0.50696150696150699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2013</v>
       </c>
       <c r="B16">
         <f>IF(ISNA(nom_unconverted!B16),NA(),nom_unconverted!B16/nom_unconverted!$K16*100)</f>
-        <v>3.4137881871565945</v>
+        <v>3.7881873727087574</v>
       </c>
       <c r="C16">
         <f>IF(ISNA(nom_unconverted!C16),NA(),nom_unconverted!C16/nom_unconverted!$K16*100)</f>
-        <v>4.6159555326337829</v>
+        <v>5.1221995926680242</v>
       </c>
       <c r="D16">
         <f>IF(ISNA(nom_unconverted!D16),NA(),nom_unconverted!D16/nom_unconverted!$K16*100)</f>
-        <v>5.7905923282145455</v>
+        <v>6.4256619144602842</v>
       </c>
       <c r="E16" t="e">
         <f>IF(ISNA(nom_unconverted!E16),NA(),nom_unconverted!E16/nom_unconverted!$K16*100)</f>
@@ -3049,25 +3241,29 @@
         <v>#N/A</v>
       </c>
       <c r="J16" t="e">
-        <f>nom_unconverted!J16/nom_unconverted!$K16*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J16),NA(),nom_unconverted!J16/nom_unconverted!$K16*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K16">
+        <f>kaitz_index!D16</f>
+        <v>0.51051779935275077</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>2014</v>
       </c>
       <c r="B17">
         <f>IF(ISNA(nom_unconverted!B17),NA(),nom_unconverted!B17/nom_unconverted!$K17*100)</f>
-        <v>3.428277708520437</v>
+        <v>3.8052208835341368</v>
       </c>
       <c r="C17">
         <f>IF(ISNA(nom_unconverted!C17),NA(),nom_unconverted!C17/nom_unconverted!$K17*100)</f>
-        <v>4.6403864497915146</v>
+        <v>5.1506024096385543</v>
       </c>
       <c r="D17">
         <f>IF(ISNA(nom_unconverted!D17),NA(),nom_unconverted!D17/nom_unconverted!$K17*100)</f>
-        <v>5.8796319539268715</v>
+        <v>6.5261044176706831</v>
       </c>
       <c r="E17" t="e">
         <f>IF(ISNA(nom_unconverted!E17),NA(),nom_unconverted!E17/nom_unconverted!$K17*100)</f>
@@ -3090,25 +3286,29 @@
         <v>#N/A</v>
       </c>
       <c r="J17" t="e">
-        <f>nom_unconverted!J17/nom_unconverted!$K17*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J17),NA(),nom_unconverted!J17/nom_unconverted!$K17*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K17">
+        <f>kaitz_index!D17</f>
+        <v>0.51792828685258963</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>2015</v>
       </c>
       <c r="B18">
         <f>IF(ISNA(nom_unconverted!B18),NA(),nom_unconverted!B18/nom_unconverted!$K18*100)</f>
-        <v>3.4878056499953285</v>
+        <v>3.8699999999999997</v>
       </c>
       <c r="C18">
         <f>IF(ISNA(nom_unconverted!C18),NA(),nom_unconverted!C18/nom_unconverted!$K18*100)</f>
-        <v>4.7765813811305531</v>
+        <v>5.3</v>
       </c>
       <c r="D18">
         <f>IF(ISNA(nom_unconverted!D18),NA(),nom_unconverted!D18/nom_unconverted!$K18*100)</f>
-        <v>6.0383198591650391</v>
+        <v>6.7</v>
       </c>
       <c r="E18" t="e">
         <f>IF(ISNA(nom_unconverted!E18),NA(),nom_unconverted!E18/nom_unconverted!$K18*100)</f>
@@ -3131,21 +3331,25 @@
         <v>#N/A</v>
       </c>
       <c r="J18" t="e">
-        <f>nom_unconverted!J18/nom_unconverted!$K18*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J18),NA(),nom_unconverted!J18/nom_unconverted!$K18*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K18">
+        <f>kaitz_index!D18</f>
+        <v>0.52466718872357088</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>2016</v>
       </c>
       <c r="B19">
         <f>IF(ISNA(nom_unconverted!B19),NA(),nom_unconverted!B19/nom_unconverted!$K19*100)</f>
-        <v>3.4529851486225436</v>
+        <v>3.8316831683168315</v>
       </c>
       <c r="C19">
         <f>IF(ISNA(nom_unconverted!C19),NA(),nom_unconverted!C19/nom_unconverted!$K19*100)</f>
-        <v>4.7288943895864293</v>
+        <v>5.2475247524752477</v>
       </c>
       <c r="D19" t="e">
         <f>IF(ISNA(nom_unconverted!D19),NA(),nom_unconverted!D19/nom_unconverted!$K19*100)</f>
@@ -3161,32 +3365,36 @@
       </c>
       <c r="G19">
         <f>IF(ISNA(nom_unconverted!G19),NA(),nom_unconverted!G19/nom_unconverted!$K19*100)</f>
-        <v>5.9780363038168067</v>
+        <v>6.6336633663366342</v>
       </c>
       <c r="H19">
         <f>IF(ISNA(nom_unconverted!H19),NA(),nom_unconverted!H19/nom_unconverted!$K19*100)</f>
-        <v>6.4241584160419416</v>
+        <v>7.1287128712871297</v>
       </c>
       <c r="I19" t="e">
         <f>IF(ISNA(nom_unconverted!I19),NA(),nom_unconverted!I19/nom_unconverted!$K19*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J19" t="e">
-        <f>nom_unconverted!J19/nom_unconverted!$K19*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J19),NA(),nom_unconverted!J19/nom_unconverted!$K19*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K19">
+        <f>kaitz_index!D19</f>
+        <v>0.54504163512490533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>2017</v>
       </c>
       <c r="B20">
         <f>IF(ISNA(nom_unconverted!B20),NA(),nom_unconverted!B20/nom_unconverted!$K20*100)</f>
-        <v>3.5234674187786559</v>
+        <v>3.9092664092664089</v>
       </c>
       <c r="C20">
         <f>IF(ISNA(nom_unconverted!C20),NA(),nom_unconverted!C20/nom_unconverted!$K20*100)</f>
-        <v>4.8719549494223386</v>
+        <v>5.4054054054054053</v>
       </c>
       <c r="D20" t="e">
         <f>IF(ISNA(nom_unconverted!D20),NA(),nom_unconverted!D20/nom_unconverted!$K20*100)</f>
@@ -3202,32 +3410,36 @@
       </c>
       <c r="G20">
         <f>IF(ISNA(nom_unconverted!G20),NA(),nom_unconverted!G20/nom_unconverted!$K20*100)</f>
-        <v>6.1334432845406228</v>
+        <v>6.8050193050193055</v>
       </c>
       <c r="H20">
         <f>IF(ISNA(nom_unconverted!H20),NA(),nom_unconverted!H20/nom_unconverted!$K20*100)</f>
-        <v>6.5249396644049176</v>
+        <v>7.2393822393822402</v>
       </c>
       <c r="I20" t="e">
         <f>IF(ISNA(nom_unconverted!I20),NA(),nom_unconverted!I20/nom_unconverted!$K20*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J20" t="e">
-        <f>nom_unconverted!J20/nom_unconverted!$K20*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J20),NA(),nom_unconverted!J20/nom_unconverted!$K20*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K20">
+        <f>kaitz_index!D20</f>
+        <v>0.54824561403508776</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2018</v>
       </c>
       <c r="B21">
         <f>IF(ISNA(nom_unconverted!B21),NA(),nom_unconverted!B21/nom_unconverted!$K21*100)</f>
-        <v>3.5720644900318912</v>
+        <v>3.9622641509433967</v>
       </c>
       <c r="C21">
         <f>IF(ISNA(nom_unconverted!C21),NA(),nom_unconverted!C21/nom_unconverted!$K21*100)</f>
-        <v>5.0179001169495612</v>
+        <v>5.5660377358490569</v>
       </c>
       <c r="D21" t="e">
         <f>IF(ISNA(nom_unconverted!D21),NA(),nom_unconverted!D21/nom_unconverted!$K21*100)</f>
@@ -3243,32 +3455,36 @@
       </c>
       <c r="G21">
         <f>IF(ISNA(nom_unconverted!G21),NA(),nom_unconverted!G21/nom_unconverted!$K21*100)</f>
-        <v>6.2766276039131803</v>
+        <v>6.9622641509433967</v>
       </c>
       <c r="H21">
         <f>IF(ISNA(nom_unconverted!H21),NA(),nom_unconverted!H21/nom_unconverted!$K21*100)</f>
-        <v>6.6593487992737401</v>
+        <v>7.3867924528301891</v>
       </c>
       <c r="I21" t="e">
         <f>IF(ISNA(nom_unconverted!I21),NA(),nom_unconverted!I21/nom_unconverted!$K21*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J21" t="e">
-        <f>nom_unconverted!J21/nom_unconverted!$K21*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J21),NA(),nom_unconverted!J21/nom_unconverted!$K21*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K21">
+        <f>kaitz_index!D21</f>
+        <v>0.55729537366548043</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>2019</v>
       </c>
       <c r="B22">
         <f>IF(ISNA(nom_unconverted!B22),NA(),nom_unconverted!B22/nom_unconverted!$K22*100)</f>
-        <v>3.6364332096525551</v>
+        <v>4.0352504638218916</v>
       </c>
       <c r="C22">
         <f>IF(ISNA(nom_unconverted!C22),NA(),nom_unconverted!C22/nom_unconverted!$K22*100)</f>
-        <v>5.1411641929570608</v>
+        <v>5.7050092764378482</v>
       </c>
       <c r="D22" t="e">
         <f>IF(ISNA(nom_unconverted!D22),NA(),nom_unconverted!D22/nom_unconverted!$K22*100)</f>
@@ -3284,32 +3500,36 @@
       </c>
       <c r="G22">
         <f>IF(ISNA(nom_unconverted!G22),NA(),nom_unconverted!G22/nom_unconverted!$K22*100)</f>
-        <v>6.4369047619137181</v>
+        <v>7.1428571428571441</v>
       </c>
       <c r="H22">
         <f>IF(ISNA(nom_unconverted!H22),NA(),nom_unconverted!H22/nom_unconverted!$K22*100)</f>
-        <v>6.8632452071833283</v>
+        <v>7.6159554730983308</v>
       </c>
       <c r="I22" t="e">
         <f>IF(ISNA(nom_unconverted!I22),NA(),nom_unconverted!I22/nom_unconverted!$K22*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J22" t="e">
-        <f>nom_unconverted!J22/nom_unconverted!$K22*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J22),NA(),nom_unconverted!J22/nom_unconverted!$K22*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K22">
+        <f>kaitz_index!D22</f>
+        <v>0.56659765355417535</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2020</v>
       </c>
       <c r="B23">
         <f>IF(ISNA(nom_unconverted!B23),NA(),nom_unconverted!B23/nom_unconverted!$K23*100)</f>
-        <v>3.7663579309123154</v>
+        <v>4.178145087235996</v>
       </c>
       <c r="C23">
         <f>IF(ISNA(nom_unconverted!C23),NA(),nom_unconverted!C23/nom_unconverted!$K23*100)</f>
-        <v>5.3391227811833923</v>
+        <v>5.9228650137741052</v>
       </c>
       <c r="D23" t="e">
         <f>IF(ISNA(nom_unconverted!D23),NA(),nom_unconverted!D23/nom_unconverted!$K23*100)</f>
@@ -3325,32 +3545,36 @@
       </c>
       <c r="G23">
         <f>IF(ISNA(nom_unconverted!G23),NA(),nom_unconverted!G23/nom_unconverted!$K23*100)</f>
-        <v>6.7877219853804363</v>
+        <v>7.5298438934802565</v>
       </c>
       <c r="H23">
         <f>IF(ISNA(nom_unconverted!H23),NA(),nom_unconverted!H23/nom_unconverted!$K23*100)</f>
-        <v>7.2181628917704161</v>
+        <v>8.0073461891643714</v>
       </c>
       <c r="I23" t="e">
         <f>IF(ISNA(nom_unconverted!I23),NA(),nom_unconverted!I23/nom_unconverted!$K23*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J23" t="e">
-        <f>nom_unconverted!J23/nom_unconverted!$K23*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J23),NA(),nom_unconverted!J23/nom_unconverted!$K23*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K23">
+        <f>kaitz_index!D23</f>
+        <v>0.58602150537634412</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>2021</v>
       </c>
       <c r="B24">
         <f>IF(ISNA(nom_unconverted!B24),NA(),nom_unconverted!B24/nom_unconverted!$K24*100)</f>
-        <v>3.7303576503974472</v>
+        <v>4.1397849462365599</v>
       </c>
       <c r="C24">
         <f>IF(ISNA(nom_unconverted!C24),NA(),nom_unconverted!C24/nom_unconverted!$K24*100)</f>
-        <v>5.2967848888760285</v>
+        <v>5.8781362007168454</v>
       </c>
       <c r="D24" t="e">
         <f>IF(ISNA(nom_unconverted!D24),NA(),nom_unconverted!D24/nom_unconverted!$K24*100)</f>
@@ -3366,32 +3590,36 @@
       </c>
       <c r="G24">
         <f>IF(ISNA(nom_unconverted!G24),NA(),nom_unconverted!G24/nom_unconverted!$K24*100)</f>
-        <v>6.7501709864334751</v>
+        <v>7.4910394265232982</v>
       </c>
       <c r="H24">
         <f>IF(ISNA(nom_unconverted!H24),NA(),nom_unconverted!H24/nom_unconverted!$K24*100)</f>
-        <v>7.1942611829093632</v>
+        <v>7.9838709677419368</v>
       </c>
       <c r="I24" t="e">
         <f>IF(ISNA(nom_unconverted!I24),NA(),nom_unconverted!I24/nom_unconverted!$K24*100)</f>
         <v>#N/A</v>
       </c>
       <c r="J24" t="e">
-        <f>nom_unconverted!J24/nom_unconverted!$K24*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J24),NA(),nom_unconverted!J24/nom_unconverted!$K24*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K24">
+        <f>kaitz_index!D24</f>
+        <v>0.58541392904073586</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>2022</v>
       </c>
       <c r="B25">
         <f>IF(ISNA(nom_unconverted!B25),NA(),nom_unconverted!B25/nom_unconverted!$K25*100)</f>
-        <v>3.5986813333286114</v>
+        <v>3.9917012448132776</v>
       </c>
       <c r="C25">
         <f>IF(ISNA(nom_unconverted!C25),NA(),nom_unconverted!C25/nom_unconverted!$K25*100)</f>
-        <v>5.1099778600071559</v>
+        <v>5.6680497925311206</v>
       </c>
       <c r="D25" t="e">
         <f>IF(ISNA(nom_unconverted!D25),NA(),nom_unconverted!D25/nom_unconverted!$K25*100)</f>
@@ -3399,11 +3627,11 @@
       </c>
       <c r="E25">
         <f>IF(ISNA(nom_unconverted!E25),NA(),nom_unconverted!E25/nom_unconverted!$K25*100)</f>
-        <v>6.8681693638163521</v>
+        <v>7.618257261410788</v>
       </c>
       <c r="F25">
         <f>IF(ISNA(nom_unconverted!F25),NA(),nom_unconverted!F25/nom_unconverted!$K25*100)</f>
-        <v>7.1075826749733491</v>
+        <v>7.8838174273858916</v>
       </c>
       <c r="G25" t="e">
         <f>IF(ISNA(nom_unconverted!G25),NA(),nom_unconverted!G25/nom_unconverted!$K25*100)</f>
@@ -3418,21 +3646,25 @@
         <v>#N/A</v>
       </c>
       <c r="J25" t="e">
-        <f>nom_unconverted!J25/nom_unconverted!$K25*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J25),NA(),nom_unconverted!J25/nom_unconverted!$K25*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K25">
+        <f>kaitz_index!D25</f>
+        <v>0.59635907093534213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>2023</v>
       </c>
       <c r="B26">
         <f>IF(ISNA(nom_unconverted!B26),NA(),nom_unconverted!B26/nom_unconverted!$K26*100)</f>
-        <v>3.6990101072046406</v>
+        <v>4.1057542768273718</v>
       </c>
       <c r="C26">
         <f>IF(ISNA(nom_unconverted!C26),NA(),nom_unconverted!C26/nom_unconverted!$K26*100)</f>
-        <v>5.2472700195005224</v>
+        <v>5.8242612752721623</v>
       </c>
       <c r="D26" t="e">
         <f>IF(ISNA(nom_unconverted!D26),NA(),nom_unconverted!D26/nom_unconverted!$K26*100)</f>
@@ -3440,11 +3672,11 @@
       </c>
       <c r="E26">
         <f>IF(ISNA(nom_unconverted!E26),NA(),nom_unconverted!E26/nom_unconverted!$K26*100)</f>
-        <v>7.1318035779059166</v>
+        <v>7.9160186625194404</v>
       </c>
       <c r="F26">
         <f>IF(ISNA(nom_unconverted!F26),NA(),nom_unconverted!F26/nom_unconverted!$K26*100)</f>
-        <v>7.2999404009606739</v>
+        <v>8.1026438569206842</v>
       </c>
       <c r="G26" t="e">
         <f>IF(ISNA(nom_unconverted!G26),NA(),nom_unconverted!G26/nom_unconverted!$K26*100)</f>
@@ -3459,25 +3691,29 @@
         <v>#N/A</v>
       </c>
       <c r="J26" t="e">
-        <f>nom_unconverted!J26/nom_unconverted!$K26*100</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <f>IF(ISNA(nom_unconverted!J26),NA(),nom_unconverted!J26/nom_unconverted!$K26*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K26">
+        <f>kaitz_index!D26</f>
+        <v>0.59474885844748859</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>2024</v>
       </c>
       <c r="B27">
         <f>IF(ISNA(nom_unconverted!B27),NA(),nom_unconverted!B27/nom_unconverted!$K27*100)</f>
-        <v>4.3416096864427214</v>
+        <v>4.8156508653122643</v>
       </c>
       <c r="C27">
         <f>IF(ISNA(nom_unconverted!C27),NA(),nom_unconverted!C27/nom_unconverted!$K27*100)</f>
-        <v>5.8340380161574057</v>
+        <v>6.4710308502633556</v>
       </c>
       <c r="D27">
         <f>IF(ISNA(nom_unconverted!D27),NA(),nom_unconverted!D27/nom_unconverted!$K27*100)</f>
-        <v>7.7606273145163618</v>
+        <v>8.6079759217456733</v>
       </c>
       <c r="E27" t="e">
         <f>IF(ISNA(nom_unconverted!E27),NA(),nom_unconverted!E27/nom_unconverted!$K27*100)</f>
@@ -3500,8 +3736,57 @@
         <v>#N/A</v>
       </c>
       <c r="J27" t="e">
-        <f>nom_unconverted!J27/nom_unconverted!$K27*100</f>
-        <v>#N/A</v>
+        <f>IF(ISNA(nom_unconverted!J27),NA(),nom_unconverted!J27/nom_unconverted!$K27*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K27">
+        <f>kaitz_index!D27</f>
+        <v>0.61307609860664525</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B28">
+        <f>IF(ISNA(nom_unconverted!B28),NA(),nom_unconverted!B28/nom_unconverted!$K28*100)</f>
+        <v>5.4710144927536231</v>
+      </c>
+      <c r="C28">
+        <f>IF(ISNA(nom_unconverted!C28),NA(),nom_unconverted!C28/nom_unconverted!$K28*100)</f>
+        <v>7.2463768115942031</v>
+      </c>
+      <c r="D28">
+        <f>IF(ISNA(nom_unconverted!D28),NA(),nom_unconverted!D28/nom_unconverted!$K28*100)</f>
+        <v>8.8478260869565233</v>
+      </c>
+      <c r="E28" t="e">
+        <f>IF(ISNA(nom_unconverted!E28),NA(),nom_unconverted!E28/nom_unconverted!$K28*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F28" t="e">
+        <f>IF(ISNA(nom_unconverted!F28),NA(),nom_unconverted!F28/nom_unconverted!$K28*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G28" t="e">
+        <f>IF(ISNA(nom_unconverted!G28),NA(),nom_unconverted!G28/nom_unconverted!$K28*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H28" t="e">
+        <f>IF(ISNA(nom_unconverted!H28),NA(),nom_unconverted!H28/nom_unconverted!$K28*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I28" t="e">
+        <f>IF(ISNA(nom_unconverted!I28),NA(),nom_unconverted!I28/nom_unconverted!$K28*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J28" t="e">
+        <f>IF(ISNA(nom_unconverted!J28),NA(),nom_unconverted!J28/nom_unconverted!$K28*100)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K28">
+        <f>kaitz_index!D28</f>
+        <v>0.62074224707676662</v>
       </c>
     </row>
   </sheetData>
@@ -3511,13 +3796,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECE490B-0F3A-467A-A10C-92E0D8D54D53}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="10" max="10" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
@@ -3551,8 +3836,11 @@
       <c r="K1" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1999</v>
       </c>
@@ -3562,41 +3850,45 @@
       </c>
       <c r="C2">
         <f>IF(ISNA(nom_converted!C2),NA(),nom_converted!C2/nom_converted!$K2*100)</f>
-        <v>3.7259676122962895</v>
+        <v>4.1322314049586781</v>
       </c>
       <c r="D2">
         <f>IF(ISNA(nom_converted!D2),NA(),nom_converted!D2/nom_converted!$K2*100)</f>
-        <v>3.7259676122962895</v>
+        <v>4.1322314049586781</v>
       </c>
       <c r="E2">
         <f>IF(ISNA(nom_converted!E2),NA(),nom_converted!E2/nom_converted!$K2*100)</f>
-        <v>3.7259676122962895</v>
+        <v>4.1322314049586781</v>
       </c>
       <c r="F2">
         <f>IF(ISNA(nom_converted!F2),NA(),nom_converted!F2/nom_converted!$K2*100)</f>
-        <v>3.7259676122962895</v>
+        <v>4.1322314049586781</v>
       </c>
       <c r="G2">
         <f>IF(ISNA(nom_converted!G2),NA(),nom_converted!G2/nom_converted!$K2*100)</f>
-        <v>4.4711611347555484</v>
+        <v>4.9586776859504145</v>
       </c>
       <c r="H2">
         <f>IF(ISNA(nom_converted!H2),NA(),nom_converted!H2/nom_converted!$K2*100)</f>
-        <v>4.4711611347555484</v>
+        <v>4.9586776859504145</v>
       </c>
       <c r="I2">
         <f>IF(ISNA(nom_converted!I2),NA(),nom_converted!I2/nom_converted!$K2*100)</f>
-        <v>4.4711611347555484</v>
+        <v>4.9586776859504145</v>
       </c>
       <c r="J2">
         <f>IF(ISNA(nom_converted!J2),NA(),nom_converted!J2/nom_converted!$K2*100)</f>
-        <v>4.4711611347555484</v>
-      </c>
-      <c r="K2">
-        <v>80.515997780000006</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>4.9586776859504145</v>
+      </c>
+      <c r="K2" s="7">
+        <v>72.599999999999994</v>
+      </c>
+      <c r="L2">
+        <f>kaitz_index!D2</f>
+        <v>0.43269230769230771</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2000</v>
       </c>
@@ -3606,41 +3898,45 @@
       </c>
       <c r="C3">
         <f>IF(ISNA(nom_converted!C3),NA(),nom_converted!C3/nom_converted!$K3*100)</f>
-        <v>3.9279001136179477</v>
+        <v>4.3596730245231603</v>
       </c>
       <c r="D3">
         <f>IF(ISNA(nom_converted!D3),NA(),nom_converted!D3/nom_converted!$K3*100)</f>
-        <v>3.9279001136179477</v>
+        <v>4.3596730245231603</v>
       </c>
       <c r="E3">
         <f>IF(ISNA(nom_converted!E3),NA(),nom_converted!E3/nom_converted!$K3*100)</f>
-        <v>3.9279001136179477</v>
+        <v>4.3596730245231603</v>
       </c>
       <c r="F3">
         <f>IF(ISNA(nom_converted!F3),NA(),nom_converted!F3/nom_converted!$K3*100)</f>
-        <v>3.9279001136179477</v>
+        <v>4.3596730245231603</v>
       </c>
       <c r="G3">
         <f>IF(ISNA(nom_converted!G3),NA(),nom_converted!G3/nom_converted!$K3*100)</f>
-        <v>4.5416345063707526</v>
+        <v>5.0408719346049047</v>
       </c>
       <c r="H3">
         <f>IF(ISNA(nom_converted!H3),NA(),nom_converted!H3/nom_converted!$K3*100)</f>
-        <v>4.5416345063707526</v>
+        <v>5.0408719346049047</v>
       </c>
       <c r="I3">
         <f>IF(ISNA(nom_converted!I3),NA(),nom_converted!I3/nom_converted!$K3*100)</f>
-        <v>4.5416345063707526</v>
+        <v>5.0408719346049047</v>
       </c>
       <c r="J3">
         <f>IF(ISNA(nom_converted!J3),NA(),nom_converted!J3/nom_converted!$K3*100)</f>
-        <v>4.5416345063707526</v>
-      </c>
-      <c r="K3">
-        <v>81.468466800000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>5.0408719346049047</v>
+      </c>
+      <c r="K3" s="7">
+        <v>73.400000000000006</v>
+      </c>
+      <c r="L3">
+        <f>kaitz_index!D3</f>
+        <v>0.4277456647398844</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2001</v>
       </c>
@@ -3650,41 +3946,45 @@
       </c>
       <c r="C4">
         <f>IF(ISNA(nom_converted!C4),NA(),nom_converted!C4/nom_converted!$K4*100)</f>
-        <v>4.2313024035612399</v>
+        <v>4.6916890080428955</v>
       </c>
       <c r="D4">
         <f>IF(ISNA(nom_converted!D4),NA(),nom_converted!D4/nom_converted!$K4*100)</f>
-        <v>4.2313024035612399</v>
+        <v>4.6916890080428955</v>
       </c>
       <c r="E4">
         <f>IF(ISNA(nom_converted!E4),NA(),nom_converted!E4/nom_converted!$K4*100)</f>
-        <v>4.2313024035612399</v>
+        <v>4.6916890080428955</v>
       </c>
       <c r="F4">
         <f>IF(ISNA(nom_converted!F4),NA(),nom_converted!F4/nom_converted!$K4*100)</f>
-        <v>4.2313024035612399</v>
+        <v>4.6916890080428955</v>
       </c>
       <c r="G4">
         <f>IF(ISNA(nom_converted!G4),NA(),nom_converted!G4/nom_converted!$K4*100)</f>
-        <v>4.9566685298860236</v>
+        <v>5.4959785522788209</v>
       </c>
       <c r="H4">
         <f>IF(ISNA(nom_converted!H4),NA(),nom_converted!H4/nom_converted!$K4*100)</f>
-        <v>4.9566685298860236</v>
+        <v>5.4959785522788209</v>
       </c>
       <c r="I4">
         <f>IF(ISNA(nom_converted!I4),NA(),nom_converted!I4/nom_converted!$K4*100)</f>
-        <v>4.9566685298860236</v>
+        <v>5.4959785522788209</v>
       </c>
       <c r="J4">
         <f>IF(ISNA(nom_converted!J4),NA(),nom_converted!J4/nom_converted!$K4*100)</f>
-        <v>4.9566685298860236</v>
-      </c>
-      <c r="K4">
-        <v>82.716848529999993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>5.4959785522788209</v>
+      </c>
+      <c r="K4" s="7">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="L4">
+        <f>kaitz_index!D4</f>
+        <v>0.45555555555555549</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>2002</v>
       </c>
@@ -3694,41 +3994,45 @@
       </c>
       <c r="C5">
         <f>IF(ISNA(nom_converted!C5),NA(),nom_converted!C5/nom_converted!$K5*100)</f>
-        <v>4.1679330469780185</v>
+        <v>4.6235138705416112</v>
       </c>
       <c r="D5">
         <f>IF(ISNA(nom_converted!D5),NA(),nom_converted!D5/nom_converted!$K5*100)</f>
-        <v>4.1679330469780185</v>
+        <v>4.6235138705416112</v>
       </c>
       <c r="E5">
         <f>IF(ISNA(nom_converted!E5),NA(),nom_converted!E5/nom_converted!$K5*100)</f>
-        <v>4.1679330469780185</v>
+        <v>4.6235138705416112</v>
       </c>
       <c r="F5">
         <f>IF(ISNA(nom_converted!F5),NA(),nom_converted!F5/nom_converted!$K5*100)</f>
-        <v>4.1679330469780185</v>
+        <v>4.6235138705416112</v>
       </c>
       <c r="G5">
         <f>IF(ISNA(nom_converted!G5),NA(),nom_converted!G5/nom_converted!$K5*100)</f>
-        <v>5.0015196563736213</v>
+        <v>5.5482166446499335</v>
       </c>
       <c r="H5">
         <f>IF(ISNA(nom_converted!H5),NA(),nom_converted!H5/nom_converted!$K5*100)</f>
-        <v>5.0015196563736213</v>
+        <v>5.5482166446499335</v>
       </c>
       <c r="I5">
         <f>IF(ISNA(nom_converted!I5),NA(),nom_converted!I5/nom_converted!$K5*100)</f>
-        <v>5.0015196563736213</v>
+        <v>5.5482166446499335</v>
       </c>
       <c r="J5">
         <f>IF(ISNA(nom_converted!J5),NA(),nom_converted!J5/nom_converted!$K5*100)</f>
-        <v>5.0015196563736213</v>
-      </c>
-      <c r="K5">
-        <v>83.974477530000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>5.5482166446499335</v>
+      </c>
+      <c r="K5" s="7">
+        <v>75.7</v>
+      </c>
+      <c r="L5">
+        <f>kaitz_index!D5</f>
+        <v>0.44871794871794879</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>2003</v>
       </c>
@@ -3738,962 +4042,1532 @@
       </c>
       <c r="C6">
         <f>IF(ISNA(nom_converted!C6),NA(),nom_converted!C6/nom_converted!$K6*100)</f>
-        <v>4.463741038241972</v>
+        <v>4.9543676662320726</v>
       </c>
       <c r="D6">
         <f>IF(ISNA(nom_converted!D6),NA(),nom_converted!D6/nom_converted!$K6*100)</f>
-        <v>4.463741038241972</v>
+        <v>4.9543676662320726</v>
       </c>
       <c r="E6">
         <f>IF(ISNA(nom_converted!E6),NA(),nom_converted!E6/nom_converted!$K6*100)</f>
-        <v>4.463741038241972</v>
+        <v>4.9543676662320726</v>
       </c>
       <c r="F6">
         <f>IF(ISNA(nom_converted!F6),NA(),nom_converted!F6/nom_converted!$K6*100)</f>
-        <v>4.463741038241972</v>
+        <v>4.9543676662320726</v>
       </c>
       <c r="G6">
         <f>IF(ISNA(nom_converted!G6),NA(),nom_converted!G6/nom_converted!$K6*100)</f>
-        <v>5.2860091242339138</v>
+        <v>5.867014341590612</v>
       </c>
       <c r="H6">
         <f>IF(ISNA(nom_converted!H6),NA(),nom_converted!H6/nom_converted!$K6*100)</f>
-        <v>5.2860091242339138</v>
+        <v>5.867014341590612</v>
       </c>
       <c r="I6">
         <f>IF(ISNA(nom_converted!I6),NA(),nom_converted!I6/nom_converted!$K6*100)</f>
-        <v>5.2860091242339138</v>
+        <v>5.867014341590612</v>
       </c>
       <c r="J6">
         <f>IF(ISNA(nom_converted!J6),NA(),nom_converted!J6/nom_converted!$K6*100)</f>
-        <v>5.2860091242339138</v>
-      </c>
-      <c r="K6">
-        <v>85.130386540000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>5.867014341590612</v>
+      </c>
+      <c r="K6" s="7">
+        <v>76.7</v>
+      </c>
+      <c r="L6">
+        <f>kaitz_index!D6</f>
+        <v>0.46343975283213179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>2004</v>
       </c>
       <c r="B7">
         <f>IF(ISNA(nom_converted!B7),NA(),nom_converted!B7/nom_converted!$K7*100)</f>
-        <v>3.4756803085082799</v>
+        <v>3.8560411311053984</v>
       </c>
       <c r="C7">
         <f>IF(ISNA(nom_converted!C7),NA(),nom_converted!C7/nom_converted!$K7*100)</f>
-        <v>4.7500964216279824</v>
+        <v>5.2699228791773782</v>
       </c>
       <c r="D7">
         <f>IF(ISNA(nom_converted!D7),NA(),nom_converted!D7/nom_converted!$K7*100)</f>
-        <v>4.7500964216279824</v>
+        <v>5.2699228791773782</v>
       </c>
       <c r="E7">
         <f>IF(ISNA(nom_converted!E7),NA(),nom_converted!E7/nom_converted!$K7*100)</f>
-        <v>4.7500964216279824</v>
+        <v>5.2699228791773782</v>
       </c>
       <c r="F7">
         <f>IF(ISNA(nom_converted!F7),NA(),nom_converted!F7/nom_converted!$K7*100)</f>
-        <v>4.7500964216279824</v>
+        <v>5.2699228791773782</v>
       </c>
       <c r="G7">
         <f>IF(ISNA(nom_converted!G7),NA(),nom_converted!G7/nom_converted!$K7*100)</f>
-        <v>5.6190164987550517</v>
+        <v>6.2339331619537273</v>
       </c>
       <c r="H7">
         <f>IF(ISNA(nom_converted!H7),NA(),nom_converted!H7/nom_converted!$K7*100)</f>
-        <v>5.6190164987550517</v>
+        <v>6.2339331619537273</v>
       </c>
       <c r="I7">
         <f>IF(ISNA(nom_converted!I7),NA(),nom_converted!I7/nom_converted!$K7*100)</f>
-        <v>5.6190164987550517</v>
+        <v>6.2339331619537273</v>
       </c>
       <c r="J7">
         <f>IF(ISNA(nom_converted!J7),NA(),nom_converted!J7/nom_converted!$K7*100)</f>
-        <v>5.6190164987550517</v>
-      </c>
-      <c r="K7">
-        <v>86.31403736</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.2339331619537273</v>
+      </c>
+      <c r="K7" s="7">
+        <v>77.8</v>
+      </c>
+      <c r="L7">
+        <f>kaitz_index!D7</f>
+        <v>0.48067393458870167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>2005</v>
       </c>
       <c r="B8">
         <f>IF(ISNA(nom_converted!B8),NA(),nom_converted!B8/nom_converted!$K8*100)</f>
-        <v>3.4045545177744434</v>
+        <v>3.7783375314861458</v>
       </c>
       <c r="C8">
         <f>IF(ISNA(nom_converted!C8),NA(),nom_converted!C8/nom_converted!$K8*100)</f>
-        <v>4.8231189001804609</v>
+        <v>5.3526448362720398</v>
       </c>
       <c r="D8">
         <f>IF(ISNA(nom_converted!D8),NA(),nom_converted!D8/nom_converted!$K8*100)</f>
-        <v>4.8231189001804609</v>
+        <v>5.3526448362720398</v>
       </c>
       <c r="E8">
         <f>IF(ISNA(nom_converted!E8),NA(),nom_converted!E8/nom_converted!$K8*100)</f>
-        <v>4.8231189001804609</v>
+        <v>5.3526448362720398</v>
       </c>
       <c r="F8">
         <f>IF(ISNA(nom_converted!F8),NA(),nom_converted!F8/nom_converted!$K8*100)</f>
-        <v>4.8231189001804609</v>
+        <v>5.3526448362720398</v>
       </c>
       <c r="G8">
         <f>IF(ISNA(nom_converted!G8),NA(),nom_converted!G8/nom_converted!$K8*100)</f>
-        <v>5.7310001049203123</v>
+        <v>6.3602015113350117</v>
       </c>
       <c r="H8">
         <f>IF(ISNA(nom_converted!H8),NA(),nom_converted!H8/nom_converted!$K8*100)</f>
-        <v>5.7310001049203123</v>
+        <v>6.3602015113350117</v>
       </c>
       <c r="I8">
         <f>IF(ISNA(nom_converted!I8),NA(),nom_converted!I8/nom_converted!$K8*100)</f>
-        <v>5.7310001049203123</v>
+        <v>6.3602015113350117</v>
       </c>
       <c r="J8">
         <f>IF(ISNA(nom_converted!J8),NA(),nom_converted!J8/nom_converted!$K8*100)</f>
-        <v>5.7310001049203123</v>
-      </c>
-      <c r="K8">
-        <v>88.117255409999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.3602015113350117</v>
+      </c>
+      <c r="K8" s="7">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="L8">
+        <f>kaitz_index!D8</f>
+        <v>0.48698167791706848</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>2006</v>
       </c>
       <c r="B9">
         <f>IF(ISNA(nom_converted!B9),NA(),nom_converted!B9/nom_converted!$K9*100)</f>
-        <v>3.655249411060483</v>
+        <v>4.0540540540540535</v>
       </c>
       <c r="C9">
         <f>IF(ISNA(nom_converted!C9),NA(),nom_converted!C9/nom_converted!$K9*100)</f>
-        <v>4.9290484482482269</v>
+        <v>5.4668304668304666</v>
       </c>
       <c r="D9">
         <f>IF(ISNA(nom_converted!D9),NA(),nom_converted!D9/nom_converted!$K9*100)</f>
-        <v>4.9290484482482269</v>
+        <v>5.4668304668304666</v>
       </c>
       <c r="E9">
         <f>IF(ISNA(nom_converted!E9),NA(),nom_converted!E9/nom_converted!$K9*100)</f>
-        <v>4.9290484482482269</v>
+        <v>5.4668304668304666</v>
       </c>
       <c r="F9">
         <f>IF(ISNA(nom_converted!F9),NA(),nom_converted!F9/nom_converted!$K9*100)</f>
-        <v>4.9290484482482269</v>
+        <v>5.4668304668304666</v>
       </c>
       <c r="G9">
         <f>IF(ISNA(nom_converted!G9),NA(),nom_converted!G9/nom_converted!$K9*100)</f>
-        <v>5.925934651264722</v>
+        <v>6.5724815724815713</v>
       </c>
       <c r="H9">
         <f>IF(ISNA(nom_converted!H9),NA(),nom_converted!H9/nom_converted!$K9*100)</f>
-        <v>5.925934651264722</v>
+        <v>6.5724815724815713</v>
       </c>
       <c r="I9">
         <f>IF(ISNA(nom_converted!I9),NA(),nom_converted!I9/nom_converted!$K9*100)</f>
-        <v>5.925934651264722</v>
+        <v>6.5724815724815713</v>
       </c>
       <c r="J9">
         <f>IF(ISNA(nom_converted!J9),NA(),nom_converted!J9/nom_converted!$K9*100)</f>
-        <v>5.925934651264722</v>
-      </c>
-      <c r="K9">
-        <v>90.281117069999993</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.5724815724815713</v>
+      </c>
+      <c r="K9" s="7">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="L9">
+        <f>kaitz_index!D9</f>
+        <v>0.49906716417910441</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>2007</v>
       </c>
       <c r="B10">
         <f>IF(ISNA(nom_converted!B10),NA(),nom_converted!B10/nom_converted!$K10*100)</f>
-        <v>3.6782312924859499</v>
+        <v>4.0816326530612246</v>
       </c>
       <c r="C10">
         <f>IF(ISNA(nom_converted!C10),NA(),nom_converted!C10/nom_converted!$K10*100)</f>
-        <v>4.9764305721868736</v>
+        <v>5.5222088835534215</v>
       </c>
       <c r="D10">
         <f>IF(ISNA(nom_converted!D10),NA(),nom_converted!D10/nom_converted!$K10*100)</f>
-        <v>4.9764305721868736</v>
+        <v>5.5222088835534215</v>
       </c>
       <c r="E10">
         <f>IF(ISNA(nom_converted!E10),NA(),nom_converted!E10/nom_converted!$K10*100)</f>
-        <v>4.9764305721868736</v>
+        <v>5.5222088835534215</v>
       </c>
       <c r="F10">
         <f>IF(ISNA(nom_converted!F10),NA(),nom_converted!F10/nom_converted!$K10*100)</f>
-        <v>4.9764305721868736</v>
+        <v>5.5222088835534215</v>
       </c>
       <c r="G10">
         <f>IF(ISNA(nom_converted!G10),NA(),nom_converted!G10/nom_converted!$K10*100)</f>
-        <v>5.9717166866242479</v>
+        <v>6.6266506602641053</v>
       </c>
       <c r="H10">
         <f>IF(ISNA(nom_converted!H10),NA(),nom_converted!H10/nom_converted!$K10*100)</f>
-        <v>5.9717166866242479</v>
+        <v>6.6266506602641053</v>
       </c>
       <c r="I10">
         <f>IF(ISNA(nom_converted!I10),NA(),nom_converted!I10/nom_converted!$K10*100)</f>
-        <v>5.9717166866242479</v>
+        <v>6.6266506602641053</v>
       </c>
       <c r="J10">
         <f>IF(ISNA(nom_converted!J10),NA(),nom_converted!J10/nom_converted!$K10*100)</f>
-        <v>5.9717166866242479</v>
-      </c>
-      <c r="K10">
-        <v>92.43573146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.6266506602641053</v>
+      </c>
+      <c r="K10" s="7">
+        <v>83.3</v>
+      </c>
+      <c r="L10">
+        <f>kaitz_index!D10</f>
+        <v>0.49954751131221714</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>2008</v>
       </c>
       <c r="B11">
         <f>IF(ISNA(nom_converted!B11),NA(),nom_converted!B11/nom_converted!$K11*100)</f>
-        <v>3.6889659838609457</v>
+        <v>4.0951276102088165</v>
       </c>
       <c r="C11">
         <f>IF(ISNA(nom_converted!C11),NA(),nom_converted!C11/nom_converted!$K11*100)</f>
-        <v>4.984806726067057</v>
+        <v>5.5336426914153121</v>
       </c>
       <c r="D11">
         <f>IF(ISNA(nom_converted!D11),NA(),nom_converted!D11/nom_converted!$K11*100)</f>
-        <v>4.984806726067057</v>
+        <v>5.5336426914153121</v>
       </c>
       <c r="E11">
         <f>IF(ISNA(nom_converted!E11),NA(),nom_converted!E11/nom_converted!$K11*100)</f>
-        <v>4.984806726067057</v>
+        <v>5.5336426914153121</v>
       </c>
       <c r="F11">
         <f>IF(ISNA(nom_converted!F11),NA(),nom_converted!F11/nom_converted!$K11*100)</f>
-        <v>4.984806726067057</v>
+        <v>5.5336426914153121</v>
       </c>
       <c r="G11">
         <f>IF(ISNA(nom_converted!G11),NA(),nom_converted!G11/nom_converted!$K11*100)</f>
-        <v>5.9880382684201763</v>
+        <v>6.6473317865429236</v>
       </c>
       <c r="H11">
         <f>IF(ISNA(nom_converted!H11),NA(),nom_converted!H11/nom_converted!$K11*100)</f>
-        <v>5.9880382684201763</v>
+        <v>6.6473317865429236</v>
       </c>
       <c r="I11">
         <f>IF(ISNA(nom_converted!I11),NA(),nom_converted!I11/nom_converted!$K11*100)</f>
-        <v>5.9880382684201763</v>
+        <v>6.6473317865429236</v>
       </c>
       <c r="J11">
         <f>IF(ISNA(nom_converted!J11),NA(),nom_converted!J11/nom_converted!$K11*100)</f>
-        <v>5.9880382684201763</v>
-      </c>
-      <c r="K11">
-        <v>95.690771220000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.6473317865429236</v>
+      </c>
+      <c r="K11" s="7">
+        <v>86.2</v>
+      </c>
+      <c r="L11">
+        <f>kaitz_index!D11</f>
+        <v>0.50395778364116106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>2009</v>
       </c>
       <c r="B12">
         <f>IF(ISNA(nom_converted!B12),NA(),nom_converted!B12/nom_converted!$K12*100)</f>
-        <v>3.6589877736558298</v>
+        <v>4.0614334470989757</v>
       </c>
       <c r="C12">
         <f>IF(ISNA(nom_converted!C12),NA(),nom_converted!C12/nom_converted!$K12*100)</f>
-        <v>4.9503952231814177</v>
+        <v>5.4948805460750849</v>
       </c>
       <c r="D12">
         <f>IF(ISNA(nom_converted!D12),NA(),nom_converted!D12/nom_converted!$K12*100)</f>
-        <v>4.9503952231814177</v>
+        <v>5.4948805460750849</v>
       </c>
       <c r="E12">
         <f>IF(ISNA(nom_converted!E12),NA(),nom_converted!E12/nom_converted!$K12*100)</f>
-        <v>4.9503952231814177</v>
+        <v>5.4948805460750849</v>
       </c>
       <c r="F12">
         <f>IF(ISNA(nom_converted!F12),NA(),nom_converted!F12/nom_converted!$K12*100)</f>
-        <v>4.9503952231814177</v>
+        <v>5.4948805460750849</v>
       </c>
       <c r="G12">
         <f>IF(ISNA(nom_converted!G12),NA(),nom_converted!G12/nom_converted!$K12*100)</f>
-        <v>5.944573974006671</v>
+        <v>6.5984072810011369</v>
       </c>
       <c r="H12">
         <f>IF(ISNA(nom_converted!H12),NA(),nom_converted!H12/nom_converted!$K12*100)</f>
-        <v>5.944573974006671</v>
+        <v>6.5984072810011369</v>
       </c>
       <c r="I12">
         <f>IF(ISNA(nom_converted!I12),NA(),nom_converted!I12/nom_converted!$K12*100)</f>
-        <v>5.944573974006671</v>
+        <v>6.5984072810011369</v>
       </c>
       <c r="J12">
         <f>IF(ISNA(nom_converted!J12),NA(),nom_converted!J12/nom_converted!$K12*100)</f>
-        <v>5.944573974006671</v>
-      </c>
-      <c r="K12">
-        <v>97.567967449999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.5984072810011369</v>
+      </c>
+      <c r="K12" s="7">
+        <v>87.9</v>
+      </c>
+      <c r="L12">
+        <f>kaitz_index!D12</f>
+        <v>0.50129645635263609</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>2010</v>
       </c>
       <c r="B13">
         <f>IF(ISNA(nom_converted!B13),NA(),nom_converted!B13/nom_converted!$K13*100)</f>
-        <v>3.64</v>
+        <v>4.0399556048834633</v>
       </c>
       <c r="C13">
         <f>IF(ISNA(nom_converted!C13),NA(),nom_converted!C13/nom_converted!$K13*100)</f>
-        <v>4.92</v>
+        <v>5.4605993340732528</v>
       </c>
       <c r="D13">
         <f>IF(ISNA(nom_converted!D13),NA(),nom_converted!D13/nom_converted!$K13*100)</f>
-        <v>4.92</v>
+        <v>5.4605993340732528</v>
       </c>
       <c r="E13">
         <f>IF(ISNA(nom_converted!E13),NA(),nom_converted!E13/nom_converted!$K13*100)</f>
-        <v>4.92</v>
+        <v>5.4605993340732528</v>
       </c>
       <c r="F13">
         <f>IF(ISNA(nom_converted!F13),NA(),nom_converted!F13/nom_converted!$K13*100)</f>
-        <v>5.93</v>
+        <v>6.5815760266370704</v>
       </c>
       <c r="G13">
         <f>IF(ISNA(nom_converted!G13),NA(),nom_converted!G13/nom_converted!$K13*100)</f>
-        <v>5.93</v>
+        <v>6.5815760266370704</v>
       </c>
       <c r="H13">
         <f>IF(ISNA(nom_converted!H13),NA(),nom_converted!H13/nom_converted!$K13*100)</f>
-        <v>5.93</v>
+        <v>6.5815760266370704</v>
       </c>
       <c r="I13">
         <f>IF(ISNA(nom_converted!I13),NA(),nom_converted!I13/nom_converted!$K13*100)</f>
-        <v>5.93</v>
+        <v>6.5815760266370704</v>
       </c>
       <c r="J13">
         <f>IF(ISNA(nom_converted!J13),NA(),nom_converted!J13/nom_converted!$K13*100)</f>
-        <v>5.93</v>
-      </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.5815760266370704</v>
+      </c>
+      <c r="K13" s="7">
+        <v>90.1</v>
+      </c>
+      <c r="L13">
+        <f>kaitz_index!D13</f>
+        <v>0.50042194092827008</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>2011</v>
       </c>
       <c r="B14">
         <f>IF(ISNA(nom_converted!B14),NA(),nom_converted!B14/nom_converted!$K14*100)</f>
-        <v>3.5433639050791199</v>
+        <v>3.9316239316239323</v>
       </c>
       <c r="C14">
         <f>IF(ISNA(nom_converted!C14),NA(),nom_converted!C14/nom_converted!$K14*100)</f>
-        <v>4.795095719373375</v>
+        <v>5.3205128205128212</v>
       </c>
       <c r="D14">
         <f>IF(ISNA(nom_converted!D14),NA(),nom_converted!D14/nom_converted!$K14*100)</f>
-        <v>4.795095719373375</v>
+        <v>5.3205128205128212</v>
       </c>
       <c r="E14">
         <f>IF(ISNA(nom_converted!E14),NA(),nom_converted!E14/nom_converted!$K14*100)</f>
-        <v>4.795095719373375</v>
+        <v>5.3205128205128212</v>
       </c>
       <c r="F14">
         <f>IF(ISNA(nom_converted!F14),NA(),nom_converted!F14/nom_converted!$K14*100)</f>
-        <v>5.8542534083915898</v>
+        <v>6.4957264957264966</v>
       </c>
       <c r="G14">
         <f>IF(ISNA(nom_converted!G14),NA(),nom_converted!G14/nom_converted!$K14*100)</f>
-        <v>5.8542534083915898</v>
+        <v>6.4957264957264966</v>
       </c>
       <c r="H14">
         <f>IF(ISNA(nom_converted!H14),NA(),nom_converted!H14/nom_converted!$K14*100)</f>
-        <v>5.8542534083915898</v>
+        <v>6.4957264957264966</v>
       </c>
       <c r="I14">
         <f>IF(ISNA(nom_converted!I14),NA(),nom_converted!I14/nom_converted!$K14*100)</f>
-        <v>5.8542534083915898</v>
+        <v>6.4957264957264966</v>
       </c>
       <c r="J14">
         <f>IF(ISNA(nom_converted!J14),NA(),nom_converted!J14/nom_converted!$K14*100)</f>
-        <v>5.8542534083915898</v>
-      </c>
-      <c r="K14">
-        <v>103.8561124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.4957264957264966</v>
+      </c>
+      <c r="K14" s="7">
+        <v>93.6</v>
+      </c>
+      <c r="L14">
+        <f>kaitz_index!D14</f>
+        <v>0.50414593698175791</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>2012</v>
       </c>
       <c r="B15">
         <f>IF(ISNA(nom_converted!B15),NA(),nom_converted!B15/nom_converted!$K15*100)</f>
-        <v>3.4544722212704428</v>
+        <v>3.8333333333333339</v>
       </c>
       <c r="C15">
         <f>IF(ISNA(nom_converted!C15),NA(),nom_converted!C15/nom_converted!$K15*100)</f>
-        <v>4.6748020820453284</v>
+        <v>5.1875</v>
       </c>
       <c r="D15">
         <f>IF(ISNA(nom_converted!D15),NA(),nom_converted!D15/nom_converted!$K15*100)</f>
-        <v>4.6748020820453284</v>
+        <v>5.1875</v>
       </c>
       <c r="E15">
         <f>IF(ISNA(nom_converted!E15),NA(),nom_converted!E15/nom_converted!$K15*100)</f>
-        <v>4.6748020820453284</v>
+        <v>5.1875</v>
       </c>
       <c r="F15">
         <f>IF(ISNA(nom_converted!F15),NA(),nom_converted!F15/nom_converted!$K15*100)</f>
-        <v>5.8106475678434899</v>
+        <v>6.447916666666667</v>
       </c>
       <c r="G15">
         <f>IF(ISNA(nom_converted!G15),NA(),nom_converted!G15/nom_converted!$K15*100)</f>
-        <v>5.8106475678434899</v>
+        <v>6.447916666666667</v>
       </c>
       <c r="H15">
         <f>IF(ISNA(nom_converted!H15),NA(),nom_converted!H15/nom_converted!$K15*100)</f>
-        <v>5.8106475678434899</v>
+        <v>6.447916666666667</v>
       </c>
       <c r="I15">
         <f>IF(ISNA(nom_converted!I15),NA(),nom_converted!I15/nom_converted!$K15*100)</f>
-        <v>5.8106475678434899</v>
+        <v>6.447916666666667</v>
       </c>
       <c r="J15">
         <f>IF(ISNA(nom_converted!J15),NA(),nom_converted!J15/nom_converted!$K15*100)</f>
-        <v>5.8106475678434899</v>
-      </c>
-      <c r="K15">
-        <v>106.5285741</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.447916666666667</v>
+      </c>
+      <c r="K15" s="7">
+        <v>96</v>
+      </c>
+      <c r="L15">
+        <f>kaitz_index!D15</f>
+        <v>0.50696150696150699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2013</v>
       </c>
       <c r="B16">
         <f>IF(ISNA(nom_converted!B16),NA(),nom_converted!B16/nom_converted!$K16*100)</f>
-        <v>3.4137881871565945</v>
+        <v>3.7881873727087574</v>
       </c>
       <c r="C16">
         <f>IF(ISNA(nom_converted!C16),NA(),nom_converted!C16/nom_converted!$K16*100)</f>
-        <v>4.6159555326337829</v>
+        <v>5.1221995926680242</v>
       </c>
       <c r="D16">
         <f>IF(ISNA(nom_converted!D16),NA(),nom_converted!D16/nom_converted!$K16*100)</f>
-        <v>4.6159555326337829</v>
+        <v>5.1221995926680242</v>
       </c>
       <c r="E16">
         <f>IF(ISNA(nom_converted!E16),NA(),nom_converted!E16/nom_converted!$K16*100)</f>
-        <v>4.6159555326337829</v>
+        <v>5.1221995926680242</v>
       </c>
       <c r="F16">
         <f>IF(ISNA(nom_converted!F16),NA(),nom_converted!F16/nom_converted!$K16*100)</f>
-        <v>5.7905923282145455</v>
+        <v>6.4256619144602842</v>
       </c>
       <c r="G16">
         <f>IF(ISNA(nom_converted!G16),NA(),nom_converted!G16/nom_converted!$K16*100)</f>
-        <v>5.7905923282145455</v>
+        <v>6.4256619144602842</v>
       </c>
       <c r="H16">
         <f>IF(ISNA(nom_converted!H16),NA(),nom_converted!H16/nom_converted!$K16*100)</f>
-        <v>5.7905923282145455</v>
+        <v>6.4256619144602842</v>
       </c>
       <c r="I16">
         <f>IF(ISNA(nom_converted!I16),NA(),nom_converted!I16/nom_converted!$K16*100)</f>
-        <v>5.7905923282145455</v>
+        <v>6.4256619144602842</v>
       </c>
       <c r="J16">
         <f>IF(ISNA(nom_converted!J16),NA(),nom_converted!J16/nom_converted!$K16*100)</f>
-        <v>5.7905923282145455</v>
-      </c>
-      <c r="K16">
-        <v>108.9698539</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.4256619144602842</v>
+      </c>
+      <c r="K16" s="7">
+        <v>98.2</v>
+      </c>
+      <c r="L16">
+        <f>kaitz_index!D16</f>
+        <v>0.51051779935275077</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>2014</v>
       </c>
       <c r="B17">
         <f>IF(ISNA(nom_converted!B17),NA(),nom_converted!B17/nom_converted!$K17*100)</f>
-        <v>3.428277708520437</v>
+        <v>3.8052208835341368</v>
       </c>
       <c r="C17">
         <f>IF(ISNA(nom_converted!C17),NA(),nom_converted!C17/nom_converted!$K17*100)</f>
-        <v>4.6403864497915146</v>
+        <v>5.1506024096385543</v>
       </c>
       <c r="D17">
         <f>IF(ISNA(nom_converted!D17),NA(),nom_converted!D17/nom_converted!$K17*100)</f>
-        <v>4.6403864497915146</v>
+        <v>5.1506024096385543</v>
       </c>
       <c r="E17">
         <f>IF(ISNA(nom_converted!E17),NA(),nom_converted!E17/nom_converted!$K17*100)</f>
-        <v>4.6403864497915146</v>
+        <v>5.1506024096385543</v>
       </c>
       <c r="F17">
         <f>IF(ISNA(nom_converted!F17),NA(),nom_converted!F17/nom_converted!$K17*100)</f>
-        <v>5.8796319539268715</v>
+        <v>6.5261044176706831</v>
       </c>
       <c r="G17">
         <f>IF(ISNA(nom_converted!G17),NA(),nom_converted!G17/nom_converted!$K17*100)</f>
-        <v>5.8796319539268715</v>
+        <v>6.5261044176706831</v>
       </c>
       <c r="H17">
         <f>IF(ISNA(nom_converted!H17),NA(),nom_converted!H17/nom_converted!$K17*100)</f>
-        <v>5.8796319539268715</v>
+        <v>6.5261044176706831</v>
       </c>
       <c r="I17">
         <f>IF(ISNA(nom_converted!I17),NA(),nom_converted!I17/nom_converted!$K17*100)</f>
-        <v>5.8796319539268715</v>
+        <v>6.5261044176706831</v>
       </c>
       <c r="J17">
         <f>IF(ISNA(nom_converted!J17),NA(),nom_converted!J17/nom_converted!$K17*100)</f>
-        <v>5.8796319539268715</v>
-      </c>
-      <c r="K17">
-        <v>110.5511374</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.5261044176706831</v>
+      </c>
+      <c r="K17" s="7">
+        <v>99.6</v>
+      </c>
+      <c r="L17">
+        <f>kaitz_index!D17</f>
+        <v>0.51792828685258963</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>2015</v>
       </c>
       <c r="B18">
         <f>IF(ISNA(nom_converted!B18),NA(),nom_converted!B18/nom_converted!$K18*100)</f>
-        <v>3.4878056499953285</v>
+        <v>3.8699999999999997</v>
       </c>
       <c r="C18">
         <f>IF(ISNA(nom_converted!C18),NA(),nom_converted!C18/nom_converted!$K18*100)</f>
-        <v>4.7765813811305531</v>
+        <v>5.3</v>
       </c>
       <c r="D18">
         <f>IF(ISNA(nom_converted!D18),NA(),nom_converted!D18/nom_converted!$K18*100)</f>
-        <v>4.7765813811305531</v>
+        <v>5.3</v>
       </c>
       <c r="E18">
         <f>IF(ISNA(nom_converted!E18),NA(),nom_converted!E18/nom_converted!$K18*100)</f>
-        <v>4.7765813811305531</v>
+        <v>5.3</v>
       </c>
       <c r="F18">
         <f>IF(ISNA(nom_converted!F18),NA(),nom_converted!F18/nom_converted!$K18*100)</f>
-        <v>6.0383198591650391</v>
+        <v>6.7</v>
       </c>
       <c r="G18">
         <f>IF(ISNA(nom_converted!G18),NA(),nom_converted!G18/nom_converted!$K18*100)</f>
-        <v>6.0383198591650391</v>
+        <v>6.7</v>
       </c>
       <c r="H18">
         <f>IF(ISNA(nom_converted!H18),NA(),nom_converted!H18/nom_converted!$K18*100)</f>
-        <v>6.0383198591650391</v>
+        <v>6.7</v>
       </c>
       <c r="I18">
         <f>IF(ISNA(nom_converted!I18),NA(),nom_converted!I18/nom_converted!$K18*100)</f>
-        <v>6.0383198591650391</v>
+        <v>6.7</v>
       </c>
       <c r="J18">
         <f>IF(ISNA(nom_converted!J18),NA(),nom_converted!J18/nom_converted!$K18*100)</f>
-        <v>6.0383198591650391</v>
-      </c>
-      <c r="K18">
-        <v>110.9580174</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6.7</v>
+      </c>
+      <c r="K18" s="7">
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <f>kaitz_index!D18</f>
+        <v>0.52466718872357088</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>2016</v>
       </c>
       <c r="B19">
         <f>IF(ISNA(nom_converted!B19),NA(),nom_converted!B19/nom_converted!$K19*100)</f>
-        <v>3.4529851486225436</v>
+        <v>3.8316831683168315</v>
       </c>
       <c r="C19">
         <f>IF(ISNA(nom_converted!C19),NA(),nom_converted!C19/nom_converted!$K19*100)</f>
-        <v>4.7288943895864293</v>
+        <v>5.2475247524752477</v>
       </c>
       <c r="D19">
         <f>IF(ISNA(nom_converted!D19),NA(),nom_converted!D19/nom_converted!$K19*100)</f>
-        <v>4.7288943895864293</v>
+        <v>5.2475247524752477</v>
       </c>
       <c r="E19">
         <f>IF(ISNA(nom_converted!E19),NA(),nom_converted!E19/nom_converted!$K19*100)</f>
-        <v>4.7288943895864293</v>
+        <v>5.2475247524752477</v>
       </c>
       <c r="F19">
         <f>IF(ISNA(nom_converted!F19),NA(),nom_converted!F19/nom_converted!$K19*100)</f>
-        <v>5.9780363038168067</v>
+        <v>6.6336633663366342</v>
       </c>
       <c r="G19">
         <f>IF(ISNA(nom_converted!G19),NA(),nom_converted!G19/nom_converted!$K19*100)</f>
-        <v>5.9780363038168067</v>
+        <v>6.6336633663366342</v>
       </c>
       <c r="H19">
         <f>IF(ISNA(nom_converted!H19),NA(),nom_converted!H19/nom_converted!$K19*100)</f>
-        <v>5.9780363038168067</v>
+        <v>6.6336633663366342</v>
       </c>
       <c r="I19">
         <f>IF(ISNA(nom_converted!I19),NA(),nom_converted!I19/nom_converted!$K19*100)</f>
-        <v>5.9780363038168067</v>
+        <v>6.6336633663366342</v>
       </c>
       <c r="J19">
         <f>IF(ISNA(nom_converted!J19),NA(),nom_converted!J19/nom_converted!$K19*100)</f>
-        <v>6.4241584160419416</v>
-      </c>
-      <c r="K19">
-        <v>112.0769373</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.1287128712871297</v>
+      </c>
+      <c r="K19" s="7">
+        <v>101</v>
+      </c>
+      <c r="L19">
+        <f>kaitz_index!D19</f>
+        <v>0.54504163512490533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>2017</v>
       </c>
       <c r="B20">
         <f>IF(ISNA(nom_converted!B20),NA(),nom_converted!B20/nom_converted!$K20*100)</f>
-        <v>3.5234674187786559</v>
+        <v>3.9092664092664089</v>
       </c>
       <c r="C20">
         <f>IF(ISNA(nom_converted!C20),NA(),nom_converted!C20/nom_converted!$K20*100)</f>
-        <v>4.8719549494223386</v>
+        <v>5.4054054054054053</v>
       </c>
       <c r="D20">
         <f>IF(ISNA(nom_converted!D20),NA(),nom_converted!D20/nom_converted!$K20*100)</f>
-        <v>4.8719549494223386</v>
+        <v>5.4054054054054053</v>
       </c>
       <c r="E20">
         <f>IF(ISNA(nom_converted!E20),NA(),nom_converted!E20/nom_converted!$K20*100)</f>
-        <v>4.8719549494223386</v>
+        <v>5.4054054054054053</v>
       </c>
       <c r="F20">
         <f>IF(ISNA(nom_converted!F20),NA(),nom_converted!F20/nom_converted!$K20*100)</f>
-        <v>6.1334432845406228</v>
+        <v>6.8050193050193055</v>
       </c>
       <c r="G20">
         <f>IF(ISNA(nom_converted!G20),NA(),nom_converted!G20/nom_converted!$K20*100)</f>
-        <v>6.1334432845406228</v>
+        <v>6.8050193050193055</v>
       </c>
       <c r="H20">
         <f>IF(ISNA(nom_converted!H20),NA(),nom_converted!H20/nom_converted!$K20*100)</f>
-        <v>6.1334432845406228</v>
+        <v>6.8050193050193055</v>
       </c>
       <c r="I20">
         <f>IF(ISNA(nom_converted!I20),NA(),nom_converted!I20/nom_converted!$K20*100)</f>
-        <v>6.1334432845406228</v>
+        <v>6.8050193050193055</v>
       </c>
       <c r="J20">
         <f>IF(ISNA(nom_converted!J20),NA(),nom_converted!J20/nom_converted!$K20*100)</f>
-        <v>6.5249396644049176</v>
-      </c>
-      <c r="K20">
-        <v>114.9435916</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.2393822393822402</v>
+      </c>
+      <c r="K20" s="7">
+        <v>103.6</v>
+      </c>
+      <c r="L20">
+        <f>kaitz_index!D20</f>
+        <v>0.54824561403508776</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2018</v>
       </c>
       <c r="B21">
         <f>IF(ISNA(nom_converted!B21),NA(),nom_converted!B21/nom_converted!$K21*100)</f>
-        <v>3.5720644900318912</v>
+        <v>3.9622641509433967</v>
       </c>
       <c r="C21">
         <f>IF(ISNA(nom_converted!C21),NA(),nom_converted!C21/nom_converted!$K21*100)</f>
-        <v>5.0179001169495612</v>
+        <v>5.5660377358490569</v>
       </c>
       <c r="D21">
         <f>IF(ISNA(nom_converted!D21),NA(),nom_converted!D21/nom_converted!$K21*100)</f>
-        <v>5.0179001169495612</v>
+        <v>5.5660377358490569</v>
       </c>
       <c r="E21">
         <f>IF(ISNA(nom_converted!E21),NA(),nom_converted!E21/nom_converted!$K21*100)</f>
-        <v>5.0179001169495612</v>
+        <v>5.5660377358490569</v>
       </c>
       <c r="F21">
         <f>IF(ISNA(nom_converted!F21),NA(),nom_converted!F21/nom_converted!$K21*100)</f>
-        <v>6.2766276039131803</v>
+        <v>6.9622641509433967</v>
       </c>
       <c r="G21">
         <f>IF(ISNA(nom_converted!G21),NA(),nom_converted!G21/nom_converted!$K21*100)</f>
-        <v>6.2766276039131803</v>
+        <v>6.9622641509433967</v>
       </c>
       <c r="H21">
         <f>IF(ISNA(nom_converted!H21),NA(),nom_converted!H21/nom_converted!$K21*100)</f>
-        <v>6.2766276039131803</v>
+        <v>6.9622641509433967</v>
       </c>
       <c r="I21">
         <f>IF(ISNA(nom_converted!I21),NA(),nom_converted!I21/nom_converted!$K21*100)</f>
-        <v>6.2766276039131803</v>
+        <v>6.9622641509433967</v>
       </c>
       <c r="J21">
         <f>IF(ISNA(nom_converted!J21),NA(),nom_converted!J21/nom_converted!$K21*100)</f>
-        <v>6.6593487992737401</v>
-      </c>
-      <c r="K21">
-        <v>117.5790642</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.3867924528301891</v>
+      </c>
+      <c r="K21" s="7">
+        <v>106</v>
+      </c>
+      <c r="L21">
+        <f>kaitz_index!D21</f>
+        <v>0.55729537366548043</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>2019</v>
       </c>
       <c r="B22">
         <f>IF(ISNA(nom_converted!B22),NA(),nom_converted!B22/nom_converted!$K22*100)</f>
-        <v>3.6364332096525551</v>
+        <v>4.0352504638218916</v>
       </c>
       <c r="C22">
         <f>IF(ISNA(nom_converted!C22),NA(),nom_converted!C22/nom_converted!$K22*100)</f>
-        <v>5.1411641929570608</v>
+        <v>5.7050092764378482</v>
       </c>
       <c r="D22">
         <f>IF(ISNA(nom_converted!D22),NA(),nom_converted!D22/nom_converted!$K22*100)</f>
-        <v>5.1411641929570608</v>
+        <v>5.7050092764378482</v>
       </c>
       <c r="E22">
         <f>IF(ISNA(nom_converted!E22),NA(),nom_converted!E22/nom_converted!$K22*100)</f>
-        <v>5.1411641929570608</v>
+        <v>5.7050092764378482</v>
       </c>
       <c r="F22">
         <f>IF(ISNA(nom_converted!F22),NA(),nom_converted!F22/nom_converted!$K22*100)</f>
-        <v>6.4369047619137181</v>
+        <v>7.1428571428571441</v>
       </c>
       <c r="G22">
         <f>IF(ISNA(nom_converted!G22),NA(),nom_converted!G22/nom_converted!$K22*100)</f>
-        <v>6.4369047619137181</v>
+        <v>7.1428571428571441</v>
       </c>
       <c r="H22">
         <f>IF(ISNA(nom_converted!H22),NA(),nom_converted!H22/nom_converted!$K22*100)</f>
-        <v>6.4369047619137181</v>
+        <v>7.1428571428571441</v>
       </c>
       <c r="I22">
         <f>IF(ISNA(nom_converted!I22),NA(),nom_converted!I22/nom_converted!$K22*100)</f>
-        <v>6.4369047619137181</v>
+        <v>7.1428571428571441</v>
       </c>
       <c r="J22">
         <f>IF(ISNA(nom_converted!J22),NA(),nom_converted!J22/nom_converted!$K22*100)</f>
-        <v>6.8632452071833283</v>
-      </c>
-      <c r="K22">
-        <v>119.62271130000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.6159554730983308</v>
+      </c>
+      <c r="K22" s="7">
+        <v>107.8</v>
+      </c>
+      <c r="L22">
+        <f>kaitz_index!D22</f>
+        <v>0.56659765355417535</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2020</v>
       </c>
       <c r="B23">
         <f>IF(ISNA(nom_converted!B23),NA(),nom_converted!B23/nom_converted!$K23*100)</f>
-        <v>3.7663579309123154</v>
+        <v>4.178145087235996</v>
       </c>
       <c r="C23">
         <f>IF(ISNA(nom_converted!C23),NA(),nom_converted!C23/nom_converted!$K23*100)</f>
-        <v>5.3391227811833923</v>
+        <v>5.9228650137741052</v>
       </c>
       <c r="D23">
         <f>IF(ISNA(nom_converted!D23),NA(),nom_converted!D23/nom_converted!$K23*100)</f>
-        <v>5.3391227811833923</v>
+        <v>5.9228650137741052</v>
       </c>
       <c r="E23">
         <f>IF(ISNA(nom_converted!E23),NA(),nom_converted!E23/nom_converted!$K23*100)</f>
-        <v>5.3391227811833923</v>
+        <v>5.9228650137741052</v>
       </c>
       <c r="F23">
         <f>IF(ISNA(nom_converted!F23),NA(),nom_converted!F23/nom_converted!$K23*100)</f>
-        <v>6.7877219853804363</v>
+        <v>7.5298438934802565</v>
       </c>
       <c r="G23">
         <f>IF(ISNA(nom_converted!G23),NA(),nom_converted!G23/nom_converted!$K23*100)</f>
-        <v>6.7877219853804363</v>
+        <v>7.5298438934802565</v>
       </c>
       <c r="H23">
         <f>IF(ISNA(nom_converted!H23),NA(),nom_converted!H23/nom_converted!$K23*100)</f>
-        <v>6.7877219853804363</v>
+        <v>7.5298438934802565</v>
       </c>
       <c r="I23">
         <f>IF(ISNA(nom_converted!I23),NA(),nom_converted!I23/nom_converted!$K23*100)</f>
-        <v>6.7877219853804363</v>
+        <v>7.5298438934802565</v>
       </c>
       <c r="J23">
         <f>IF(ISNA(nom_converted!J23),NA(),nom_converted!J23/nom_converted!$K23*100)</f>
-        <v>7.2181628917704161</v>
-      </c>
-      <c r="K23">
-        <v>120.8063621</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8.0073461891643714</v>
+      </c>
+      <c r="K23" s="7">
+        <v>108.9</v>
+      </c>
+      <c r="L23">
+        <f>kaitz_index!D23</f>
+        <v>0.58602150537634412</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>2021</v>
       </c>
       <c r="B24">
         <f>IF(ISNA(nom_converted!B24),NA(),nom_converted!B24/nom_converted!$K24*100)</f>
-        <v>3.7303576503974472</v>
+        <v>4.1397849462365599</v>
       </c>
       <c r="C24">
         <f>IF(ISNA(nom_converted!C24),NA(),nom_converted!C24/nom_converted!$K24*100)</f>
-        <v>5.2967848888760285</v>
+        <v>5.8781362007168454</v>
       </c>
       <c r="D24">
         <f>IF(ISNA(nom_converted!D24),NA(),nom_converted!D24/nom_converted!$K24*100)</f>
-        <v>5.2967848888760285</v>
+        <v>5.8781362007168454</v>
       </c>
       <c r="E24">
         <f>IF(ISNA(nom_converted!E24),NA(),nom_converted!E24/nom_converted!$K24*100)</f>
-        <v>5.2967848888760285</v>
+        <v>5.8781362007168454</v>
       </c>
       <c r="F24">
         <f>IF(ISNA(nom_converted!F24),NA(),nom_converted!F24/nom_converted!$K24*100)</f>
-        <v>6.7501709864334751</v>
+        <v>7.4910394265232982</v>
       </c>
       <c r="G24">
         <f>IF(ISNA(nom_converted!G24),NA(),nom_converted!G24/nom_converted!$K24*100)</f>
-        <v>6.7501709864334751</v>
+        <v>7.4910394265232982</v>
       </c>
       <c r="H24">
         <f>IF(ISNA(nom_converted!H24),NA(),nom_converted!H24/nom_converted!$K24*100)</f>
-        <v>7.1942611829093632</v>
+        <v>7.9838709677419368</v>
       </c>
       <c r="I24">
         <f>IF(ISNA(nom_converted!I24),NA(),nom_converted!I24/nom_converted!$K24*100)</f>
-        <v>7.1942611829093632</v>
+        <v>7.9838709677419368</v>
       </c>
       <c r="J24">
         <f>IF(ISNA(nom_converted!J24),NA(),nom_converted!J24/nom_converted!$K24*100)</f>
-        <v>7.1942611829093632</v>
-      </c>
-      <c r="K24">
-        <v>123.84871459999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.9838709677419368</v>
+      </c>
+      <c r="K24" s="7">
+        <v>111.6</v>
+      </c>
+      <c r="L24">
+        <f>kaitz_index!D24</f>
+        <v>0.58541392904073586</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>2022</v>
       </c>
       <c r="B25">
         <f>IF(ISNA(nom_converted!B25),NA(),nom_converted!B25/nom_converted!$K25*100)</f>
-        <v>3.5986813333286114</v>
+        <v>3.9917012448132776</v>
       </c>
       <c r="C25">
         <f>IF(ISNA(nom_converted!C25),NA(),nom_converted!C25/nom_converted!$K25*100)</f>
-        <v>5.1099778600071559</v>
+        <v>5.6680497925311206</v>
       </c>
       <c r="D25">
         <f>IF(ISNA(nom_converted!D25),NA(),nom_converted!D25/nom_converted!$K25*100)</f>
-        <v>5.1099778600071559</v>
+        <v>5.6680497925311206</v>
       </c>
       <c r="E25">
         <f>IF(ISNA(nom_converted!E25),NA(),nom_converted!E25/nom_converted!$K25*100)</f>
-        <v>5.1099778600071559</v>
+        <v>5.6680497925311206</v>
       </c>
       <c r="F25">
         <f>IF(ISNA(nom_converted!F25),NA(),nom_converted!F25/nom_converted!$K25*100)</f>
-        <v>6.8681693638163521</v>
+        <v>7.618257261410788</v>
       </c>
       <c r="G25">
         <f>IF(ISNA(nom_converted!G25),NA(),nom_converted!G25/nom_converted!$K25*100)</f>
-        <v>6.8681693638163521</v>
+        <v>7.618257261410788</v>
       </c>
       <c r="H25">
         <f>IF(ISNA(nom_converted!H25),NA(),nom_converted!H25/nom_converted!$K25*100)</f>
-        <v>7.1075826749733491</v>
+        <v>7.8838174273858916</v>
       </c>
       <c r="I25">
         <f>IF(ISNA(nom_converted!I25),NA(),nom_converted!I25/nom_converted!$K25*100)</f>
-        <v>7.1075826749733491</v>
+        <v>7.8838174273858916</v>
       </c>
       <c r="J25">
         <f>IF(ISNA(nom_converted!J25),NA(),nom_converted!J25/nom_converted!$K25*100)</f>
-        <v>7.1075826749733491</v>
-      </c>
-      <c r="K25">
-        <v>133.6600703</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.8838174273858916</v>
+      </c>
+      <c r="K25" s="7">
+        <v>120.5</v>
+      </c>
+      <c r="L25">
+        <f>kaitz_index!D25</f>
+        <v>0.59635907093534213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>2023</v>
       </c>
       <c r="B26">
         <f>IF(ISNA(nom_converted!B26),NA(),nom_converted!B26/nom_converted!$K26*100)</f>
-        <v>3.6990101072046406</v>
+        <v>4.1057542768273718</v>
       </c>
       <c r="C26">
         <f>IF(ISNA(nom_converted!C26),NA(),nom_converted!C26/nom_converted!$K26*100)</f>
-        <v>5.2472700195005224</v>
+        <v>5.8242612752721623</v>
       </c>
       <c r="D26">
         <f>IF(ISNA(nom_converted!D26),NA(),nom_converted!D26/nom_converted!$K26*100)</f>
-        <v>5.2472700195005224</v>
+        <v>5.8242612752721623</v>
       </c>
       <c r="E26">
         <f>IF(ISNA(nom_converted!E26),NA(),nom_converted!E26/nom_converted!$K26*100)</f>
-        <v>5.2472700195005224</v>
+        <v>5.8242612752721623</v>
       </c>
       <c r="F26">
         <f>IF(ISNA(nom_converted!F26),NA(),nom_converted!F26/nom_converted!$K26*100)</f>
-        <v>7.1318035779059166</v>
+        <v>7.9160186625194404</v>
       </c>
       <c r="G26">
         <f>IF(ISNA(nom_converted!G26),NA(),nom_converted!G26/nom_converted!$K26*100)</f>
-        <v>7.1318035779059166</v>
+        <v>7.9160186625194404</v>
       </c>
       <c r="H26">
         <f>IF(ISNA(nom_converted!H26),NA(),nom_converted!H26/nom_converted!$K26*100)</f>
-        <v>7.2999404009606739</v>
+        <v>8.1026438569206842</v>
       </c>
       <c r="I26">
         <f>IF(ISNA(nom_converted!I26),NA(),nom_converted!I26/nom_converted!$K26*100)</f>
-        <v>7.2999404009606739</v>
+        <v>8.1026438569206842</v>
       </c>
       <c r="J26">
         <f>IF(ISNA(nom_converted!J26),NA(),nom_converted!J26/nom_converted!$K26*100)</f>
-        <v>7.2999404009606739</v>
-      </c>
-      <c r="K26">
-        <v>142.74089140000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8.1026438569206842</v>
+      </c>
+      <c r="K26" s="7">
+        <v>128.6</v>
+      </c>
+      <c r="L26">
+        <f>kaitz_index!D26</f>
+        <v>0.59474885844748859</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>2024</v>
       </c>
       <c r="B27">
         <f>IF(ISNA(nom_converted!B27),NA(),nom_converted!B27/nom_converted!$K27*100)</f>
-        <v>4.3416096864427214</v>
+        <v>4.8156508653122643</v>
       </c>
       <c r="C27">
         <f>IF(ISNA(nom_converted!C27),NA(),nom_converted!C27/nom_converted!$K27*100)</f>
-        <v>5.8340380161574057</v>
+        <v>6.4710308502633556</v>
       </c>
       <c r="D27">
         <f>IF(ISNA(nom_converted!D27),NA(),nom_converted!D27/nom_converted!$K27*100)</f>
-        <v>5.8340380161574057</v>
+        <v>6.4710308502633556</v>
       </c>
       <c r="E27">
         <f>IF(ISNA(nom_converted!E27),NA(),nom_converted!E27/nom_converted!$K27*100)</f>
-        <v>5.8340380161574057</v>
+        <v>6.4710308502633556</v>
       </c>
       <c r="F27">
         <f>IF(ISNA(nom_converted!F27),NA(),nom_converted!F27/nom_converted!$K27*100)</f>
-        <v>7.7606273145163618</v>
+        <v>8.6079759217456733</v>
       </c>
       <c r="G27">
         <f>IF(ISNA(nom_converted!G27),NA(),nom_converted!G27/nom_converted!$K27*100)</f>
-        <v>7.7606273145163618</v>
+        <v>8.6079759217456733</v>
       </c>
       <c r="H27">
         <f>IF(ISNA(nom_converted!H27),NA(),nom_converted!H27/nom_converted!$K27*100)</f>
-        <v>7.7606273145163618</v>
+        <v>8.6079759217456733</v>
       </c>
       <c r="I27">
         <f>IF(ISNA(nom_converted!I27),NA(),nom_converted!I27/nom_converted!$K27*100)</f>
-        <v>7.7606273145163618</v>
+        <v>8.6079759217456733</v>
       </c>
       <c r="J27">
         <f>IF(ISNA(nom_converted!J27),NA(),nom_converted!J27/nom_converted!$K27*100)</f>
-        <v>7.7606273145163618</v>
-      </c>
-      <c r="K27">
-        <v>147.41076380000001</v>
+        <v>8.6079759217456733</v>
+      </c>
+      <c r="K27" s="7">
+        <v>132.9</v>
+      </c>
+      <c r="L27">
+        <f>kaitz_index!D27</f>
+        <v>0.61307609860664525</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B28">
+        <f>IF(ISNA(nom_converted!B28),NA(),nom_converted!B28/nom_converted!$K28*100)</f>
+        <v>5.4710144927536231</v>
+      </c>
+      <c r="C28">
+        <f>IF(ISNA(nom_converted!C28),NA(),nom_converted!C28/nom_converted!$K28*100)</f>
+        <v>7.2463768115942031</v>
+      </c>
+      <c r="D28">
+        <f>IF(ISNA(nom_converted!D28),NA(),nom_converted!D28/nom_converted!$K28*100)</f>
+        <v>7.2463768115942031</v>
+      </c>
+      <c r="E28">
+        <f>IF(ISNA(nom_converted!E28),NA(),nom_converted!E28/nom_converted!$K28*100)</f>
+        <v>7.2463768115942031</v>
+      </c>
+      <c r="F28">
+        <f>IF(ISNA(nom_converted!F28),NA(),nom_converted!F28/nom_converted!$K28*100)</f>
+        <v>8.8478260869565233</v>
+      </c>
+      <c r="G28">
+        <f>IF(ISNA(nom_converted!G28),NA(),nom_converted!G28/nom_converted!$K28*100)</f>
+        <v>8.8478260869565233</v>
+      </c>
+      <c r="H28">
+        <f>IF(ISNA(nom_converted!H28),NA(),nom_converted!H28/nom_converted!$K28*100)</f>
+        <v>8.8478260869565233</v>
+      </c>
+      <c r="I28">
+        <f>IF(ISNA(nom_converted!I28),NA(),nom_converted!I28/nom_converted!$K28*100)</f>
+        <v>8.8478260869565233</v>
+      </c>
+      <c r="J28">
+        <f>IF(ISNA(nom_converted!J28),NA(),nom_converted!J28/nom_converted!$K28*100)</f>
+        <v>8.8478260869565233</v>
+      </c>
+      <c r="K28" s="7">
+        <v>138</v>
+      </c>
+      <c r="L28">
+        <f>kaitz_index!D28</f>
+        <v>0.62074224707676662</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F133FA42-F8F1-4246-9D15-DCE9513EE795}">
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>1999</v>
+      </c>
+      <c r="B2" s="10">
+        <v>3.6</v>
+      </c>
+      <c r="C2" s="10">
+        <v>8.32</v>
+      </c>
+      <c r="D2" s="11">
+        <f>B2/C2</f>
+        <v>0.43269230769230771</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>2000</v>
+      </c>
+      <c r="B3" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="C3" s="10">
+        <v>8.65</v>
+      </c>
+      <c r="D3" s="11">
+        <f t="shared" ref="D3:D28" si="0">B3/C3</f>
+        <v>0.4277456647398844</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>2001</v>
+      </c>
+      <c r="B4" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="10">
+        <v>9</v>
+      </c>
+      <c r="D4" s="11">
+        <f t="shared" si="0"/>
+        <v>0.45555555555555549</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>2002</v>
+      </c>
+      <c r="B5" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="C5" s="10">
+        <v>9.36</v>
+      </c>
+      <c r="D5" s="11">
+        <f t="shared" si="0"/>
+        <v>0.44871794871794879</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>2003</v>
+      </c>
+      <c r="B6" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="C6" s="10">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="D6" s="11">
+        <f t="shared" si="0"/>
+        <v>0.46343975283213179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>2004</v>
+      </c>
+      <c r="B7" s="10">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="C7" s="10">
+        <v>10.09</v>
+      </c>
+      <c r="D7" s="11">
+        <f t="shared" si="0"/>
+        <v>0.48067393458870167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>2005</v>
+      </c>
+      <c r="B8" s="10">
+        <v>5.05</v>
+      </c>
+      <c r="C8" s="10">
+        <v>10.37</v>
+      </c>
+      <c r="D8" s="11">
+        <f t="shared" si="0"/>
+        <v>0.48698167791706848</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>2006</v>
+      </c>
+      <c r="B9" s="10">
+        <v>5.35</v>
+      </c>
+      <c r="C9" s="10">
+        <v>10.72</v>
+      </c>
+      <c r="D9" s="11">
+        <f t="shared" si="0"/>
+        <v>0.49906716417910441</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>2007</v>
+      </c>
+      <c r="B10" s="10">
+        <v>5.52</v>
+      </c>
+      <c r="C10" s="10">
+        <v>11.05</v>
+      </c>
+      <c r="D10" s="11">
+        <f t="shared" si="0"/>
+        <v>0.49954751131221714</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>2008</v>
+      </c>
+      <c r="B11" s="10">
+        <v>5.73</v>
+      </c>
+      <c r="C11" s="10">
+        <v>11.37</v>
+      </c>
+      <c r="D11" s="11">
+        <f t="shared" si="0"/>
+        <v>0.50395778364116106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>2009</v>
+      </c>
+      <c r="B12" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="C12" s="10">
+        <v>11.57</v>
+      </c>
+      <c r="D12" s="11">
+        <f t="shared" si="0"/>
+        <v>0.50129645635263609</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>2010</v>
+      </c>
+      <c r="B13" s="10">
+        <v>5.93</v>
+      </c>
+      <c r="C13" s="10">
+        <v>11.85</v>
+      </c>
+      <c r="D13" s="11">
+        <f t="shared" si="0"/>
+        <v>0.50042194092827008</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>2011</v>
+      </c>
+      <c r="B14" s="10">
+        <v>6.08</v>
+      </c>
+      <c r="C14" s="10">
+        <v>12.06</v>
+      </c>
+      <c r="D14" s="11">
+        <f t="shared" si="0"/>
+        <v>0.50414593698175791</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>2012</v>
+      </c>
+      <c r="B15" s="10">
+        <v>6.19</v>
+      </c>
+      <c r="C15" s="10">
+        <v>12.21</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="0"/>
+        <v>0.50696150696150699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>2013</v>
+      </c>
+      <c r="B16" s="10">
+        <v>6.31</v>
+      </c>
+      <c r="C16" s="10">
+        <v>12.36</v>
+      </c>
+      <c r="D16" s="11">
+        <f t="shared" si="0"/>
+        <v>0.51051779935275077</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>2014</v>
+      </c>
+      <c r="B17" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="C17" s="10">
+        <v>12.55</v>
+      </c>
+      <c r="D17" s="11">
+        <f t="shared" si="0"/>
+        <v>0.51792828685258963</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>2015</v>
+      </c>
+      <c r="B18" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="C18" s="10">
+        <v>12.77</v>
+      </c>
+      <c r="D18" s="11">
+        <f t="shared" si="0"/>
+        <v>0.52466718872357088</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>2016</v>
+      </c>
+      <c r="B19" s="10">
+        <v>7.2</v>
+      </c>
+      <c r="C19" s="10">
+        <v>13.21</v>
+      </c>
+      <c r="D19" s="11">
+        <f t="shared" si="0"/>
+        <v>0.54504163512490533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>2017</v>
+      </c>
+      <c r="B20" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="C20" s="10">
+        <v>13.68</v>
+      </c>
+      <c r="D20" s="11">
+        <f t="shared" si="0"/>
+        <v>0.54824561403508776</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>2018</v>
+      </c>
+      <c r="B21" s="10">
+        <v>7.83</v>
+      </c>
+      <c r="C21" s="10">
+        <v>14.05</v>
+      </c>
+      <c r="D21" s="11">
+        <f t="shared" si="0"/>
+        <v>0.55729537366548043</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>2019</v>
+      </c>
+      <c r="B22" s="10">
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="C22" s="10">
+        <v>14.49</v>
+      </c>
+      <c r="D22" s="11">
+        <f t="shared" si="0"/>
+        <v>0.56659765355417535</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>2020</v>
+      </c>
+      <c r="B23" s="10">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="C23" s="10">
+        <v>14.88</v>
+      </c>
+      <c r="D23" s="11">
+        <f t="shared" si="0"/>
+        <v>0.58602150537634412</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
+        <v>2021</v>
+      </c>
+      <c r="B24" s="10">
+        <v>8.91</v>
+      </c>
+      <c r="C24" s="10">
+        <v>15.22</v>
+      </c>
+      <c r="D24" s="11">
+        <f t="shared" si="0"/>
+        <v>0.58541392904073586</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <v>2022</v>
+      </c>
+      <c r="B25" s="10">
+        <v>9.5</v>
+      </c>
+      <c r="C25" s="10">
+        <v>15.93</v>
+      </c>
+      <c r="D25" s="11">
+        <f t="shared" si="0"/>
+        <v>0.59635907093534213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
+        <v>2023</v>
+      </c>
+      <c r="B26" s="10">
+        <v>10.42</v>
+      </c>
+      <c r="C26" s="10">
+        <v>17.52</v>
+      </c>
+      <c r="D26" s="11">
+        <f t="shared" si="0"/>
+        <v>0.59474885844748859</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B27" s="10">
+        <v>11.44</v>
+      </c>
+      <c r="C27" s="10">
+        <v>18.66</v>
+      </c>
+      <c r="D27" s="11">
+        <f t="shared" si="0"/>
+        <v>0.61307609860664525</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B28" s="8">
+        <v>12.21</v>
+      </c>
+      <c r="C28" s="10">
+        <v>19.670000000000002</v>
+      </c>
+      <c r="D28" s="11">
+        <f t="shared" si="0"/>
+        <v>0.62074224707676662</v>
       </c>
     </row>
   </sheetData>
